--- a/Data/National Accounts/PSA-10MFG_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-10MFG_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1601C7-F16B-4B0A-9C3E-ECB837A428F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2659EF9-FEF4-401D-A1EE-479576852F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="MFG" sheetId="10" r:id="rId1"/>
@@ -742,10 +742,10 @@
     <t>Table 11.7 Gross Value Added in Manufacturing, by Industry</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -793,10 +793,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1261,7 +1263,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1271,7 +1273,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -2051,28 +2053,28 @@
         <v>739921.86273153918</v>
       </c>
       <c r="CT12" s="18">
-        <v>652765.08463331964</v>
+        <v>652803.95551031455</v>
       </c>
       <c r="CU12" s="18">
-        <v>466604.21930988552</v>
+        <v>466605.56002555974</v>
       </c>
       <c r="CV12" s="18">
-        <v>317387.52750569675</v>
+        <v>317612.301866116</v>
       </c>
       <c r="CW12" s="18">
-        <v>792200.13741566241</v>
+        <v>791388.74369322602</v>
       </c>
       <c r="CX12" s="18">
-        <v>725160.69822619599</v>
+        <v>725339.24960295158</v>
       </c>
       <c r="CY12" s="18">
-        <v>517331.57083265297</v>
+        <v>516052.68870181474</v>
       </c>
       <c r="CZ12" s="18">
-        <v>355264.50230980269</v>
+        <v>353846.83479139139</v>
       </c>
       <c r="DA12" s="18">
-        <v>842693.78403568966</v>
+        <v>843036.00159373693</v>
       </c>
       <c r="DB12" s="8"/>
       <c r="DC12" s="8"/>
@@ -2445,25 +2447,25 @@
         <v>34671.473660445023</v>
       </c>
       <c r="CU13" s="18">
-        <v>37861.238055089772</v>
+        <v>38339.235616951526</v>
       </c>
       <c r="CV13" s="18">
-        <v>70664.100874267649</v>
+        <v>69764.463867217186</v>
       </c>
       <c r="CW13" s="18">
-        <v>61460.354977993484</v>
+        <v>60837.500524964184</v>
       </c>
       <c r="CX13" s="18">
-        <v>34991.23476469981</v>
+        <v>34992.251361903902</v>
       </c>
       <c r="CY13" s="18">
-        <v>37035.199897113562</v>
+        <v>37344.394541419315</v>
       </c>
       <c r="CZ13" s="18">
-        <v>64978.50874019209</v>
+        <v>64176.430393890696</v>
       </c>
       <c r="DA13" s="18">
-        <v>58597.995876494395</v>
+        <v>58143.645237766279</v>
       </c>
       <c r="DB13" s="8"/>
       <c r="DC13" s="8"/>
@@ -2842,19 +2844,19 @@
         <v>5788.5890671431025</v>
       </c>
       <c r="CW14" s="18">
-        <v>3409.372387895306</v>
+        <v>3440.0731588684121</v>
       </c>
       <c r="CX14" s="18">
-        <v>2709.8794167779797</v>
+        <v>2711.5990015773696</v>
       </c>
       <c r="CY14" s="18">
-        <v>3077.5657362847642</v>
+        <v>3070.4467353869186</v>
       </c>
       <c r="CZ14" s="18">
-        <v>6466.5519475278761</v>
+        <v>6505.9924939683769</v>
       </c>
       <c r="DA14" s="18">
-        <v>3795.6514633118086</v>
+        <v>3830.2896871736684</v>
       </c>
       <c r="DB14" s="8"/>
       <c r="DC14" s="8"/>
@@ -3224,28 +3226,28 @@
         <v>11425.060090716914</v>
       </c>
       <c r="CT15" s="18">
-        <v>7612.5259160094465</v>
+        <v>7501.5541159378081</v>
       </c>
       <c r="CU15" s="18">
         <v>8816.4836895156877</v>
       </c>
       <c r="CV15" s="18">
-        <v>10447.723926306637</v>
+        <v>10503.971969998816</v>
       </c>
       <c r="CW15" s="18">
-        <v>10787.096490446507</v>
+        <v>10777.81311524265</v>
       </c>
       <c r="CX15" s="18">
-        <v>9258.9047215758474</v>
+        <v>9005.294187067826</v>
       </c>
       <c r="CY15" s="18">
         <v>9468.1547354707618</v>
       </c>
       <c r="CZ15" s="18">
-        <v>11840.280431904212</v>
+        <v>11904.025666345613</v>
       </c>
       <c r="DA15" s="18">
-        <v>10024.233730706997</v>
+        <v>9878.8490943499964</v>
       </c>
       <c r="DB15" s="8"/>
       <c r="DC15" s="8"/>
@@ -3621,22 +3623,22 @@
         <v>10138.776589738296</v>
       </c>
       <c r="CV16" s="18">
-        <v>13549.020415327257</v>
+        <v>13551.313181385492</v>
       </c>
       <c r="CW16" s="18">
-        <v>8412.9038523777781</v>
+        <v>8427.8717803730688</v>
       </c>
       <c r="CX16" s="18">
-        <v>11465.476852887688</v>
+        <v>11576.835865076846</v>
       </c>
       <c r="CY16" s="18">
-        <v>9890.3445600700816</v>
+        <v>9891.3385753632465</v>
       </c>
       <c r="CZ16" s="18">
-        <v>12610.654437627978</v>
+        <v>12573.423159422535</v>
       </c>
       <c r="DA16" s="18">
-        <v>7960.5465825408719</v>
+        <v>8000.6917150929221</v>
       </c>
       <c r="DB16" s="8"/>
       <c r="DC16" s="8"/>
@@ -4015,19 +4017,19 @@
         <v>2179.9556931339048</v>
       </c>
       <c r="CW17" s="18">
-        <v>6586.0845030181026</v>
+        <v>6618.6398187111499</v>
       </c>
       <c r="CX17" s="18">
-        <v>2655.1327440875102</v>
+        <v>2634.031312713003</v>
       </c>
       <c r="CY17" s="18">
-        <v>1882.5464334738153</v>
+        <v>1886.5130083780955</v>
       </c>
       <c r="CZ17" s="18">
-        <v>2340.9835855942933</v>
+        <v>2326.3832894072102</v>
       </c>
       <c r="DA17" s="18">
-        <v>7166.2168193593207</v>
+        <v>7279.3142165950012</v>
       </c>
       <c r="DB17" s="8"/>
       <c r="DC17" s="8"/>
@@ -4397,7 +4399,7 @@
         <v>11762.637796863324</v>
       </c>
       <c r="CT18" s="18">
-        <v>5036.5026534118515</v>
+        <v>5125.0445884274304</v>
       </c>
       <c r="CU18" s="18">
         <v>5536.1973702793912</v>
@@ -4406,19 +4408,19 @@
         <v>4030.9399629234704</v>
       </c>
       <c r="CW18" s="18">
-        <v>11786.141970676079</v>
+        <v>11808.504710241454</v>
       </c>
       <c r="CX18" s="18">
-        <v>5482.2809535537162</v>
+        <v>5455.4881546191646</v>
       </c>
       <c r="CY18" s="18">
-        <v>6192.7117038197321</v>
+        <v>6248.7212187093755</v>
       </c>
       <c r="CZ18" s="18">
-        <v>4025.2397895278409</v>
+        <v>4011.4102042900558</v>
       </c>
       <c r="DA18" s="18">
-        <v>13304.233400173689</v>
+        <v>13349.035817676442</v>
       </c>
       <c r="DB18" s="8"/>
       <c r="DC18" s="8"/>
@@ -4794,22 +4796,22 @@
         <v>6562.5373744854769</v>
       </c>
       <c r="CV19" s="18">
-        <v>8901.2404627608266</v>
+        <v>8901.048772566588</v>
       </c>
       <c r="CW19" s="18">
-        <v>6374.2278474744671</v>
+        <v>6546.2469925851656</v>
       </c>
       <c r="CX19" s="18">
-        <v>6535.2678221002461</v>
+        <v>6364.3547760292931</v>
       </c>
       <c r="CY19" s="18">
-        <v>6759.9264127084389</v>
+        <v>6467.5468610922289</v>
       </c>
       <c r="CZ19" s="18">
-        <v>9185.8853199791702</v>
+        <v>9184.5316726311794</v>
       </c>
       <c r="DA19" s="18">
-        <v>6654.6646724554266</v>
+        <v>6865.8499506906701</v>
       </c>
       <c r="DB19" s="8"/>
       <c r="DC19" s="8"/>
@@ -5188,19 +5190,19 @@
         <v>3996.3728275373805</v>
       </c>
       <c r="CW20" s="18">
-        <v>10586.966128664761</v>
+        <v>10574.44918417195</v>
       </c>
       <c r="CX20" s="18">
-        <v>11246.357030636907</v>
+        <v>10800.472694292406</v>
       </c>
       <c r="CY20" s="18">
-        <v>13623.880283045895</v>
+        <v>13292.164068710536</v>
       </c>
       <c r="CZ20" s="18">
-        <v>3761.8324339080218</v>
+        <v>3780.2728390869797</v>
       </c>
       <c r="DA20" s="18">
-        <v>9618.985555903364</v>
+        <v>9245.4713167641967</v>
       </c>
       <c r="DB20" s="8"/>
       <c r="DC20" s="8"/>
@@ -5579,19 +5581,19 @@
         <v>13399.385203797865</v>
       </c>
       <c r="CW21" s="18">
-        <v>63973.454734673403</v>
+        <v>64853.207270038954</v>
       </c>
       <c r="CX21" s="18">
-        <v>16519.357809588459</v>
+        <v>16533.56085914767</v>
       </c>
       <c r="CY21" s="18">
-        <v>49577.166037735529</v>
+        <v>49871.327742005204</v>
       </c>
       <c r="CZ21" s="18">
-        <v>12224.013275266028</v>
+        <v>12257.099537546863</v>
       </c>
       <c r="DA21" s="18">
-        <v>61584.074259903078</v>
+        <v>62419.04300002128</v>
       </c>
       <c r="DB21" s="8"/>
       <c r="DC21" s="8"/>
@@ -5964,25 +5966,25 @@
         <v>85624.590730194963</v>
       </c>
       <c r="CU22" s="18">
-        <v>73924.315417802834</v>
+        <v>73908.659388376254</v>
       </c>
       <c r="CV22" s="18">
         <v>112729.19612436718</v>
       </c>
       <c r="CW22" s="18">
-        <v>188795.18446743657</v>
+        <v>188588.10168597411</v>
       </c>
       <c r="CX22" s="18">
-        <v>80630.133189867134</v>
+        <v>80823.917184121383</v>
       </c>
       <c r="CY22" s="18">
-        <v>69239.905583759304</v>
+        <v>70393.353857717681</v>
       </c>
       <c r="CZ22" s="18">
-        <v>96631.752679299971</v>
+        <v>97090.395940088638</v>
       </c>
       <c r="DA22" s="18">
-        <v>168530.23052436719</v>
+        <v>168464.79429278313</v>
       </c>
       <c r="DB22" s="8"/>
       <c r="DC22" s="8"/>
@@ -6361,19 +6363,19 @@
         <v>11949.360841651247</v>
       </c>
       <c r="CW23" s="18">
-        <v>13905.349719374564</v>
+        <v>13982.757518583807</v>
       </c>
       <c r="CX23" s="18">
-        <v>7777.3635815565631</v>
+        <v>7889.6014001064668</v>
       </c>
       <c r="CY23" s="18">
-        <v>7412.2511115986126</v>
+        <v>7418.3680997554511</v>
       </c>
       <c r="CZ23" s="18">
-        <v>11582.99874274695</v>
+        <v>11597.963357962792</v>
       </c>
       <c r="DA23" s="18">
-        <v>14400.761470434838</v>
+        <v>14482.457635219325</v>
       </c>
       <c r="DB23" s="8"/>
       <c r="DC23" s="8"/>
@@ -6752,19 +6754,19 @@
         <v>13224.340922464045</v>
       </c>
       <c r="CW24" s="18">
-        <v>7786.1138279072329</v>
+        <v>7696.3867397988506</v>
       </c>
       <c r="CX24" s="18">
-        <v>8158.4844371489089</v>
+        <v>8178.0849449331254</v>
       </c>
       <c r="CY24" s="18">
-        <v>9111.4683462217217</v>
+        <v>9128.9131583011767</v>
       </c>
       <c r="CZ24" s="18">
-        <v>13117.702486840692</v>
+        <v>13221.60924947173</v>
       </c>
       <c r="DA24" s="18">
-        <v>7655.8888442455172</v>
+        <v>7748.0053688307962</v>
       </c>
       <c r="DB24" s="8"/>
       <c r="DC24" s="8"/>
@@ -7134,7 +7136,7 @@
         <v>30092.391775344906</v>
       </c>
       <c r="CT25" s="18">
-        <v>11496.377056675046</v>
+        <v>11496.37705667505</v>
       </c>
       <c r="CU25" s="18">
         <v>17670.419785892082</v>
@@ -7143,19 +7145,19 @@
         <v>25229.493552927423</v>
       </c>
       <c r="CW25" s="18">
-        <v>28918.641219954399</v>
+        <v>28405.845869920733</v>
       </c>
       <c r="CX25" s="18">
-        <v>12316.772228295402</v>
+        <v>12329.494994279736</v>
       </c>
       <c r="CY25" s="18">
-        <v>18126.382922263416</v>
+        <v>18169.977421025185</v>
       </c>
       <c r="CZ25" s="18">
-        <v>25660.574823625509</v>
+        <v>25533.687088519415</v>
       </c>
       <c r="DA25" s="18">
-        <v>30090.262471090522</v>
+        <v>29600.614010033132</v>
       </c>
       <c r="DB25" s="8"/>
       <c r="DC25" s="8"/>
@@ -7525,28 +7527,28 @@
         <v>12243.933381034396</v>
       </c>
       <c r="CT26" s="18">
-        <v>19900.624432548502</v>
+        <v>19892.182033287478</v>
       </c>
       <c r="CU26" s="18">
-        <v>10578.79962053091</v>
+        <v>10578.79962050137</v>
       </c>
       <c r="CV26" s="18">
-        <v>26023.540724010178</v>
+        <v>26247.217461046181</v>
       </c>
       <c r="CW26" s="18">
-        <v>10687.226957416628</v>
+        <v>10696.518759001527</v>
       </c>
       <c r="CX26" s="18">
-        <v>12770.977684892059</v>
+        <v>12726.833856354759</v>
       </c>
       <c r="CY26" s="18">
-        <v>6111.0626784823507</v>
+        <v>6304.7140298225822</v>
       </c>
       <c r="CZ26" s="18">
-        <v>19113.37800944304</v>
+        <v>19953.412172536337</v>
       </c>
       <c r="DA26" s="18">
-        <v>6826.7557028863957</v>
+        <v>6562.8157869009738</v>
       </c>
       <c r="DB26" s="8"/>
       <c r="DC26" s="8"/>
@@ -7922,22 +7924,22 @@
         <v>9848.9203660120984</v>
       </c>
       <c r="CV27" s="18">
-        <v>3932.7402463165963</v>
+        <v>3934.1223860753671</v>
       </c>
       <c r="CW27" s="18">
-        <v>11046.800793402348</v>
+        <v>10993.453071962802</v>
       </c>
       <c r="CX27" s="18">
-        <v>5422.9044935341644</v>
+        <v>5440.8800611707175</v>
       </c>
       <c r="CY27" s="18">
-        <v>9863.4155554017452</v>
+        <v>10001.403871930983</v>
       </c>
       <c r="CZ27" s="18">
-        <v>3961.3771127872569</v>
+        <v>4021.5137767293854</v>
       </c>
       <c r="DA27" s="18">
-        <v>11775.772139873116</v>
+        <v>12152.598837638405</v>
       </c>
       <c r="DB27" s="8"/>
       <c r="DC27" s="8"/>
@@ -8307,28 +8309,28 @@
         <v>53619.376274092647</v>
       </c>
       <c r="CT28" s="18">
-        <v>116923.80754777728</v>
+        <v>116913.70144027553</v>
       </c>
       <c r="CU28" s="18">
         <v>95083.233029488067</v>
       </c>
       <c r="CV28" s="18">
-        <v>112180.30249272712</v>
+        <v>112180.35113482544</v>
       </c>
       <c r="CW28" s="18">
-        <v>52714.26519732608</v>
+        <v>52566.692329711077</v>
       </c>
       <c r="CX28" s="18">
-        <v>116609.48125037079</v>
+        <v>117045.68821326265</v>
       </c>
       <c r="CY28" s="18">
-        <v>95263.09254681837</v>
+        <v>95292.529863154894</v>
       </c>
       <c r="CZ28" s="18">
-        <v>111913.92384799823</v>
+        <v>112070.91636854087</v>
       </c>
       <c r="DA28" s="18">
-        <v>58649.895918148512</v>
+        <v>58692.731816551561</v>
       </c>
       <c r="DB28" s="8"/>
       <c r="DC28" s="8"/>
@@ -8707,19 +8709,19 @@
         <v>11654.96018256485</v>
       </c>
       <c r="CW29" s="18">
-        <v>13805.337342912964</v>
+        <v>13497.494042916049</v>
       </c>
       <c r="CX29" s="18">
-        <v>18399.178800343034</v>
+        <v>18309.176147330618</v>
       </c>
       <c r="CY29" s="18">
-        <v>16714.869422901393</v>
+        <v>16706.736346984675</v>
       </c>
       <c r="CZ29" s="18">
-        <v>10669.688580552436</v>
+        <v>10559.578727696433</v>
       </c>
       <c r="DA29" s="18">
-        <v>12881.26076153991</v>
+        <v>12618.084127551199</v>
       </c>
       <c r="DB29" s="8"/>
       <c r="DC29" s="8"/>
@@ -9098,19 +9100,19 @@
         <v>11552.551415007732</v>
       </c>
       <c r="CW30" s="18">
-        <v>22846.302372081234</v>
+        <v>23319.771792744184</v>
       </c>
       <c r="CX30" s="18">
-        <v>11622.601698493083</v>
+        <v>11603.865467799111</v>
       </c>
       <c r="CY30" s="18">
-        <v>5106.1280312044582</v>
+        <v>4687.607303933135</v>
       </c>
       <c r="CZ30" s="18">
-        <v>9622.9792526924757</v>
+        <v>9990.6417878434913</v>
       </c>
       <c r="DA30" s="18">
-        <v>18690.50585224606</v>
+        <v>18686.348306944376</v>
       </c>
       <c r="DB30" s="8"/>
       <c r="DC30" s="8"/>
@@ -9480,7 +9482,7 @@
         <v>16397.69898466114</v>
       </c>
       <c r="CT31" s="18">
-        <v>18031.308375545887</v>
+        <v>18031.308375545901</v>
       </c>
       <c r="CU31" s="18">
         <v>9174.7269188510472</v>
@@ -9489,19 +9491,19 @@
         <v>15527.028792913537</v>
       </c>
       <c r="CW31" s="18">
-        <v>17234.884740315072</v>
+        <v>17326.954530812276</v>
       </c>
       <c r="CX31" s="18">
-        <v>19431.484517010525</v>
+        <v>19395.633141136699</v>
       </c>
       <c r="CY31" s="18">
-        <v>10273.311835216999</v>
+        <v>10270.498353227369</v>
       </c>
       <c r="CZ31" s="18">
-        <v>16794.557768209357</v>
+        <v>16868.872772465707</v>
       </c>
       <c r="DA31" s="18">
-        <v>17425.060923134224</v>
+        <v>17537.400557122703</v>
       </c>
       <c r="DB31" s="8"/>
       <c r="DC31" s="8"/>
@@ -9877,22 +9879,22 @@
         <v>3762.3270102261195</v>
       </c>
       <c r="CV32" s="18">
-        <v>3868.8258614727965</v>
+        <v>3858.993362131705</v>
       </c>
       <c r="CW32" s="18">
-        <v>9681.1778512082346</v>
+        <v>9769.799060851863</v>
       </c>
       <c r="CX32" s="18">
-        <v>5573.9263954897706</v>
+        <v>5523.3045004083615</v>
       </c>
       <c r="CY32" s="18">
-        <v>3707.3145566309177</v>
+        <v>3651.1008437080436</v>
       </c>
       <c r="CZ32" s="18">
-        <v>3804.1442077520278</v>
+        <v>3784.0821880188996</v>
       </c>
       <c r="DA32" s="18">
-        <v>9502.2205949253221</v>
+        <v>10025.05594074243</v>
       </c>
       <c r="DB32" s="8"/>
       <c r="DC32" s="8"/>
@@ -10265,25 +10267,25 @@
         <v>25642.540088621958</v>
       </c>
       <c r="CU33" s="18">
-        <v>19540.116511027336</v>
+        <v>19540.116511027343</v>
       </c>
       <c r="CV33" s="18">
         <v>14617.231431413606</v>
       </c>
       <c r="CW33" s="18">
-        <v>14026.047539839536</v>
+        <v>14027.488798673803</v>
       </c>
       <c r="CX33" s="18">
-        <v>25808.346074313726</v>
+        <v>25796.806838232209</v>
       </c>
       <c r="CY33" s="18">
-        <v>21272.278229243668</v>
+        <v>21210.497103157279</v>
       </c>
       <c r="CZ33" s="18">
-        <v>16271.066942881633</v>
+        <v>16231.752236068445</v>
       </c>
       <c r="DA33" s="18">
-        <v>16124.982889446794</v>
+        <v>16603.955991284784</v>
       </c>
       <c r="DB33" s="8"/>
       <c r="DC33" s="8"/>
@@ -10833,28 +10835,28 @@
         <v>1300294.3704998048</v>
       </c>
       <c r="CT35" s="19">
-        <v>1079443.9715020258</v>
+        <v>1079441.864007202</v>
       </c>
       <c r="CU35" s="19">
-        <v>886735.36256382335</v>
+        <v>887199.04481190327</v>
       </c>
       <c r="CV35" s="19">
-        <v>812834.42852673109</v>
+        <v>812433.19001920801</v>
       </c>
       <c r="CW35" s="19">
-        <v>1367024.0723380574</v>
+        <v>1366144.3144493739</v>
       </c>
       <c r="CX35" s="19">
-        <v>1150546.2446934192</v>
+        <v>1150476.4245645148</v>
       </c>
       <c r="CY35" s="19">
-        <v>927040.54745211871</v>
+        <v>926828.99644106906</v>
       </c>
       <c r="CZ35" s="19">
-        <v>821842.59672615991</v>
+        <v>821490.82971392316</v>
       </c>
       <c r="DA35" s="19">
-        <v>1393953.9844888775</v>
+        <v>1395223.0543014701</v>
       </c>
       <c r="DB35" s="8"/>
       <c r="DC35" s="8"/>
@@ -11415,7 +11417,7 @@
     </row>
     <row r="42" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:179" x14ac:dyDescent="0.2">
@@ -11425,7 +11427,7 @@
     </row>
     <row r="45" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:179" x14ac:dyDescent="0.2">
@@ -12205,28 +12207,28 @@
         <v>562830.10294719902</v>
       </c>
       <c r="CT51" s="18">
-        <v>541441.9224220328</v>
+        <v>541475.15558805084</v>
       </c>
       <c r="CU51" s="18">
-        <v>465782.66321338457</v>
+        <v>465784.04989443324</v>
       </c>
       <c r="CV51" s="18">
-        <v>304529.11754568666</v>
+        <v>304749.99791886448</v>
       </c>
       <c r="CW51" s="18">
-        <v>591941.98224381288</v>
+        <v>591334.82984857308</v>
       </c>
       <c r="CX51" s="18">
-        <v>599688.11643442535</v>
+        <v>599840.31368365278</v>
       </c>
       <c r="CY51" s="18">
-        <v>505316.51899276185</v>
+        <v>504022.58931919397</v>
       </c>
       <c r="CZ51" s="18">
-        <v>338120.82869563671</v>
+        <v>336737.89758528268</v>
       </c>
       <c r="DA51" s="18">
-        <v>628859.9891452922</v>
+        <v>629127.06621503388</v>
       </c>
       <c r="DB51" s="8"/>
       <c r="DC51" s="8"/>
@@ -12599,25 +12601,25 @@
         <v>30521.731856055085</v>
       </c>
       <c r="CU52" s="18">
-        <v>34903.422675058158</v>
+        <v>35344.187913168105</v>
       </c>
       <c r="CV52" s="18">
-        <v>51860.842242500199</v>
+        <v>51201.300878111819</v>
       </c>
       <c r="CW52" s="18">
-        <v>45154.297449221769</v>
+        <v>44696.692620064379</v>
       </c>
       <c r="CX52" s="18">
-        <v>30271.977354260627</v>
+        <v>30272.865017331358</v>
       </c>
       <c r="CY52" s="18">
-        <v>34961.722102397347</v>
+        <v>35255.247453778065</v>
       </c>
       <c r="CZ52" s="18">
-        <v>48546.528663164368</v>
+        <v>47947.983140371303</v>
       </c>
       <c r="DA52" s="18">
-        <v>43642.206588143708</v>
+        <v>43306.558778910614</v>
       </c>
       <c r="DB52" s="8"/>
       <c r="DC52" s="8"/>
@@ -12996,19 +12998,19 @@
         <v>5968.7136757122771</v>
       </c>
       <c r="CW53" s="18">
-        <v>2348.848983726532</v>
+        <v>2374.5553833639515</v>
       </c>
       <c r="CX53" s="18">
-        <v>2644.9089613875194</v>
+        <v>2646.5085847580426</v>
       </c>
       <c r="CY53" s="18">
-        <v>3120.0849030512663</v>
+        <v>3112.8765167362394</v>
       </c>
       <c r="CZ53" s="18">
-        <v>6582.1198585686943</v>
+        <v>6626.8874246283167</v>
       </c>
       <c r="DA53" s="18">
-        <v>2547.1402177367713</v>
+        <v>2575.1883170188926</v>
       </c>
       <c r="DB53" s="8"/>
       <c r="DC53" s="8"/>
@@ -13378,28 +13380,28 @@
         <v>10939.296871250179</v>
       </c>
       <c r="CT54" s="18">
-        <v>8475.5176675947077</v>
+        <v>8352.3513289453949</v>
       </c>
       <c r="CU54" s="18">
         <v>9971.3875606527763</v>
       </c>
       <c r="CV54" s="18">
-        <v>9292.1983395067473</v>
+        <v>9342.2253101544884</v>
       </c>
       <c r="CW54" s="18">
-        <v>10276.88280697864</v>
+        <v>10267.32005716917</v>
       </c>
       <c r="CX54" s="18">
-        <v>10278.816405436006</v>
+        <v>9992.4134451428909</v>
       </c>
       <c r="CY54" s="18">
         <v>10688.825186978505</v>
       </c>
       <c r="CZ54" s="18">
-        <v>10447.028088872346</v>
+        <v>10503.272386342414</v>
       </c>
       <c r="DA54" s="18">
-        <v>9786.8473998351728</v>
+        <v>9695.9109708965771</v>
       </c>
       <c r="DB54" s="8"/>
       <c r="DC54" s="8"/>
@@ -13775,22 +13777,22 @@
         <v>11404.064966978978</v>
       </c>
       <c r="CV55" s="18">
-        <v>15868.448080163122</v>
+        <v>15871.133339911765</v>
       </c>
       <c r="CW55" s="18">
-        <v>11225.353828919026</v>
+        <v>11249.583938101598</v>
       </c>
       <c r="CX55" s="18">
-        <v>12300.45532726567</v>
+        <v>12427.67896731275</v>
       </c>
       <c r="CY55" s="18">
-        <v>11462.916243019699</v>
+        <v>11464.234529876709</v>
       </c>
       <c r="CZ55" s="18">
-        <v>14710.970055927479</v>
+        <v>14666.462641665974</v>
       </c>
       <c r="DA55" s="18">
-        <v>10412.632501456075</v>
+        <v>10542.527102964159</v>
       </c>
       <c r="DB55" s="8"/>
       <c r="DC55" s="8"/>
@@ -14169,19 +14171,19 @@
         <v>1868.9085283615859</v>
       </c>
       <c r="CW56" s="18">
-        <v>6894.4020248177694</v>
+        <v>6927.8485806821645</v>
       </c>
       <c r="CX56" s="18">
-        <v>3103.916191064216</v>
+        <v>3079.1726853645123</v>
       </c>
       <c r="CY56" s="18">
-        <v>1547.8142205564404</v>
+        <v>1551.03061222007</v>
       </c>
       <c r="CZ56" s="18">
-        <v>1995.3518867423036</v>
+        <v>1983.119564275351</v>
       </c>
       <c r="DA56" s="18">
-        <v>7456.4053848843723</v>
+        <v>7573.3902834049368</v>
       </c>
       <c r="DB56" s="8"/>
       <c r="DC56" s="8"/>
@@ -14551,7 +14553,7 @@
         <v>15689.602455175147</v>
       </c>
       <c r="CT57" s="18">
-        <v>6931.5982128748838</v>
+        <v>7053.2744412877692</v>
       </c>
       <c r="CU57" s="18">
         <v>10350.328511573563</v>
@@ -14560,19 +14562,19 @@
         <v>5877.3446553762151</v>
       </c>
       <c r="CW57" s="18">
-        <v>15659.934311451434</v>
+        <v>15695.370488245426</v>
       </c>
       <c r="CX57" s="18">
-        <v>7561.454660694053</v>
+        <v>7519.578741261088</v>
       </c>
       <c r="CY57" s="18">
-        <v>11421.400609738332</v>
+        <v>11523.625997424504</v>
       </c>
       <c r="CZ57" s="18">
-        <v>6059.970747367759</v>
+        <v>6039.5189494960432</v>
       </c>
       <c r="DA57" s="18">
-        <v>17768.595172336863</v>
+        <v>17834.935067156912</v>
       </c>
       <c r="DB57" s="8"/>
       <c r="DC57" s="8"/>
@@ -14948,22 +14950,22 @@
         <v>8612.0558641426614</v>
       </c>
       <c r="CV58" s="18">
-        <v>10113.202819766913</v>
+        <v>10112.985029693606</v>
       </c>
       <c r="CW58" s="18">
-        <v>6099.7988409115715</v>
+        <v>6264.4120626332588</v>
       </c>
       <c r="CX58" s="18">
-        <v>6986.7753053883716</v>
+        <v>6801.5142340903476</v>
       </c>
       <c r="CY58" s="18">
-        <v>8884.7515247557021</v>
+        <v>8490.2496666788138</v>
       </c>
       <c r="CZ58" s="18">
-        <v>10995.805660223363</v>
+        <v>10994.193766839817</v>
       </c>
       <c r="DA58" s="18">
-        <v>6466.9845313395672</v>
+        <v>6672.2137945430113</v>
       </c>
       <c r="DB58" s="8"/>
       <c r="DC58" s="8"/>
@@ -15342,19 +15344,19 @@
         <v>3665.7517647738023</v>
       </c>
       <c r="CW59" s="18">
-        <v>8840.8112508124032</v>
+        <v>8830.5858914695054</v>
       </c>
       <c r="CX59" s="18">
-        <v>11765.595839661113</v>
+        <v>11316.664157585219</v>
       </c>
       <c r="CY59" s="18">
-        <v>12588.218072611169</v>
+        <v>12292.525278251953</v>
       </c>
       <c r="CZ59" s="18">
-        <v>3395.9691340658483</v>
+        <v>3412.0352604088093</v>
       </c>
       <c r="DA59" s="18">
-        <v>7903.8353589814178</v>
+        <v>7580.853978844998</v>
       </c>
       <c r="DB59" s="8"/>
       <c r="DC59" s="8"/>
@@ -15733,19 +15735,19 @@
         <v>24484.18503053821</v>
       </c>
       <c r="CW60" s="18">
-        <v>55602.432294023019</v>
+        <v>56367.067891491315</v>
       </c>
       <c r="CX60" s="18">
-        <v>10436.258297397319</v>
+        <v>10445.231206363831</v>
       </c>
       <c r="CY60" s="18">
-        <v>50151.419110357412</v>
+        <v>50448.988094147586</v>
       </c>
       <c r="CZ60" s="18">
-        <v>22554.186231502987</v>
+        <v>22615.232771978874</v>
       </c>
       <c r="DA60" s="18">
-        <v>51856.956670046668</v>
+        <v>52560.043276405631</v>
       </c>
       <c r="DB60" s="8"/>
       <c r="DC60" s="8"/>
@@ -16118,25 +16120,25 @@
         <v>113489.62374023037</v>
       </c>
       <c r="CU61" s="18">
-        <v>92888.763353487506</v>
+        <v>92869.054186221998</v>
       </c>
       <c r="CV61" s="18">
         <v>115231.53236119729</v>
       </c>
       <c r="CW61" s="18">
-        <v>161772.94325838255</v>
+        <v>161598.41372265352</v>
       </c>
       <c r="CX61" s="18">
-        <v>104989.94859544333</v>
+        <v>105240.70149476588</v>
       </c>
       <c r="CY61" s="18">
-        <v>86802.482710500015</v>
+        <v>88251.239792695269</v>
       </c>
       <c r="CZ61" s="18">
-        <v>100333.28137078212</v>
+        <v>100806.97444775305</v>
       </c>
       <c r="DA61" s="18">
-        <v>144486.70274741884</v>
+        <v>144431.68995618518</v>
       </c>
       <c r="DB61" s="8"/>
       <c r="DC61" s="8"/>
@@ -16515,19 +16517,19 @@
         <v>18189.210622826722</v>
       </c>
       <c r="CW62" s="18">
-        <v>17964.99147756007</v>
+        <v>18049.029538004401</v>
       </c>
       <c r="CX62" s="18">
-        <v>9991.3162911952131</v>
+        <v>10139.949434126303</v>
       </c>
       <c r="CY62" s="18">
-        <v>12501.064454921159</v>
+        <v>12511.662650414935</v>
       </c>
       <c r="CZ62" s="18">
-        <v>18557.872655425417</v>
+        <v>18581.916008185824</v>
       </c>
       <c r="DA62" s="18">
-        <v>19657.909458692404</v>
+        <v>19750.95396082248</v>
       </c>
       <c r="DB62" s="8"/>
       <c r="DC62" s="8"/>
@@ -16906,19 +16908,19 @@
         <v>11432.481981911205</v>
       </c>
       <c r="CW63" s="18">
-        <v>6316.3031185153959</v>
+        <v>6243.514112477118</v>
       </c>
       <c r="CX63" s="18">
-        <v>6942.9587949541601</v>
+        <v>6959.632068049832</v>
       </c>
       <c r="CY63" s="18">
-        <v>9542.4436261970986</v>
+        <v>9560.3640253785779</v>
       </c>
       <c r="CZ63" s="18">
-        <v>11404.747920195914</v>
+        <v>11495.077793487479</v>
       </c>
       <c r="DA63" s="18">
-        <v>6122.0476998643153</v>
+        <v>6191.1007186748702</v>
       </c>
       <c r="DB63" s="8"/>
       <c r="DC63" s="8"/>
@@ -17297,19 +17299,19 @@
         <v>26130.163539206602</v>
       </c>
       <c r="CW64" s="18">
-        <v>25300.872161507665</v>
+        <v>24852.214543360271</v>
       </c>
       <c r="CX64" s="18">
-        <v>10755.375156476352</v>
+        <v>10766.469386059245</v>
       </c>
       <c r="CY64" s="18">
-        <v>19927.51371279161</v>
+        <v>19975.38444927329</v>
       </c>
       <c r="CZ64" s="18">
-        <v>26180.226053171922</v>
+        <v>26050.76871983915</v>
       </c>
       <c r="DA64" s="18">
-        <v>26740.479780820046</v>
+        <v>26305.326570432677</v>
       </c>
       <c r="DB64" s="8"/>
       <c r="DC64" s="8"/>
@@ -17679,28 +17681,28 @@
         <v>15469.838928658122</v>
       </c>
       <c r="CT65" s="18">
-        <v>31451.591474340414</v>
+        <v>31438.248833082049</v>
       </c>
       <c r="CU65" s="18">
-        <v>19814.221443093717</v>
+        <v>19814.221443038419</v>
       </c>
       <c r="CV65" s="18">
-        <v>28494.219151420795</v>
+        <v>28739.131787705483</v>
       </c>
       <c r="CW65" s="18">
-        <v>14818.152729078502</v>
+        <v>14831.398907249837</v>
       </c>
       <c r="CX65" s="18">
-        <v>19993.143922103671</v>
+        <v>19923.87956107955</v>
       </c>
       <c r="CY65" s="18">
-        <v>11956.415216260131</v>
+        <v>12335.043373420143</v>
       </c>
       <c r="CZ65" s="18">
-        <v>21221.145065751625</v>
+        <v>22154.081813561264</v>
       </c>
       <c r="DA65" s="18">
-        <v>9187.6021065644745</v>
+        <v>8992.610787920843</v>
       </c>
       <c r="DB65" s="8"/>
       <c r="DC65" s="8"/>
@@ -18076,22 +18078,22 @@
         <v>12584.138507505093</v>
       </c>
       <c r="CV66" s="18">
-        <v>4198.6871896312823</v>
+        <v>4200.1627949690283</v>
       </c>
       <c r="CW66" s="18">
-        <v>9637.1923701613741</v>
+        <v>9595.297061801808</v>
       </c>
       <c r="CX66" s="18">
-        <v>4801.2192308465728</v>
+        <v>4817.099222329176</v>
       </c>
       <c r="CY66" s="18">
-        <v>12562.649230807358</v>
+        <v>12735.571821292739</v>
       </c>
       <c r="CZ66" s="18">
-        <v>4283.5764487888318</v>
+        <v>4348.241621411722</v>
       </c>
       <c r="DA66" s="18">
-        <v>10412.944251394296</v>
+        <v>10751.209958423067</v>
       </c>
       <c r="DB66" s="8"/>
       <c r="DC66" s="8"/>
@@ -18461,28 +18463,28 @@
         <v>72993.292253543448</v>
       </c>
       <c r="CT67" s="18">
-        <v>146416.51321272017</v>
+        <v>146403.85795410693</v>
       </c>
       <c r="CU67" s="18">
         <v>99338.567456231453</v>
       </c>
       <c r="CV67" s="18">
-        <v>96963.123979733209</v>
+        <v>96963.16602356534</v>
       </c>
       <c r="CW67" s="18">
-        <v>69758.772141552676</v>
+        <v>69563.483408840693</v>
       </c>
       <c r="CX67" s="18">
-        <v>141727.17110701563</v>
+        <v>142257.33707812655</v>
       </c>
       <c r="CY67" s="18">
-        <v>98725.445625373919</v>
+        <v>98755.95284591071</v>
       </c>
       <c r="CZ67" s="18">
-        <v>96870.827852494142</v>
+        <v>97006.717962577968</v>
       </c>
       <c r="DA67" s="18">
-        <v>77519.795620696968</v>
+        <v>77576.413455007772</v>
       </c>
       <c r="DB67" s="8"/>
       <c r="DC67" s="8"/>
@@ -18861,19 +18863,19 @@
         <v>12804.819639840462</v>
       </c>
       <c r="CW68" s="18">
-        <v>13463.46991975027</v>
+        <v>13163.24987394076</v>
       </c>
       <c r="CX68" s="18">
-        <v>16211.027417783072</v>
+        <v>16131.728472352414</v>
       </c>
       <c r="CY68" s="18">
-        <v>22321.037736506856</v>
+        <v>22310.176826387979</v>
       </c>
       <c r="CZ68" s="18">
-        <v>11758.92632007569</v>
+        <v>11637.575669860074</v>
       </c>
       <c r="DA68" s="18">
-        <v>12548.98231847326</v>
+        <v>12292.594454917213</v>
       </c>
       <c r="DB68" s="8"/>
       <c r="DC68" s="8"/>
@@ -19252,19 +19254,19 @@
         <v>13650.998576206039</v>
       </c>
       <c r="CW69" s="18">
-        <v>22540.403114992281</v>
+        <v>23030.967534018317</v>
       </c>
       <c r="CX69" s="18">
-        <v>14038.186925295442</v>
+        <v>14014.367852341631</v>
       </c>
       <c r="CY69" s="18">
-        <v>5530.3604105660852</v>
+        <v>5082.8539525223696</v>
       </c>
       <c r="CZ69" s="18">
-        <v>12503.026151841314</v>
+        <v>12986.467813637915</v>
       </c>
       <c r="DA69" s="18">
-        <v>18288.556068500475</v>
+        <v>18505.023781317446</v>
       </c>
       <c r="DB69" s="8"/>
       <c r="DC69" s="8"/>
@@ -19643,19 +19645,19 @@
         <v>18622.208873610638</v>
       </c>
       <c r="CW70" s="18">
-        <v>19327.858018265193</v>
+        <v>19438.115870811147</v>
       </c>
       <c r="CX70" s="18">
-        <v>21611.744911385147</v>
+        <v>21570.962292120574</v>
       </c>
       <c r="CY70" s="18">
-        <v>13743.129406595333</v>
+        <v>13739.300763022191</v>
       </c>
       <c r="CZ70" s="18">
-        <v>20859.600905836123</v>
+        <v>20955.324763699144</v>
       </c>
       <c r="DA70" s="18">
-        <v>19484.490835011908</v>
+        <v>19617.496877123624</v>
       </c>
       <c r="DB70" s="8"/>
       <c r="DC70" s="8"/>
@@ -20031,22 +20033,22 @@
         <v>3905.7230088270881</v>
       </c>
       <c r="CV71" s="18">
-        <v>4416.9705288139594</v>
+        <v>4405.7731069899855</v>
       </c>
       <c r="CW71" s="18">
-        <v>8775.6251077577399</v>
+        <v>8855.9569149387644</v>
       </c>
       <c r="CX71" s="18">
-        <v>6324.4380983127448</v>
+        <v>6264.6172998216825</v>
       </c>
       <c r="CY71" s="18">
-        <v>3876.4251550760437</v>
+        <v>3814.0816695477879</v>
       </c>
       <c r="CZ71" s="18">
-        <v>4245.3535398220502</v>
+        <v>4222.1405668748303</v>
       </c>
       <c r="DA71" s="18">
-        <v>8553.0071510262533</v>
+        <v>9047.1660381157162</v>
       </c>
       <c r="DB71" s="8"/>
       <c r="DC71" s="8"/>
@@ -20425,19 +20427,19 @@
         <v>15805.60683587414</v>
       </c>
       <c r="CW72" s="18">
-        <v>13253.28787183822</v>
+        <v>13254.641561775439</v>
       </c>
       <c r="CX72" s="18">
-        <v>26921.624553383255</v>
+        <v>26909.839706370141</v>
       </c>
       <c r="CY72" s="18">
-        <v>26017.144556915242</v>
+        <v>25943.805735018621</v>
       </c>
       <c r="CZ72" s="18">
-        <v>18234.309106757515</v>
+        <v>18190.906672536563</v>
       </c>
       <c r="DA72" s="18">
-        <v>15229.945542391586</v>
+        <v>15679.620918370609</v>
       </c>
       <c r="DB72" s="8"/>
       <c r="DC72" s="8"/>
@@ -20987,28 +20989,28 @@
         <v>1101039.1812641178</v>
       </c>
       <c r="CT74" s="19">
-        <v>1034833.3039380098</v>
+        <v>1034839.0490939198</v>
       </c>
       <c r="CU74" s="19">
-        <v>949471.1570761425</v>
+        <v>949893.59982798039</v>
       </c>
       <c r="CV74" s="19">
-        <v>799468.73596265807</v>
+        <v>799317.80227540119</v>
       </c>
       <c r="CW74" s="19">
-        <v>1136974.6153240369</v>
+        <v>1136484.5498116657</v>
       </c>
       <c r="CX74" s="19">
-        <v>1079346.4297811745</v>
+        <v>1079338.5245904056</v>
       </c>
       <c r="CY74" s="19">
-        <v>973649.78280873864</v>
+        <v>973865.63056017121</v>
       </c>
       <c r="CZ74" s="19">
-        <v>809861.65241301444</v>
+        <v>809962.79734471464</v>
       </c>
       <c r="DA74" s="19">
-        <v>1154934.0565509079</v>
+        <v>1156609.895262491</v>
       </c>
       <c r="DB74" s="8"/>
       <c r="DC74" s="8"/>
@@ -21577,7 +21579,7 @@
     </row>
     <row r="81" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="CX81" s="4"/>
       <c r="CY81" s="4"/>
@@ -21601,7 +21603,7 @@
     </row>
     <row r="84" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CX84" s="4"/>
       <c r="CY84" s="4"/>
@@ -22377,28 +22379,28 @@
         <v>3.5651917153950876</v>
       </c>
       <c r="CP90" s="16">
-        <v>4.579703136388602</v>
+        <v>4.58593065203317</v>
       </c>
       <c r="CQ90" s="16">
-        <v>4.4837694801492347</v>
+        <v>4.4840696982390966</v>
       </c>
       <c r="CR90" s="16">
-        <v>8.5081532025715916</v>
+        <v>8.5849988522039382</v>
       </c>
       <c r="CS90" s="16">
-        <v>7.0653777536900435</v>
+        <v>6.955718374327887</v>
       </c>
       <c r="CT90" s="16">
-        <v>11.090607524381227</v>
+        <v>11.111344145568822</v>
       </c>
       <c r="CU90" s="16">
-        <v>10.871601546551361</v>
+        <v>10.597200914954044</v>
       </c>
       <c r="CV90" s="16">
-        <v>11.933983386737239</v>
+        <v>11.408416082242766</v>
       </c>
       <c r="CW90" s="16">
-        <v>6.3738497679070178</v>
+        <v>6.526155231812524</v>
       </c>
       <c r="CX90" s="20"/>
       <c r="CY90" s="20"/>
@@ -22759,25 +22761,25 @@
         <v>13.736557215121479</v>
       </c>
       <c r="CQ91" s="16">
-        <v>9.3726085318716343</v>
+        <v>10.7534360720758</v>
       </c>
       <c r="CR91" s="16">
-        <v>10.495453151205993</v>
+        <v>9.0887162432743622</v>
       </c>
       <c r="CS91" s="16">
-        <v>7.1604258111590298</v>
+        <v>6.0744355263828425</v>
       </c>
       <c r="CT91" s="16">
-        <v>0.9222599171479402</v>
+        <v>0.92519200251021516</v>
       </c>
       <c r="CU91" s="16">
-        <v>-2.1817515760427284</v>
+        <v>-2.5948380543412384</v>
       </c>
       <c r="CV91" s="16">
-        <v>-8.0459413814546537</v>
+        <v>-8.0098565423826642</v>
       </c>
       <c r="CW91" s="16">
-        <v>-4.6572446620654659</v>
+        <v>-4.4279519440357404</v>
       </c>
       <c r="CX91" s="20"/>
       <c r="CY91" s="20"/>
@@ -23144,19 +23146,19 @@
         <v>1.7496300376174361</v>
       </c>
       <c r="CS92" s="16">
-        <v>2.2102764225434584</v>
+        <v>3.1306611533775879</v>
       </c>
       <c r="CT92" s="16">
-        <v>18.342397988281078</v>
+        <v>18.417493502658601</v>
       </c>
       <c r="CU92" s="16">
-        <v>6.3337894218808088</v>
+        <v>6.087818935063666</v>
       </c>
       <c r="CV92" s="16">
-        <v>11.712057506949193</v>
+        <v>12.39340741766182</v>
       </c>
       <c r="CW92" s="16">
-        <v>11.329917400280308</v>
+        <v>11.343262491359795</v>
       </c>
       <c r="CX92" s="20"/>
       <c r="CY92" s="20"/>
@@ -23514,28 +23516,28 @@
         <v>-21.151920326257283</v>
       </c>
       <c r="CP93" s="16">
-        <v>-3.8022976680799445</v>
+        <v>-5.204622245797097</v>
       </c>
       <c r="CQ93" s="16">
         <v>-7.1547910813814042</v>
       </c>
       <c r="CR93" s="16">
-        <v>-0.23284941091660016</v>
+        <v>0.30427303651418924</v>
       </c>
       <c r="CS93" s="16">
-        <v>-5.5838971104297741</v>
+        <v>-5.6651516082630025</v>
       </c>
       <c r="CT93" s="16">
-        <v>21.627234162894609</v>
+        <v>20.045713833286499</v>
       </c>
       <c r="CU93" s="16">
         <v>7.3915074184283185</v>
       </c>
       <c r="CV93" s="16">
-        <v>13.328802669557675</v>
+        <v>13.328802669557717</v>
       </c>
       <c r="CW93" s="16">
-        <v>-7.0719934730826992</v>
+        <v>-8.3408759391205507</v>
       </c>
       <c r="CX93" s="20"/>
       <c r="CY93" s="20"/>
@@ -23899,22 +23901,22 @@
         <v>2.4484460905930518</v>
       </c>
       <c r="CR94" s="16">
-        <v>12.637336402777223</v>
+        <v>12.656396899689753</v>
       </c>
       <c r="CS94" s="16">
-        <v>2.6075194718278425</v>
+        <v>2.7900749830019862</v>
       </c>
       <c r="CT94" s="16">
-        <v>-2.7326704386160543</v>
+        <v>-1.7879566794578494</v>
       </c>
       <c r="CU94" s="16">
-        <v>-2.4503156516897633</v>
+        <v>-2.4405115566456743</v>
       </c>
       <c r="CV94" s="16">
-        <v>-6.9257108553601228</v>
+        <v>-7.216201181935773</v>
       </c>
       <c r="CW94" s="16">
-        <v>-5.3769456750543299</v>
+        <v>-5.0686588074935912</v>
       </c>
       <c r="CX94" s="20"/>
       <c r="CY94" s="20"/>
@@ -24281,19 +24283,19 @@
         <v>12.517171123622845</v>
       </c>
       <c r="CS95" s="16">
-        <v>24.458784955426836</v>
+        <v>25.073990398530441</v>
       </c>
       <c r="CT95" s="16">
-        <v>35.747907532603506</v>
+        <v>34.669063108944897</v>
       </c>
       <c r="CU95" s="16">
-        <v>55.039697384710252</v>
+        <v>55.366370109418881</v>
       </c>
       <c r="CV95" s="16">
-        <v>7.3867507017491221</v>
+        <v>6.7169987323366627</v>
       </c>
       <c r="CW95" s="16">
-        <v>8.8084554043509371</v>
+        <v>9.9820267604848283</v>
       </c>
       <c r="CX95" s="20"/>
       <c r="CY95" s="20"/>
@@ -24651,7 +24653,7 @@
         <v>-10.645959670856683</v>
       </c>
       <c r="CP96" s="16">
-        <v>-2.2990233338171748</v>
+        <v>-0.58143592798595023</v>
       </c>
       <c r="CQ96" s="16">
         <v>-33.382321293221466</v>
@@ -24660,19 +24662,19 @@
         <v>-26.022929740117775</v>
       </c>
       <c r="CS96" s="16">
-        <v>0.19982060332608853</v>
+        <v>0.38993730972794083</v>
       </c>
       <c r="CT96" s="16">
-        <v>8.8509493753544177</v>
+        <v>6.4476232448375157</v>
       </c>
       <c r="CU96" s="16">
-        <v>11.858578905889132</v>
+        <v>12.870275403386231</v>
       </c>
       <c r="CV96" s="16">
-        <v>-0.1414105257845506</v>
+        <v>-0.48449639074381423</v>
       </c>
       <c r="CW96" s="16">
-        <v>12.8803083593819</v>
+        <v>13.045945657276107</v>
       </c>
       <c r="CX96" s="20"/>
       <c r="CY96" s="20"/>
@@ -25036,22 +25038,22 @@
         <v>5.4533826141970394</v>
       </c>
       <c r="CR97" s="16">
-        <v>4.0312745101402641</v>
+        <v>4.0290341734926756</v>
       </c>
       <c r="CS97" s="16">
-        <v>4.1053252226280108</v>
+        <v>6.9147806539024117</v>
       </c>
       <c r="CT97" s="16">
-        <v>7.0070921486024247</v>
+        <v>4.2085981054868</v>
       </c>
       <c r="CU97" s="16">
-        <v>3.0078158334060134</v>
+        <v>-1.4474662462504568</v>
       </c>
       <c r="CV97" s="16">
-        <v>3.1978111186770235</v>
+        <v>3.1848258256745794</v>
       </c>
       <c r="CW97" s="16">
-        <v>4.3995419004683214</v>
+        <v>4.8822318874847497</v>
       </c>
       <c r="CX97" s="20"/>
       <c r="CY97" s="20"/>
@@ -25418,19 +25420,19 @@
         <v>-7.5599032873561498</v>
       </c>
       <c r="CS98" s="16">
-        <v>3.2458737702778961</v>
+        <v>3.1238064229955285</v>
       </c>
       <c r="CT98" s="16">
-        <v>25.730075400708358</v>
+        <v>20.745254887197234</v>
       </c>
       <c r="CU98" s="16">
-        <v>0.9908015469108733</v>
+        <v>-1.4681371457260468</v>
       </c>
       <c r="CV98" s="16">
-        <v>-5.8688316568773615</v>
+        <v>-5.4074031071711772</v>
       </c>
       <c r="CW98" s="16">
-        <v>-9.1431346903107453</v>
+        <v>-12.567821209987883</v>
       </c>
       <c r="CX98" s="20"/>
       <c r="CY98" s="20"/>
@@ -25797,19 +25799,19 @@
         <v>4.1249885566563762</v>
       </c>
       <c r="CS99" s="16">
-        <v>-8.4634547348552758</v>
+        <v>-7.2046590654701248</v>
       </c>
       <c r="CT99" s="16">
-        <v>0.8637882001014674</v>
+        <v>0.95050908834957681</v>
       </c>
       <c r="CU99" s="16">
-        <v>-8.5607305798909579</v>
+        <v>-8.0181838092804725</v>
       </c>
       <c r="CV99" s="16">
-        <v>-8.7718347570058199</v>
+        <v>-8.5249110229866147</v>
       </c>
       <c r="CW99" s="16">
-        <v>-3.7349561387299701</v>
+        <v>-3.7533444720508413</v>
       </c>
       <c r="CX99" s="20"/>
       <c r="CY99" s="20"/>
@@ -26170,25 +26172,25 @@
         <v>8.6027829096410926</v>
       </c>
       <c r="CQ100" s="16">
-        <v>4.5999706818217447</v>
+        <v>4.5778180219051734</v>
       </c>
       <c r="CR100" s="16">
         <v>6.9655477149282774E-2</v>
       </c>
       <c r="CS100" s="16">
-        <v>4.7823167342053523</v>
+        <v>4.6673847053052953</v>
       </c>
       <c r="CT100" s="16">
-        <v>-5.8329709931875442</v>
+        <v>-5.6066528378519394</v>
       </c>
       <c r="CU100" s="16">
-        <v>-6.3367645781612509</v>
+        <v>-4.7562837152630379</v>
       </c>
       <c r="CV100" s="16">
-        <v>-14.279746506227099</v>
+        <v>-13.872892490979197</v>
       </c>
       <c r="CW100" s="16">
-        <v>-10.733829890965623</v>
+        <v>-10.670507425064983</v>
       </c>
       <c r="CX100" s="20"/>
       <c r="CY100" s="20"/>
@@ -26555,19 +26557,19 @@
         <v>1.7495388209537737</v>
       </c>
       <c r="CS101" s="16">
-        <v>1.0776607006631309</v>
+        <v>1.6403361760706616</v>
       </c>
       <c r="CT101" s="16">
-        <v>-6.063468698039614</v>
+        <v>-4.7078381884310261</v>
       </c>
       <c r="CU101" s="16">
-        <v>-3.1894718917683633</v>
+        <v>-3.1095786386959361</v>
       </c>
       <c r="CV101" s="16">
-        <v>-3.0659556084982285</v>
+        <v>-2.9407220046749956</v>
       </c>
       <c r="CW101" s="16">
-        <v>3.5627421176614291</v>
+        <v>3.5736879222241384</v>
       </c>
       <c r="CX101" s="20"/>
       <c r="CY101" s="20"/>
@@ -26934,19 +26936,19 @@
         <v>1.5609262792335841</v>
       </c>
       <c r="CS102" s="16">
-        <v>4.935402848432517</v>
+        <v>3.7261284472129574</v>
       </c>
       <c r="CT102" s="16">
-        <v>3.0252787848202871</v>
+        <v>3.2727938465145741</v>
       </c>
       <c r="CU102" s="16">
-        <v>-5.8905163291028941</v>
+        <v>-5.7103343655432894</v>
       </c>
       <c r="CV102" s="16">
-        <v>-0.80637996440493964</v>
+        <v>-2.0656401769514332E-2</v>
       </c>
       <c r="CW102" s="16">
-        <v>-1.6725286393188696</v>
+        <v>0.67068652832919895</v>
       </c>
       <c r="CX102" s="20"/>
       <c r="CY102" s="20"/>
@@ -27304,7 +27306,7 @@
         <v>-16.73766195547087</v>
       </c>
       <c r="CP103" s="16">
-        <v>-17.856313621749663</v>
+        <v>-17.856313621749649</v>
       </c>
       <c r="CQ103" s="16">
         <v>-14.939334835677855</v>
@@ -27313,19 +27315,19 @@
         <v>-7.405981884874052</v>
       </c>
       <c r="CS103" s="16">
-        <v>-3.9004894132482235</v>
+        <v>-5.604559178994819</v>
       </c>
       <c r="CT103" s="16">
-        <v>7.13611921021689</v>
+        <v>7.2467868224708241</v>
       </c>
       <c r="CU103" s="16">
-        <v>2.5803752366730492</v>
+        <v>2.8270841394042492</v>
       </c>
       <c r="CV103" s="16">
-        <v>1.7086402063273454</v>
+        <v>1.2057060715620054</v>
       </c>
       <c r="CW103" s="16">
-        <v>4.0514394926953941</v>
+        <v>4.2060642924826652</v>
       </c>
       <c r="CX103" s="20"/>
       <c r="CY103" s="20"/>
@@ -27683,28 +27685,28 @@
         <v>0.15751410617865247</v>
       </c>
       <c r="CP104" s="16">
-        <v>0.26094093430999976</v>
+        <v>0.21840745017122742</v>
       </c>
       <c r="CQ104" s="16">
-        <v>-8.4171432054417892</v>
+        <v>-8.4171432056975277</v>
       </c>
       <c r="CR104" s="16">
-        <v>-12.923534735720295</v>
+        <v>-12.175097778985474</v>
       </c>
       <c r="CS104" s="16">
-        <v>-12.714103998875686</v>
+        <v>-12.638214974525937</v>
       </c>
       <c r="CT104" s="16">
-        <v>-35.826246416647791</v>
+        <v>-36.020926034872701</v>
       </c>
       <c r="CU104" s="16">
-        <v>-42.232929087509653</v>
+        <v>-40.402368359409593</v>
       </c>
       <c r="CV104" s="16">
-        <v>-26.553507026011999</v>
+        <v>-23.978942902616467</v>
       </c>
       <c r="CW104" s="16">
-        <v>-36.122291310106178</v>
+        <v>-38.645311294591842</v>
       </c>
       <c r="CX104" s="20"/>
       <c r="CY104" s="20"/>
@@ -28068,22 +28070,22 @@
         <v>10.395784850224388</v>
       </c>
       <c r="CR105" s="16">
-        <v>-0.2799808239171</v>
+        <v>-0.24493477596675461</v>
       </c>
       <c r="CS105" s="16">
-        <v>0.26805994830962732</v>
+        <v>-0.21615920540234868</v>
       </c>
       <c r="CT105" s="16">
-        <v>-3.5115139578152395</v>
+        <v>-3.1916788382648349</v>
       </c>
       <c r="CU105" s="16">
-        <v>0.14717541467457806</v>
+        <v>1.5482255948082724</v>
       </c>
       <c r="CV105" s="16">
-        <v>0.72816572356848042</v>
+        <v>2.2213693952007247</v>
       </c>
       <c r="CW105" s="16">
-        <v>6.5989362902800082</v>
+        <v>10.543964285724144</v>
       </c>
       <c r="CX105" s="20"/>
       <c r="CY105" s="20"/>
@@ -28441,28 +28443,28 @@
         <v>-3.0048306654661445</v>
       </c>
       <c r="CP106" s="16">
-        <v>7.6848260797214891</v>
+        <v>7.6755185276369957</v>
       </c>
       <c r="CQ106" s="16">
         <v>5.8363616123773454</v>
       </c>
       <c r="CR106" s="16">
-        <v>2.9563391982313334</v>
+        <v>2.9563838407600258</v>
       </c>
       <c r="CS106" s="16">
-        <v>-1.6880298497688528</v>
+        <v>-1.963252871500103</v>
       </c>
       <c r="CT106" s="16">
-        <v>-0.26883002187389593</v>
+        <v>0.1128924765542223</v>
       </c>
       <c r="CU106" s="16">
-        <v>0.18916007754438624</v>
+        <v>0.2201196015304987</v>
       </c>
       <c r="CV106" s="16">
-        <v>-0.23745580891633722</v>
+        <v>-9.7552526068540146E-2</v>
       </c>
       <c r="CW106" s="16">
-        <v>11.260008459955756</v>
+        <v>11.65384241492022</v>
       </c>
       <c r="CX106" s="20"/>
       <c r="CY106" s="20"/>
@@ -28829,19 +28831,19 @@
         <v>15.759460572032793</v>
       </c>
       <c r="CS107" s="16">
-        <v>19.842138947397586</v>
+        <v>17.169795735792206</v>
       </c>
       <c r="CT107" s="16">
-        <v>11.640508674102151</v>
+        <v>11.094400498658061</v>
       </c>
       <c r="CU107" s="16">
-        <v>-1.8952374062346706</v>
+        <v>-1.9429729560483793</v>
       </c>
       <c r="CV107" s="16">
-        <v>-8.4536676795028711</v>
+        <v>-9.39841438932622</v>
       </c>
       <c r="CW107" s="16">
-        <v>-6.6936182609650814</v>
+        <v>-6.5153569438053864</v>
       </c>
       <c r="CX107" s="20"/>
       <c r="CY107" s="20"/>
@@ -29208,19 +29210,19 @@
         <v>25.122321735286718</v>
       </c>
       <c r="CS108" s="16">
-        <v>23.686238657468039</v>
+        <v>26.249526615728385</v>
       </c>
       <c r="CT108" s="16">
-        <v>7.9626236075849306</v>
+        <v>7.7885823150488136</v>
       </c>
       <c r="CU108" s="16">
-        <v>-6.1315554518752862</v>
+        <v>-13.825426314498785</v>
       </c>
       <c r="CV108" s="16">
-        <v>-16.702562862508287</v>
+        <v>-13.520040474653854</v>
       </c>
       <c r="CW108" s="16">
-        <v>-18.190236880142422</v>
+        <v>-19.86907730907329</v>
       </c>
       <c r="CX108" s="20"/>
       <c r="CY108" s="20"/>
@@ -29578,7 +29580,7 @@
         <v>3.0385881392524396</v>
       </c>
       <c r="CP109" s="16">
-        <v>-2.8111525028229494</v>
+        <v>-2.8111525028228641</v>
       </c>
       <c r="CQ109" s="16">
         <v>11.472841789255625</v>
@@ -29587,19 +29589,19 @@
         <v>9.7686285235781156</v>
       </c>
       <c r="CS109" s="16">
-        <v>5.1055075253976696</v>
+        <v>5.6669874658657164</v>
       </c>
       <c r="CT109" s="16">
-        <v>7.7652498216023105</v>
+        <v>7.5664213443384938</v>
       </c>
       <c r="CU109" s="16">
-        <v>11.97403395308389</v>
+        <v>11.943368386527894</v>
       </c>
       <c r="CV109" s="16">
-        <v>8.1633710621720184</v>
+        <v>8.6419880934630555</v>
       </c>
       <c r="CW109" s="16">
-        <v>1.1034375087771906</v>
+        <v>1.2145586573577845</v>
       </c>
       <c r="CX109" s="20"/>
       <c r="CY109" s="20"/>
@@ -29963,22 +29965,22 @@
         <v>16.834614198725632</v>
       </c>
       <c r="CR110" s="16">
-        <v>26.932084629176245</v>
+        <v>26.60949072519405</v>
       </c>
       <c r="CS110" s="16">
-        <v>13.312051375100566</v>
+        <v>14.34930647095743</v>
       </c>
       <c r="CT110" s="16">
-        <v>6.9644026041784315</v>
+        <v>5.9929615800458294</v>
       </c>
       <c r="CU110" s="16">
-        <v>-1.4621922402193235</v>
+        <v>-2.9563131066427673</v>
       </c>
       <c r="CV110" s="16">
-        <v>-1.6718677975375584</v>
+        <v>-1.9412102349775608</v>
       </c>
       <c r="CW110" s="16">
-        <v>-1.8485070621916009</v>
+        <v>2.612713713973875</v>
       </c>
       <c r="CX110" s="20"/>
       <c r="CY110" s="20"/>
@@ -30339,25 +30341,25 @@
         <v>3.2728251064166045</v>
       </c>
       <c r="CQ111" s="16">
-        <v>0.33775132047895795</v>
+        <v>0.33775132047900058</v>
       </c>
       <c r="CR111" s="16">
         <v>-1.9908070340816266</v>
       </c>
       <c r="CS111" s="16">
-        <v>4.062337988219582</v>
+        <v>4.0730310051592511</v>
       </c>
       <c r="CT111" s="16">
-        <v>0.64660515346271552</v>
+        <v>0.60160479062174943</v>
       </c>
       <c r="CU111" s="16">
-        <v>8.8646437560328621</v>
+        <v>8.5484679233476726</v>
       </c>
       <c r="CV111" s="16">
-        <v>11.314286971702472</v>
+        <v>11.045325595550921</v>
       </c>
       <c r="CW111" s="16">
-        <v>14.96455322602786</v>
+        <v>18.367273213253725</v>
       </c>
       <c r="CX111" s="20"/>
       <c r="CY111" s="20"/>
@@ -30891,28 +30893,28 @@
         <v>0.91843830632096513</v>
       </c>
       <c r="CP113" s="16">
-        <v>4.8346093578163192</v>
+        <v>4.8344046798502376</v>
       </c>
       <c r="CQ113" s="16">
-        <v>5.6172406731451048</v>
+        <v>5.6724689201045067</v>
       </c>
       <c r="CR113" s="16">
-        <v>4.6606465216534616</v>
+        <v>4.6089830092172548</v>
       </c>
       <c r="CS113" s="16">
-        <v>5.1318919278719335</v>
+        <v>5.0642335646087417</v>
       </c>
       <c r="CT113" s="16">
-        <v>6.5869350395700366</v>
+        <v>6.5806749697118363</v>
       </c>
       <c r="CU113" s="16">
-        <v>4.5453453859966402</v>
+        <v>4.4668613949610148</v>
       </c>
       <c r="CV113" s="16">
-        <v>1.1082414675466197</v>
+        <v>1.1148780977917596</v>
       </c>
       <c r="CW113" s="16">
-        <v>1.9699661985294057</v>
+        <v>2.128526213851444</v>
       </c>
       <c r="CX113" s="20"/>
       <c r="CY113" s="20"/>
@@ -31477,7 +31479,7 @@
     </row>
     <row r="120" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="CX120" s="4"/>
       <c r="CY120" s="4"/>
@@ -31501,7 +31503,7 @@
     </row>
     <row r="123" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CX123" s="4"/>
       <c r="CY123" s="4"/>
@@ -32277,28 +32279,28 @@
         <v>2.6665142626613516</v>
       </c>
       <c r="CP129" s="16">
-        <v>3.787199618317814</v>
+        <v>3.7935699732767318</v>
       </c>
       <c r="CQ129" s="16">
-        <v>2.3022248506701288</v>
+        <v>2.3025294145099622</v>
       </c>
       <c r="CR129" s="16">
-        <v>7.6458878429231731</v>
+        <v>7.7239653156766082</v>
       </c>
       <c r="CS129" s="16">
-        <v>5.1724097812417398</v>
+        <v>5.0645348839929056</v>
       </c>
       <c r="CT129" s="16">
-        <v>10.757606975063865</v>
+        <v>10.778917092182468</v>
       </c>
       <c r="CU129" s="16">
-        <v>8.4876185615491551</v>
+        <v>8.2094995381287248</v>
       </c>
       <c r="CV129" s="16">
-        <v>11.030705838797331</v>
+        <v>10.49643966689527</v>
       </c>
       <c r="CW129" s="16">
-        <v>6.2367610355221075</v>
+        <v>6.3910046320353615</v>
       </c>
       <c r="CX129" s="20"/>
       <c r="CY129" s="20"/>
@@ -32659,25 +32661,25 @@
         <v>3.3559552089774485</v>
       </c>
       <c r="CQ130" s="16">
-        <v>6.9817591650464834</v>
+        <v>8.3327395829496851</v>
       </c>
       <c r="CR130" s="16">
-        <v>7.6913497261460009</v>
+        <v>6.3217826952233622</v>
       </c>
       <c r="CS130" s="16">
-        <v>4.7290141758360278</v>
+        <v>3.6676644185144909</v>
       </c>
       <c r="CT130" s="16">
-        <v>-0.81828417526349995</v>
+        <v>-0.81537587676027101</v>
       </c>
       <c r="CU130" s="16">
-        <v>0.16703068888671169</v>
+        <v>-0.25164097590399592</v>
       </c>
       <c r="CV130" s="16">
-        <v>-6.3907824015625607</v>
+        <v>-6.3539747661592827</v>
       </c>
       <c r="CW130" s="16">
-        <v>-3.3487197155010193</v>
+        <v>-3.1101492295421735</v>
       </c>
       <c r="CX130" s="20"/>
       <c r="CY130" s="20"/>
@@ -33044,19 +33046,19 @@
         <v>-2.2981827596206585</v>
       </c>
       <c r="CS131" s="16">
-        <v>-0.71394020422333426</v>
+        <v>0.37267164235255734</v>
       </c>
       <c r="CT131" s="16">
-        <v>16.130476502217221</v>
+        <v>16.200711442986403</v>
       </c>
       <c r="CU131" s="16">
-        <v>5.6965892259579078</v>
+        <v>5.4523965610159024</v>
       </c>
       <c r="CV131" s="16">
-        <v>10.277024769214066</v>
+        <v>11.027061854118784</v>
       </c>
       <c r="CW131" s="16">
-        <v>8.4420597230411687</v>
+        <v>8.4492842348747814</v>
       </c>
       <c r="CX131" s="20"/>
       <c r="CY131" s="20"/>
@@ -33414,28 +33416,28 @@
         <v>-20.904317395937056</v>
       </c>
       <c r="CP132" s="16">
-        <v>-2.9521964054964798</v>
+        <v>-4.3624964144733553</v>
       </c>
       <c r="CQ132" s="16">
         <v>-3.5356893705502443</v>
       </c>
       <c r="CR132" s="16">
-        <v>-1.3866287914498656</v>
+        <v>-0.85571801590707253</v>
       </c>
       <c r="CS132" s="16">
-        <v>-6.0553623516009054</v>
+        <v>-6.1427788457505557</v>
       </c>
       <c r="CT132" s="16">
-        <v>21.276561604443714</v>
+        <v>19.635933063708634</v>
       </c>
       <c r="CU132" s="16">
         <v>7.1949628069492206</v>
       </c>
       <c r="CV132" s="16">
-        <v>12.427949847515848</v>
+        <v>12.427949847515791</v>
       </c>
       <c r="CW132" s="16">
-        <v>-4.7683272870515054</v>
+        <v>-5.5653187306029821</v>
       </c>
       <c r="CX132" s="20"/>
       <c r="CY132" s="20"/>
@@ -33799,22 +33801,22 @@
         <v>-1.0071353588352991</v>
       </c>
       <c r="CR133" s="16">
-        <v>7.5440869062581584</v>
+        <v>7.5622855231811883</v>
       </c>
       <c r="CS133" s="16">
-        <v>1.8913363921587063</v>
+        <v>2.1112705023138716</v>
       </c>
       <c r="CT133" s="16">
-        <v>-5.0369104521561496</v>
+        <v>-4.0547069807437595</v>
       </c>
       <c r="CU133" s="16">
-        <v>0.51605525057185275</v>
+        <v>0.52761504842311524</v>
       </c>
       <c r="CV133" s="16">
-        <v>-7.294210614600587</v>
+        <v>-7.5903256084199029</v>
       </c>
       <c r="CW133" s="16">
-        <v>-7.2400508692135617</v>
+        <v>-6.2851820923144004</v>
       </c>
       <c r="CX133" s="20"/>
       <c r="CY133" s="20"/>
@@ -34181,19 +34183,19 @@
         <v>8.1132167080953224</v>
       </c>
       <c r="CS134" s="16">
-        <v>20.107888295273327</v>
+        <v>20.690563222143226</v>
       </c>
       <c r="CT134" s="16">
-        <v>33.982547861873599</v>
+        <v>32.914478451293149</v>
       </c>
       <c r="CU134" s="16">
-        <v>55.102009211104587</v>
+        <v>55.424314564559381</v>
       </c>
       <c r="CV134" s="16">
-        <v>6.7656258432062799</v>
+        <v>6.1111089269783747</v>
       </c>
       <c r="CW134" s="16">
-        <v>8.1515896236331997</v>
+        <v>9.3180688810494701</v>
       </c>
       <c r="CX134" s="20"/>
       <c r="CY134" s="20"/>
@@ -34551,7 +34553,7 @@
         <v>-12.601108346125656</v>
       </c>
       <c r="CP135" s="16">
-        <v>0.85329289067159664</v>
+        <v>2.6236563660334298</v>
       </c>
       <c r="CQ135" s="16">
         <v>-27.616944575651161</v>
@@ -34560,19 +34562,19 @@
         <v>-18.478495000623838</v>
       </c>
       <c r="CS135" s="16">
-        <v>-0.18909429865080085</v>
+        <v>3.6763411225734899E-2</v>
       </c>
       <c r="CT135" s="16">
-        <v>9.0867420250825006</v>
+        <v>6.6111747650667354</v>
       </c>
       <c r="CU135" s="16">
-        <v>10.348194233324222</v>
+        <v>11.335847790135148</v>
       </c>
       <c r="CV135" s="16">
-        <v>3.1072891365063953</v>
+        <v>2.7593123022227672</v>
       </c>
       <c r="CW135" s="16">
-        <v>13.465323793494193</v>
+        <v>13.631819526107051</v>
       </c>
       <c r="CX135" s="20"/>
       <c r="CY135" s="20"/>
@@ -34936,22 +34938,22 @@
         <v>8.7354786322357114</v>
       </c>
       <c r="CR136" s="16">
-        <v>3.701616173745137</v>
+        <v>3.6993829363631647</v>
       </c>
       <c r="CS136" s="16">
-        <v>4.0382300453351831</v>
+        <v>6.8458748016047934</v>
       </c>
       <c r="CT136" s="16">
-        <v>9.1026152136957705</v>
+        <v>6.2096543708993721</v>
       </c>
       <c r="CU136" s="16">
-        <v>3.1664409162560361</v>
+        <v>-1.414368408488869</v>
       </c>
       <c r="CV136" s="16">
-        <v>8.7272336586718495</v>
+        <v>8.7136363255638116</v>
       </c>
       <c r="CW136" s="16">
-        <v>6.0196360569346723</v>
+        <v>6.5098165291881003</v>
       </c>
       <c r="CX136" s="20"/>
       <c r="CY136" s="20"/>
@@ -35318,19 +35320,19 @@
         <v>-17.089635994787983</v>
       </c>
       <c r="CS137" s="16">
-        <v>-5.280035567800951</v>
+        <v>-5.3895895041749071</v>
       </c>
       <c r="CT137" s="16">
-        <v>25.683552378435408</v>
+        <v>20.887932220523382</v>
       </c>
       <c r="CU137" s="16">
-        <v>0.39408035141650544</v>
+        <v>-1.9641411208364161</v>
       </c>
       <c r="CV137" s="16">
-        <v>-7.3595444541674055</v>
+        <v>-6.9212680139198852</v>
       </c>
       <c r="CW137" s="16">
-        <v>-10.598302183466302</v>
+        <v>-14.152310254201467</v>
       </c>
       <c r="CX137" s="20"/>
       <c r="CY137" s="20"/>
@@ -35697,19 +35699,19 @@
         <v>6.9808989013568521</v>
       </c>
       <c r="CS138" s="16">
-        <v>-8.2828536189852855</v>
+        <v>-7.0215743524544791</v>
       </c>
       <c r="CT138" s="16">
-        <v>-1.2077613985195086</v>
+        <v>-1.1228215917124942</v>
       </c>
       <c r="CU138" s="16">
-        <v>-12.353806300829177</v>
+        <v>-11.833765407574532</v>
       </c>
       <c r="CV138" s="16">
-        <v>-7.8826344296451367</v>
+        <v>-7.6333039316124314</v>
       </c>
       <c r="CW138" s="16">
-        <v>-6.7361722670160447</v>
+        <v>-6.7539873147461691</v>
       </c>
       <c r="CX138" s="20"/>
       <c r="CY138" s="20"/>
@@ -36070,25 +36072,25 @@
         <v>12.441335158954473</v>
       </c>
       <c r="CQ139" s="16">
-        <v>8.3911702571248838</v>
+        <v>8.3681717842463996</v>
       </c>
       <c r="CR139" s="16">
         <v>-2.0285245811450636</v>
       </c>
       <c r="CS139" s="16">
-        <v>4.6322141328535906</v>
+        <v>4.5193311538640728</v>
       </c>
       <c r="CT139" s="16">
-        <v>-7.4893852536177121</v>
+        <v>-7.2684373897878913</v>
       </c>
       <c r="CU139" s="16">
-        <v>-6.5522248582707334</v>
+        <v>-4.9723930473837328</v>
       </c>
       <c r="CV139" s="16">
-        <v>-12.928970642962625</v>
+        <v>-12.517891255867326</v>
       </c>
       <c r="CW139" s="16">
-        <v>-10.685495462213524</v>
+        <v>-10.623076904660138</v>
       </c>
       <c r="CX139" s="20"/>
       <c r="CY139" s="20"/>
@@ -36455,19 +36457,19 @@
         <v>-1.0607796209126406</v>
       </c>
       <c r="CS140" s="16">
-        <v>-9.9030116724989625E-2</v>
+        <v>0.3682945550392418</v>
       </c>
       <c r="CT140" s="16">
-        <v>-5.2840358548626511</v>
+        <v>-3.8750191621325598</v>
       </c>
       <c r="CU140" s="16">
-        <v>3.8178240349783721</v>
+        <v>3.9058390675244823</v>
       </c>
       <c r="CV140" s="16">
-        <v>2.0268171073682453</v>
+        <v>2.1590018033343057</v>
       </c>
       <c r="CW140" s="16">
-        <v>9.4234276884959627</v>
+        <v>9.4294511471349409</v>
       </c>
       <c r="CX140" s="20"/>
       <c r="CY140" s="20"/>
@@ -36834,19 +36836,19 @@
         <v>-1.6274466819776165</v>
       </c>
       <c r="CS141" s="16">
-        <v>5.8997233906143691</v>
+        <v>4.6793361703216334</v>
       </c>
       <c r="CT141" s="16">
-        <v>2.1179312047107715</v>
+        <v>2.3631638505070782</v>
       </c>
       <c r="CU141" s="16">
-        <v>-2.6201639861818649</v>
+        <v>-2.437287817146526</v>
       </c>
       <c r="CV141" s="16">
-        <v>-0.24259003214851305</v>
+        <v>0.54752600244911775</v>
       </c>
       <c r="CW141" s="16">
-        <v>-3.0754606770160677</v>
+        <v>-0.83948547016981934</v>
       </c>
       <c r="CX141" s="20"/>
       <c r="CY141" s="20"/>
@@ -37213,19 +37215,19 @@
         <v>-7.6400336329799359</v>
       </c>
       <c r="CS142" s="16">
-        <v>-4.9475547895701339</v>
+        <v>-6.6331094769724928</v>
       </c>
       <c r="CT142" s="16">
-        <v>5.7080175793696526</v>
+        <v>5.8170559902773249</v>
       </c>
       <c r="CU142" s="16">
-        <v>1.5010554611722711</v>
+        <v>1.7448856925109197</v>
       </c>
       <c r="CV142" s="16">
-        <v>0.19158898064377183</v>
+        <v>-0.30384356090357301</v>
       </c>
       <c r="CW142" s="16">
-        <v>5.689952544412975</v>
+        <v>5.8470122432635776</v>
       </c>
       <c r="CX142" s="20"/>
       <c r="CY142" s="20"/>
@@ -37583,28 +37585,28 @@
         <v>8.739532513618343</v>
       </c>
       <c r="CP143" s="16">
-        <v>-2.0761861063216145</v>
+        <v>-2.1177281160638017</v>
       </c>
       <c r="CQ143" s="16">
-        <v>-9.5554689528197798</v>
+        <v>-9.555468953072193</v>
       </c>
       <c r="CR143" s="16">
-        <v>-15.142309818541634</v>
+        <v>-14.412943609173738</v>
       </c>
       <c r="CS143" s="16">
-        <v>-4.2126243368465879</v>
+        <v>-4.1269985056247975</v>
       </c>
       <c r="CT143" s="16">
-        <v>-36.432011911336971</v>
+        <v>-36.625351918094374</v>
       </c>
       <c r="CU143" s="16">
-        <v>-39.657405916256373</v>
+        <v>-37.746515002465721</v>
       </c>
       <c r="CV143" s="16">
-        <v>-25.52473555081265</v>
+        <v>-22.913183400207245</v>
       </c>
       <c r="CW143" s="16">
-        <v>-37.99765548012526</v>
+        <v>-39.367750512562218</v>
       </c>
       <c r="CX143" s="20"/>
       <c r="CY143" s="20"/>
@@ -37968,22 +37970,22 @@
         <v>11.798050364720496</v>
       </c>
       <c r="CR144" s="16">
-        <v>-1.4414256433944672</v>
+        <v>-1.4067877787875602</v>
       </c>
       <c r="CS144" s="16">
-        <v>-1.6681288639616696</v>
+        <v>-2.0956023338876832</v>
       </c>
       <c r="CT144" s="16">
-        <v>-1.1607342884302483</v>
+        <v>-0.83382426366770801</v>
       </c>
       <c r="CU144" s="16">
-        <v>-0.17076478207005152</v>
+        <v>1.2033665530408086</v>
       </c>
       <c r="CV144" s="16">
-        <v>2.0218048004906137</v>
+        <v>3.5255496910753976</v>
       </c>
       <c r="CW144" s="16">
-        <v>8.0495631034075927</v>
+        <v>12.046660871218535</v>
       </c>
       <c r="CX144" s="20"/>
       <c r="CY144" s="20"/>
@@ -38341,28 +38343,28 @@
         <v>-4.5864484310552029</v>
       </c>
       <c r="CP145" s="16">
-        <v>7.7044842692193924</v>
+        <v>7.6951750180132024</v>
       </c>
       <c r="CQ145" s="16">
         <v>-0.13432070943096619</v>
       </c>
       <c r="CR145" s="16">
-        <v>1.0798239033747308</v>
+        <v>1.0798677322343337</v>
       </c>
       <c r="CS145" s="16">
-        <v>-4.4312566430838842</v>
+        <v>-4.6988000387614477</v>
       </c>
       <c r="CT145" s="16">
-        <v>-3.2027412774757664</v>
+        <v>-2.832248366897673</v>
       </c>
       <c r="CU145" s="16">
-        <v>-0.61720422043298129</v>
+        <v>-0.5864938716550796</v>
       </c>
       <c r="CV145" s="16">
-        <v>-9.5186833355697331E-2</v>
+        <v>4.4915962213991634E-2</v>
       </c>
       <c r="CW145" s="16">
-        <v>11.125516176511582</v>
+        <v>11.518874060795994</v>
       </c>
       <c r="CX145" s="20"/>
       <c r="CY145" s="20"/>
@@ -38729,19 +38731,19 @@
         <v>13.381604734981337</v>
       </c>
       <c r="CS146" s="16">
-        <v>16.562039912321282</v>
+        <v>13.96283917352865</v>
       </c>
       <c r="CT146" s="16">
-        <v>14.181786571633111</v>
+        <v>13.623247311340066</v>
       </c>
       <c r="CU146" s="16">
-        <v>-3.0060910516111647</v>
+        <v>-3.0532860852651851</v>
       </c>
       <c r="CV146" s="16">
-        <v>-8.1679660407758945</v>
+        <v>-9.1156611558093772</v>
       </c>
       <c r="CW146" s="16">
-        <v>-6.7923619002223319</v>
+        <v>-6.6142892322296518</v>
       </c>
       <c r="CX146" s="20"/>
       <c r="CY146" s="20"/>
@@ -39108,19 +39110,19 @@
         <v>21.624194389745426</v>
       </c>
       <c r="CS147" s="16">
-        <v>19.58514818612494</v>
+        <v>22.18777327871031</v>
       </c>
       <c r="CT147" s="16">
-        <v>10.405611703026977</v>
+        <v>10.21828271719292</v>
       </c>
       <c r="CU147" s="16">
-        <v>-3.4597038805377593</v>
+        <v>-11.271564730035237</v>
       </c>
       <c r="CV147" s="16">
-        <v>-8.4094391919845606</v>
+        <v>-4.8680011125809841</v>
       </c>
       <c r="CW147" s="16">
-        <v>-18.863225403736365</v>
+        <v>-19.651557174121066</v>
       </c>
       <c r="CX147" s="20"/>
       <c r="CY147" s="20"/>
@@ -39487,19 +39489,19 @@
         <v>4.2633998862867202</v>
       </c>
       <c r="CS148" s="16">
-        <v>3.7138856351032814</v>
+        <v>4.3055326918291996</v>
       </c>
       <c r="CT148" s="16">
-        <v>7.4458878311363748</v>
+        <v>7.2431311933485176</v>
       </c>
       <c r="CU148" s="16">
-        <v>13.71857871836923</v>
+        <v>13.686898313370065</v>
       </c>
       <c r="CV148" s="16">
-        <v>12.014643630144619</v>
+        <v>12.528674261594944</v>
       </c>
       <c r="CW148" s="16">
-        <v>0.8103992516847569</v>
+        <v>0.92283124303132524</v>
       </c>
       <c r="CX148" s="20"/>
       <c r="CY148" s="20"/>
@@ -39863,22 +39865,22 @@
         <v>19.942185185204536</v>
       </c>
       <c r="CR149" s="16">
-        <v>25.166802471478817</v>
+        <v>24.849493248678201</v>
       </c>
       <c r="CS149" s="16">
-        <v>10.367661373866795</v>
+        <v>11.3779636125835</v>
       </c>
       <c r="CT149" s="16">
-        <v>6.5744231913599265</v>
+        <v>5.5663704608363389</v>
       </c>
       <c r="CU149" s="16">
-        <v>-0.75012625536501787</v>
+        <v>-2.3463348289724451</v>
       </c>
       <c r="CV149" s="16">
-        <v>-3.885400363719242</v>
+        <v>-4.1679981164670608</v>
       </c>
       <c r="CW149" s="16">
-        <v>-2.536776058661502</v>
+        <v>2.1591017776340919</v>
       </c>
       <c r="CX149" s="20"/>
       <c r="CY149" s="20"/>
@@ -40245,19 +40247,19 @@
         <v>-2.9483961456011656</v>
       </c>
       <c r="CS150" s="16">
-        <v>1.2068139880832689</v>
+        <v>1.2171512452981261</v>
       </c>
       <c r="CT150" s="16">
-        <v>0.12566778363911624</v>
+        <v>8.1838122669864788E-2</v>
       </c>
       <c r="CU150" s="16">
-        <v>8.8268994774521019</v>
+        <v>8.5201311239581798</v>
       </c>
       <c r="CV150" s="16">
-        <v>15.366080506133599</v>
+        <v>15.091479001290125</v>
       </c>
       <c r="CW150" s="16">
-        <v>14.914470202926381</v>
+        <v>18.295322022049064</v>
       </c>
       <c r="CX150" s="20"/>
       <c r="CY150" s="20"/>
@@ -40791,28 +40793,28 @@
         <v>0.69786260008548595</v>
       </c>
       <c r="CP152" s="16">
-        <v>4.5653788353914706</v>
+        <v>4.5659593582659426</v>
       </c>
       <c r="CQ152" s="16">
-        <v>3.9990480516738387</v>
+        <v>4.045319751156299</v>
       </c>
       <c r="CR152" s="16">
-        <v>2.8632085667841096</v>
+        <v>2.8437887662920076</v>
       </c>
       <c r="CS152" s="16">
-        <v>3.2637743207885705</v>
+        <v>3.2192649590228513</v>
       </c>
       <c r="CT152" s="16">
-        <v>4.3014778973359427</v>
+        <v>4.3001349374521993</v>
       </c>
       <c r="CU152" s="16">
-        <v>2.5465360956359291</v>
+        <v>2.5236543057592939</v>
       </c>
       <c r="CV152" s="16">
-        <v>1.2999778456429567</v>
+        <v>1.3317600382489303</v>
       </c>
       <c r="CW152" s="16">
-        <v>1.5795815478037269</v>
+        <v>1.7708419752965767</v>
       </c>
       <c r="CX152" s="20"/>
       <c r="CY152" s="20"/>
@@ -41366,7 +41368,7 @@
     </row>
     <row r="158" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="CZ158" s="6"/>
       <c r="DA158" s="6"/>
@@ -41378,7 +41380,7 @@
     </row>
     <row r="161" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="162" spans="1:179" x14ac:dyDescent="0.2">
@@ -42158,28 +42160,28 @@
         <v>131.46451457678228</v>
       </c>
       <c r="CT167" s="16">
-        <v>120.5604992153738</v>
+        <v>120.56027848615858</v>
       </c>
       <c r="CU167" s="16">
-        <v>100.17638185389579</v>
+        <v>100.17637146040374</v>
       </c>
       <c r="CV167" s="16">
-        <v>104.22239096991473</v>
+        <v>104.22060837902809</v>
       </c>
       <c r="CW167" s="16">
-        <v>133.83070658593124</v>
+        <v>133.83090319504467</v>
       </c>
       <c r="CX167" s="16">
-        <v>120.9229728509204</v>
+        <v>120.92205759706327</v>
       </c>
       <c r="CY167" s="16">
-        <v>102.37772789693092</v>
+        <v>102.38681750333261</v>
       </c>
       <c r="CZ167" s="16">
-        <v>105.07028025463585</v>
+        <v>105.0807875587498</v>
       </c>
       <c r="DA167" s="16">
-        <v>134.00340275758793</v>
+        <v>134.0009112412896</v>
       </c>
       <c r="DB167" s="8"/>
       <c r="DC167" s="8"/>
@@ -42552,25 +42554,25 @@
         <v>113.5960233972329</v>
       </c>
       <c r="CU168" s="16">
-        <v>108.47428462121927</v>
+        <v>108.47394686544081</v>
       </c>
       <c r="CV168" s="16">
-        <v>136.25714087681763</v>
+        <v>136.25525654767296</v>
       </c>
       <c r="CW168" s="16">
         <v>136.11186188226861</v>
       </c>
       <c r="CX168" s="16">
-        <v>115.5895247780204</v>
+        <v>115.58949356749244</v>
       </c>
       <c r="CY168" s="16">
-        <v>105.93070841488679</v>
+        <v>105.92577627027084</v>
       </c>
       <c r="CZ168" s="16">
-        <v>133.84789917944394</v>
+        <v>133.84594343834942</v>
       </c>
       <c r="DA168" s="16">
-        <v>134.26909512044182</v>
+        <v>134.26059903443775</v>
       </c>
       <c r="DB168" s="8"/>
       <c r="DC168" s="8"/>
@@ -42949,19 +42951,19 @@
         <v>96.982187145244836</v>
       </c>
       <c r="CW169" s="16">
-        <v>145.1507700799996</v>
+        <v>144.8723067471679</v>
       </c>
       <c r="CX169" s="16">
-        <v>102.45643446859422</v>
+        <v>102.45948254973365</v>
       </c>
       <c r="CY169" s="16">
-        <v>98.637243277421049</v>
+        <v>98.636959059532273</v>
       </c>
       <c r="CZ169" s="16">
-        <v>98.2442144244704</v>
+        <v>98.175690593284514</v>
       </c>
       <c r="DA169" s="16">
-        <v>149.01619615917281</v>
+        <v>148.73823641789875</v>
       </c>
       <c r="DB169" s="8"/>
       <c r="DC169" s="8"/>
@@ -43331,28 +43333,28 @@
         <v>104.44053420602725</v>
       </c>
       <c r="CT170" s="16">
-        <v>89.81782841554535</v>
+        <v>89.813680250025925</v>
       </c>
       <c r="CU170" s="16">
         <v>88.417821851651283</v>
       </c>
       <c r="CV170" s="16">
-        <v>112.4354382523999</v>
+        <v>112.43543825239981</v>
       </c>
       <c r="CW170" s="16">
-        <v>104.96467355958757</v>
+        <v>104.97201855236827</v>
       </c>
       <c r="CX170" s="16">
-        <v>90.077537688864908</v>
+        <v>90.121312899088622</v>
       </c>
       <c r="CY170" s="16">
         <v>88.579938111488559</v>
       </c>
       <c r="CZ170" s="16">
-        <v>113.33635107687601</v>
+        <v>113.33635107687603</v>
       </c>
       <c r="DA170" s="16">
-        <v>102.42556485427394</v>
+        <v>101.88675539619258</v>
       </c>
       <c r="DB170" s="8"/>
       <c r="DC170" s="8"/>
@@ -43728,22 +43730,22 @@
         <v>88.904935381336514</v>
       </c>
       <c r="CV171" s="16">
-        <v>85.383399478520261</v>
+        <v>85.38339947852036</v>
       </c>
       <c r="CW171" s="16">
-        <v>74.94555610981503</v>
+        <v>74.917186508813217</v>
       </c>
       <c r="CX171" s="16">
-        <v>93.211808407391743</v>
+        <v>93.153644341201698</v>
       </c>
       <c r="CY171" s="16">
-        <v>86.281225042473551</v>
+        <v>86.279974032157398</v>
       </c>
       <c r="CZ171" s="16">
-        <v>85.722793192327771</v>
+        <v>85.729077737549886</v>
       </c>
       <c r="DA171" s="16">
-        <v>76.450855068856896</v>
+        <v>75.88969548718002</v>
       </c>
       <c r="DB171" s="8"/>
       <c r="DC171" s="8"/>
@@ -44122,19 +44124,19 @@
         <v>116.64325246805976</v>
       </c>
       <c r="CW172" s="16">
-        <v>95.52800198349594</v>
+        <v>95.53672747939062</v>
       </c>
       <c r="CX172" s="16">
-        <v>85.541380006692933</v>
+        <v>85.543474883130386</v>
       </c>
       <c r="CY172" s="16">
-        <v>121.62612337267701</v>
+        <v>121.62964376814152</v>
       </c>
       <c r="CZ172" s="16">
-        <v>117.321841884054</v>
+        <v>117.30928035381925</v>
       </c>
       <c r="DA172" s="16">
-        <v>96.108197575827589</v>
+        <v>96.11698254275467</v>
       </c>
       <c r="DB172" s="8"/>
       <c r="DC172" s="8"/>
@@ -44504,7 +44506,7 @@
         <v>74.970910387748347</v>
       </c>
       <c r="CT173" s="16">
-        <v>72.660048934413922</v>
+        <v>72.661919383526964</v>
       </c>
       <c r="CU173" s="16">
         <v>53.488131937927463</v>
@@ -44513,19 +44515,19 @@
         <v>68.584372693478628</v>
       </c>
       <c r="CW173" s="16">
-        <v>75.263035822936899</v>
+        <v>75.235590769170287</v>
       </c>
       <c r="CX173" s="16">
-        <v>72.502993135060436</v>
+        <v>72.550449198491123</v>
       </c>
       <c r="CY173" s="16">
-        <v>54.220247721103355</v>
+        <v>54.225303911337853</v>
       </c>
       <c r="CZ173" s="16">
-        <v>66.42341947403402</v>
+        <v>66.419366142145819</v>
       </c>
       <c r="DA173" s="16">
-        <v>74.874987420989029</v>
+        <v>74.847683871071297</v>
       </c>
       <c r="DB173" s="8"/>
       <c r="DC173" s="8"/>
@@ -44901,22 +44903,22 @@
         <v>76.201751103466435</v>
       </c>
       <c r="CV174" s="16">
-        <v>88.016038256078204</v>
+        <v>88.016038256078232</v>
       </c>
       <c r="CW174" s="16">
-        <v>104.49898453572419</v>
+        <v>104.49898453572413</v>
       </c>
       <c r="CX174" s="16">
-        <v>93.537684216924617</v>
+        <v>93.572615699752021</v>
       </c>
       <c r="CY174" s="16">
-        <v>76.08458597714484</v>
+        <v>76.176168134077756</v>
       </c>
       <c r="CZ174" s="16">
-        <v>83.539902430328823</v>
+        <v>83.539838094659956</v>
       </c>
       <c r="DA174" s="16">
-        <v>102.90212757130229</v>
+        <v>102.90212757130215</v>
       </c>
       <c r="DB174" s="8"/>
       <c r="DC174" s="8"/>
@@ -45295,19 +45297,19 @@
         <v>109.01918853155021</v>
       </c>
       <c r="CW175" s="16">
-        <v>119.75107066890382</v>
+        <v>119.74799083701848</v>
       </c>
       <c r="CX175" s="16">
-        <v>95.586803965559625</v>
+        <v>95.43866057961236</v>
       </c>
       <c r="CY175" s="16">
-        <v>108.22723442238475</v>
+        <v>108.13208651461674</v>
       </c>
       <c r="CZ175" s="16">
-        <v>110.77345774942722</v>
+        <v>110.79231457397221</v>
       </c>
       <c r="DA175" s="16">
-        <v>121.70022677626955</v>
+        <v>121.9581770413261</v>
       </c>
       <c r="DB175" s="8"/>
       <c r="DC175" s="8"/>
@@ -45686,19 +45688,19 @@
         <v>54.726694750449369</v>
       </c>
       <c r="CW176" s="16">
-        <v>115.05513715008871</v>
+        <v>115.05513715008873</v>
       </c>
       <c r="CX176" s="16">
-        <v>158.28812720846699</v>
+        <v>158.28812720846696</v>
       </c>
       <c r="CY176" s="16">
-        <v>98.854961469069806</v>
+        <v>98.854961469069792</v>
       </c>
       <c r="CZ176" s="16">
         <v>54.198423076740873</v>
       </c>
       <c r="DA176" s="16">
-        <v>118.75759437976224</v>
+        <v>118.75759437976221</v>
       </c>
       <c r="DB176" s="8"/>
       <c r="DC176" s="8"/>
@@ -46071,25 +46073,25 @@
         <v>75.447065474623059</v>
       </c>
       <c r="CU177" s="16">
-        <v>79.583700707139784</v>
+        <v>79.583732208765511</v>
       </c>
       <c r="CV177" s="16">
         <v>97.828427527123011</v>
       </c>
       <c r="CW177" s="16">
-        <v>116.70380761132242</v>
+        <v>116.70170352639857</v>
       </c>
       <c r="CX177" s="16">
-        <v>76.797954726655192</v>
+        <v>76.7991053234676</v>
       </c>
       <c r="CY177" s="16">
-        <v>79.76719492538632</v>
+        <v>79.764719479379238</v>
       </c>
       <c r="CZ177" s="16">
-        <v>96.31076683538025</v>
+        <v>96.313173242203931</v>
       </c>
       <c r="DA177" s="16">
-        <v>116.6406508832716</v>
+        <v>116.63977229920155</v>
       </c>
       <c r="DB177" s="8"/>
       <c r="DC177" s="8"/>
@@ -46468,19 +46470,19 @@
         <v>65.694774168238411</v>
       </c>
       <c r="CW178" s="16">
-        <v>77.402484363789583</v>
+        <v>77.470965899531777</v>
       </c>
       <c r="CX178" s="16">
-        <v>77.841230873757013</v>
+        <v>77.80710792850482</v>
       </c>
       <c r="CY178" s="16">
-        <v>59.292959718167936</v>
+        <v>59.291624998452377</v>
       </c>
       <c r="CZ178" s="16">
-        <v>62.415552460215018</v>
+        <v>62.415325485561247</v>
       </c>
       <c r="DA178" s="16">
-        <v>73.256830797270041</v>
+        <v>73.325357671059237</v>
       </c>
       <c r="DB178" s="8"/>
       <c r="DC178" s="8"/>
@@ -46859,19 +46861,19 @@
         <v>115.6734027080731</v>
       </c>
       <c r="CW179" s="16">
-        <v>123.27011040814814</v>
+        <v>123.27011040814808</v>
       </c>
       <c r="CX179" s="16">
-        <v>117.50731464916859</v>
+        <v>117.50743236092819</v>
       </c>
       <c r="CY179" s="16">
-        <v>95.483596268861263</v>
+        <v>95.48708745888662</v>
       </c>
       <c r="CZ179" s="16">
-        <v>115.01966179902512</v>
+        <v>115.01974572944967</v>
       </c>
       <c r="DA179" s="16">
-        <v>125.05438081469372</v>
+        <v>125.14746118504696</v>
       </c>
       <c r="DB179" s="8"/>
       <c r="DC179" s="8"/>
@@ -47241,7 +47243,7 @@
         <v>113.05362922739322</v>
       </c>
       <c r="CT180" s="16">
-        <v>112.99087296590477</v>
+        <v>112.99087296590483</v>
       </c>
       <c r="CU180" s="16">
         <v>90.004517601145878</v>
@@ -47250,19 +47252,19 @@
         <v>96.553140645569314</v>
       </c>
       <c r="CW180" s="16">
-        <v>114.29898951843545</v>
+        <v>114.29905298926322</v>
       </c>
       <c r="CX180" s="16">
-        <v>114.51736503006921</v>
+        <v>114.51753171977013</v>
       </c>
       <c r="CY180" s="16">
-        <v>90.961588000955501</v>
+        <v>90.96184089556391</v>
       </c>
       <c r="CZ180" s="16">
-        <v>98.015100295578023</v>
+        <v>98.015100295578037</v>
       </c>
       <c r="DA180" s="16">
-        <v>112.52701042661602</v>
+        <v>112.52707291345463</v>
       </c>
       <c r="DB180" s="8"/>
       <c r="DC180" s="8"/>
@@ -47635,25 +47637,25 @@
         <v>63.273823357346807</v>
       </c>
       <c r="CU181" s="16">
-        <v>53.389933341126408</v>
+        <v>53.389933341126316</v>
       </c>
       <c r="CV181" s="16">
-        <v>91.329194127829169</v>
+        <v>91.329194127829098</v>
       </c>
       <c r="CW181" s="16">
-        <v>72.122532091631612</v>
+        <v>72.120767743445214</v>
       </c>
       <c r="CX181" s="16">
-        <v>63.876785635364456</v>
+        <v>63.877287640385497</v>
       </c>
       <c r="CY181" s="16">
-        <v>51.111161397034863</v>
+        <v>51.112216138681241</v>
       </c>
       <c r="CZ181" s="16">
-        <v>90.067609218174255</v>
+        <v>90.066527425759418</v>
       </c>
       <c r="DA181" s="16">
-        <v>74.303998189132813</v>
+        <v>72.980093786738266</v>
       </c>
       <c r="DB181" s="8"/>
       <c r="DC181" s="8"/>
@@ -48029,22 +48031,22 @@
         <v>78.264557880845558</v>
       </c>
       <c r="CV182" s="16">
-        <v>93.665950062404136</v>
+        <v>93.665950062404121</v>
       </c>
       <c r="CW182" s="16">
-        <v>114.62675402854255</v>
+        <v>114.571263413271</v>
       </c>
       <c r="CX182" s="16">
-        <v>112.94848730700376</v>
+        <v>112.94930434378574</v>
       </c>
       <c r="CY182" s="16">
-        <v>78.513818018684418</v>
+        <v>78.531250989527848</v>
       </c>
       <c r="CZ182" s="16">
-        <v>92.478263435856832</v>
+        <v>92.485977709392813</v>
       </c>
       <c r="DA182" s="16">
-        <v>113.08782468797274</v>
+        <v>113.03470850848201</v>
       </c>
       <c r="DB182" s="8"/>
       <c r="DC182" s="8"/>
@@ -48414,28 +48416,28 @@
         <v>73.457950201567598</v>
       </c>
       <c r="CT183" s="16">
-        <v>79.856981280455287</v>
+        <v>79.856981280455301</v>
       </c>
       <c r="CU183" s="16">
         <v>95.716331999031212</v>
       </c>
       <c r="CV183" s="16">
-        <v>115.69377912800596</v>
+        <v>115.693779128006</v>
       </c>
       <c r="CW183" s="16">
-        <v>75.566503794475722</v>
+        <v>75.566503794475707</v>
       </c>
       <c r="CX183" s="16">
         <v>82.277435116743476</v>
       </c>
       <c r="CY183" s="16">
-        <v>96.49294763206855</v>
+        <v>96.492947632068521</v>
       </c>
       <c r="CZ183" s="16">
-        <v>115.52902595032046</v>
+        <v>115.52902595032045</v>
       </c>
       <c r="DA183" s="16">
-        <v>75.657959942414507</v>
+        <v>75.657959942414408</v>
       </c>
       <c r="DB183" s="8"/>
       <c r="DC183" s="8"/>
@@ -48814,19 +48816,19 @@
         <v>91.020104229363923</v>
       </c>
       <c r="CW184" s="16">
-        <v>102.5392222450855</v>
+        <v>102.53922224508547</v>
       </c>
       <c r="CX184" s="16">
-        <v>113.49791920134327</v>
+        <v>113.49791920134319</v>
       </c>
       <c r="CY184" s="16">
-        <v>74.883926187551879</v>
+        <v>74.883926187551864</v>
       </c>
       <c r="CZ184" s="16">
-        <v>90.736928611725133</v>
+        <v>90.736928611725162</v>
       </c>
       <c r="DA184" s="16">
-        <v>102.64785171126989</v>
+        <v>102.64785171126985</v>
       </c>
       <c r="DB184" s="8"/>
       <c r="DC184" s="8"/>
@@ -49205,19 +49207,19 @@
         <v>84.627885282649274</v>
       </c>
       <c r="CW185" s="16">
-        <v>101.35711528994568</v>
+        <v>101.25398231011913</v>
       </c>
       <c r="CX185" s="16">
-        <v>82.792754935826423</v>
+        <v>82.799777985421201</v>
       </c>
       <c r="CY185" s="16">
-        <v>92.329028347752782</v>
+        <v>92.22392277485973</v>
       </c>
       <c r="CZ185" s="16">
-        <v>76.965201350677049</v>
+        <v>76.931171210016657</v>
       </c>
       <c r="DA185" s="16">
-        <v>102.19782131645641</v>
+        <v>100.97986648258184</v>
       </c>
       <c r="DB185" s="8"/>
       <c r="DC185" s="8"/>
@@ -49587,7 +49589,7 @@
         <v>87.990561373476055</v>
       </c>
       <c r="CT186" s="16">
-        <v>89.645234344169452</v>
+        <v>89.645234344169523</v>
       </c>
       <c r="CU186" s="16">
         <v>75.916981822219199</v>
@@ -49596,19 +49598,19 @@
         <v>83.379092664548239</v>
       </c>
       <c r="CW186" s="16">
-        <v>89.171209370576804</v>
+        <v>89.13906391941488</v>
       </c>
       <c r="CX186" s="16">
-        <v>89.911687356507457</v>
+        <v>89.915474694522658</v>
       </c>
       <c r="CY186" s="16">
-        <v>74.752347382298765</v>
+        <v>74.752700522207647</v>
       </c>
       <c r="CZ186" s="16">
-        <v>80.51236379843948</v>
+        <v>80.499218994150894</v>
       </c>
       <c r="DA186" s="16">
-        <v>89.43041453165884</v>
+        <v>89.396729190121277</v>
       </c>
       <c r="DB186" s="8"/>
       <c r="DC186" s="8"/>
@@ -49984,22 +49986,22 @@
         <v>96.32856712375947</v>
       </c>
       <c r="CV187" s="16">
-        <v>87.590031136378215</v>
+        <v>87.589471096666642</v>
       </c>
       <c r="CW187" s="16">
-        <v>110.31895428907939</v>
+        <v>110.31895428907941</v>
       </c>
       <c r="CX187" s="16">
-        <v>88.133148097011201</v>
+        <v>88.166670621134003</v>
       </c>
       <c r="CY187" s="16">
-        <v>95.637459987491795</v>
+        <v>95.726865862862667</v>
       </c>
       <c r="CZ187" s="16">
-        <v>89.60724170716496</v>
+        <v>89.624732480657897</v>
       </c>
       <c r="DA187" s="16">
-        <v>111.09800830442632</v>
+        <v>110.8087980093088</v>
       </c>
       <c r="DB187" s="8"/>
       <c r="DC187" s="8"/>
@@ -50372,25 +50374,25 @@
         <v>95.368555673559968</v>
       </c>
       <c r="CU188" s="16">
-        <v>81.734192262004484</v>
+        <v>81.734192262004512</v>
       </c>
       <c r="CV188" s="16">
         <v>92.481304787594325</v>
       </c>
       <c r="CW188" s="16">
-        <v>105.83070160004104</v>
+        <v>105.830766779293</v>
       </c>
       <c r="CX188" s="16">
-        <v>95.864742572046509</v>
+        <v>95.863844302742336</v>
       </c>
       <c r="CY188" s="16">
-        <v>81.762540015520614</v>
+        <v>81.755534711422911</v>
       </c>
       <c r="CZ188" s="16">
-        <v>89.233251710379761</v>
+        <v>89.230034149832022</v>
       </c>
       <c r="DA188" s="16">
-        <v>105.87682565616487</v>
+        <v>105.89513660901841</v>
       </c>
       <c r="DB188" s="8"/>
       <c r="DC188" s="8"/>
@@ -50940,28 +50942,28 @@
         <v>118.09701168008566</v>
       </c>
       <c r="CT190" s="16">
-        <v>104.31090373630731</v>
+        <v>104.31012097507679</v>
       </c>
       <c r="CU190" s="16">
-        <v>93.39255394492325</v>
+        <v>93.399833936408172</v>
       </c>
       <c r="CV190" s="16">
-        <v>101.67182179400413</v>
+        <v>101.64082267484491</v>
       </c>
       <c r="CW190" s="16">
-        <v>120.23347345784468</v>
+        <v>120.20790908910874</v>
       </c>
       <c r="CX190" s="16">
-        <v>106.59656741781038</v>
+        <v>106.59087935373242</v>
       </c>
       <c r="CY190" s="16">
-        <v>95.212936296029994</v>
+        <v>95.170110470779576</v>
       </c>
       <c r="CZ190" s="16">
-        <v>101.47938160517268</v>
+        <v>101.42327924282458</v>
       </c>
       <c r="DA190" s="16">
-        <v>120.69554764466623</v>
+        <v>120.63039232297301</v>
       </c>
       <c r="DB190" s="8"/>
       <c r="DC190" s="8"/>
@@ -51162,7 +51164,7 @@
     </row>
     <row r="197" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="199" spans="1:179" x14ac:dyDescent="0.2">
@@ -51172,7 +51174,7 @@
     </row>
     <row r="200" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="201" spans="1:179" x14ac:dyDescent="0.2">
@@ -51952,28 +51954,28 @@
         <v>56.904181046875514</v>
       </c>
       <c r="CT206" s="16">
-        <v>60.472345194999733</v>
+        <v>60.47606427704374</v>
       </c>
       <c r="CU206" s="16">
-        <v>52.620459159403531</v>
+        <v>52.593108925684838</v>
       </c>
       <c r="CV206" s="16">
-        <v>39.047008390252877</v>
+        <v>39.093959450204984</v>
       </c>
       <c r="CW206" s="16">
-        <v>57.950708655827952</v>
+        <v>57.928634282842673</v>
       </c>
       <c r="CX206" s="16">
-        <v>63.027514241239935</v>
+        <v>63.046859032988124</v>
       </c>
       <c r="CY206" s="16">
-        <v>55.804632521682983</v>
+        <v>55.679385375663216</v>
       </c>
       <c r="CZ206" s="16">
-        <v>43.227803441317327</v>
+        <v>43.073741299658252</v>
       </c>
       <c r="DA206" s="16">
-        <v>60.453486514813548</v>
+        <v>60.423026912769153</v>
       </c>
       <c r="DB206" s="8"/>
       <c r="DC206" s="8"/>
@@ -52343,28 +52345,28 @@
         <v>4.4108161020230563</v>
       </c>
       <c r="CT207" s="16">
-        <v>3.2119752924461951</v>
+        <v>3.211981563484525</v>
       </c>
       <c r="CU207" s="16">
-        <v>4.2697336379617639</v>
+        <v>4.3213792712186585</v>
       </c>
       <c r="CV207" s="16">
-        <v>8.6935418080588569</v>
+        <v>8.5871016502375745</v>
       </c>
       <c r="CW207" s="16">
-        <v>4.4959233872799489</v>
+        <v>4.4532264916305575</v>
       </c>
       <c r="CX207" s="16">
-        <v>3.0412714765779594</v>
+        <v>3.0415444084522965</v>
       </c>
       <c r="CY207" s="16">
-        <v>3.994992451937645</v>
+        <v>4.0292648034122873</v>
       </c>
       <c r="CZ207" s="16">
-        <v>7.9064420606861168</v>
+        <v>7.8121907235701658</v>
       </c>
       <c r="DA207" s="16">
-        <v>4.2037252684478377</v>
+        <v>4.1673369041967545</v>
       </c>
       <c r="DB207" s="8"/>
       <c r="DC207" s="8"/>
@@ -52734,28 +52736,28 @@
         <v>0.25653001963771355</v>
       </c>
       <c r="CT208" s="16">
-        <v>0.2121336164210067</v>
+        <v>0.2121340305892111</v>
       </c>
       <c r="CU208" s="16">
-        <v>0.32639388886363191</v>
+        <v>0.32622330363472207</v>
       </c>
       <c r="CV208" s="16">
-        <v>0.71214860788253842</v>
+        <v>0.71250031858081098</v>
       </c>
       <c r="CW208" s="16">
-        <v>0.24940104983405056</v>
+        <v>0.25180891377899106</v>
       </c>
       <c r="CX208" s="16">
-        <v>0.23552981284120997</v>
+        <v>0.23569357386908474</v>
       </c>
       <c r="CY208" s="16">
-        <v>0.33197746794820959</v>
+        <v>0.33128513967270423</v>
       </c>
       <c r="CZ208" s="16">
-        <v>0.78683582151711562</v>
+        <v>0.79197384299883544</v>
       </c>
       <c r="DA208" s="16">
-        <v>0.27229388527509851</v>
+        <v>0.27452884148988888</v>
       </c>
       <c r="DB208" s="8"/>
       <c r="DC208" s="8"/>
@@ -53125,28 +53127,28 @@
         <v>0.87865181530589653</v>
       </c>
       <c r="CT209" s="16">
-        <v>0.7052265904470022</v>
+        <v>0.69494748777760562</v>
       </c>
       <c r="CU209" s="16">
-        <v>0.99426323362412605</v>
+        <v>0.993743595766031</v>
       </c>
       <c r="CV209" s="16">
-        <v>1.285344660565525</v>
+        <v>1.2929028625419003</v>
       </c>
       <c r="CW209" s="16">
-        <v>0.7890933823862406</v>
+        <v>0.78892200488984654</v>
       </c>
       <c r="CX209" s="16">
-        <v>0.80473990196222189</v>
+        <v>0.78274478249100699</v>
       </c>
       <c r="CY209" s="16">
-        <v>1.0213312418203355</v>
+        <v>1.0215643632026545</v>
       </c>
       <c r="CZ209" s="16">
-        <v>1.4406992870739972</v>
+        <v>1.4490759039259249</v>
       </c>
       <c r="DA209" s="16">
-        <v>0.71912228396711342</v>
+        <v>0.70804801167050124</v>
       </c>
       <c r="DB209" s="8"/>
       <c r="DC209" s="8"/>
@@ -53516,28 +53518,28 @@
         <v>0.63055802108129566</v>
       </c>
       <c r="CT210" s="16">
-        <v>1.0920059985731128</v>
+        <v>1.092008130598066</v>
       </c>
       <c r="CU210" s="16">
-        <v>1.1433824585977928</v>
+        <v>1.1427848856496274</v>
       </c>
       <c r="CV210" s="16">
-        <v>1.6668856460577051</v>
+        <v>1.6679910850349557</v>
       </c>
       <c r="CW210" s="16">
-        <v>0.6154173889556287</v>
+        <v>0.61690933316733321</v>
       </c>
       <c r="CX210" s="16">
-        <v>0.996524642600771</v>
+        <v>1.0062645020699994</v>
       </c>
       <c r="CY210" s="16">
-        <v>1.0668729202031926</v>
+        <v>1.0672236856361852</v>
       </c>
       <c r="CZ210" s="16">
-        <v>1.5344367020963603</v>
+        <v>1.5305615966280617</v>
       </c>
       <c r="DA210" s="16">
-        <v>0.57107671208097832</v>
+        <v>0.57343459817602682</v>
       </c>
       <c r="DB210" s="8"/>
       <c r="DC210" s="8"/>
@@ -53907,28 +53909,28 @@
         <v>0.40696781036783258</v>
       </c>
       <c r="CT211" s="16">
-        <v>0.18119782881220109</v>
+        <v>0.18119818258158787</v>
       </c>
       <c r="CU211" s="16">
-        <v>0.13693319980229934</v>
+        <v>0.13686163356889053</v>
       </c>
       <c r="CV211" s="16">
-        <v>0.26819185022527797</v>
+        <v>0.26832430283681113</v>
       </c>
       <c r="CW211" s="16">
-        <v>0.48178262814009909</v>
+        <v>0.48447588945819392</v>
       </c>
       <c r="CX211" s="16">
-        <v>0.23077149278732481</v>
+        <v>0.22895135062937533</v>
       </c>
       <c r="CY211" s="16">
-        <v>0.20307056025195575</v>
+        <v>0.2035448842906423</v>
       </c>
       <c r="CZ211" s="16">
-        <v>0.28484573504947142</v>
+        <v>0.2831904149456364</v>
       </c>
       <c r="DA211" s="16">
-        <v>0.5140927820502601</v>
+        <v>0.52173121667914601</v>
       </c>
       <c r="DB211" s="8"/>
       <c r="DC211" s="8"/>
@@ -54298,28 +54300,28 @@
         <v>0.90461345244015956</v>
       </c>
       <c r="CT212" s="16">
-        <v>0.46658305445938553</v>
+        <v>0.47478653175463986</v>
       </c>
       <c r="CU212" s="16">
-        <v>0.62433479073988318</v>
+        <v>0.62400849084019594</v>
       </c>
       <c r="CV212" s="16">
-        <v>0.49591156839032779</v>
+        <v>0.49615648553552671</v>
       </c>
       <c r="CW212" s="16">
-        <v>0.8621751591043989</v>
+        <v>0.86436729892631325</v>
       </c>
       <c r="CX212" s="16">
-        <v>0.47649375058492804</v>
+        <v>0.47419382423974554</v>
       </c>
       <c r="CY212" s="16">
-        <v>0.66800872096045871</v>
+        <v>0.67420432924561513</v>
       </c>
       <c r="CZ212" s="16">
-        <v>0.48978232639224722</v>
+        <v>0.48830857986412257</v>
       </c>
       <c r="DA212" s="16">
-        <v>0.95442414514507568</v>
+        <v>0.9567671474837941</v>
       </c>
       <c r="DB212" s="8"/>
       <c r="DC212" s="8"/>
@@ -54689,28 +54691,28 @@
         <v>0.47088293941441406</v>
       </c>
       <c r="CT213" s="16">
-        <v>0.56578407899838623</v>
+        <v>0.56578518363130592</v>
       </c>
       <c r="CU213" s="16">
-        <v>0.74007845537040184</v>
+        <v>0.73969166365331385</v>
       </c>
       <c r="CV213" s="16">
-        <v>1.0950865453490197</v>
+        <v>1.0956037840300621</v>
       </c>
       <c r="CW213" s="16">
-        <v>0.46628497452663409</v>
+        <v>0.47917682805155459</v>
       </c>
       <c r="CX213" s="16">
-        <v>0.56801435424628843</v>
+        <v>0.55319297641743215</v>
       </c>
       <c r="CY213" s="16">
-        <v>0.72919425491014844</v>
+        <v>0.69781447126999308</v>
       </c>
       <c r="CZ213" s="16">
-        <v>1.1177183266688147</v>
+        <v>1.1180321606060546</v>
       </c>
       <c r="DA213" s="16">
-        <v>0.4773948599813716</v>
+        <v>0.49209693959136264</v>
       </c>
       <c r="DB213" s="8"/>
       <c r="DC213" s="8"/>
@@ -55080,28 +55082,28 @@
         <v>0.78860066188598554</v>
       </c>
       <c r="CT214" s="16">
-        <v>0.82865276806925336</v>
+        <v>0.82865438592518215</v>
       </c>
       <c r="CU214" s="16">
-        <v>1.5213354010896583</v>
+        <v>1.5205402962899115</v>
       </c>
       <c r="CV214" s="16">
-        <v>0.49165890214331087</v>
+        <v>0.49190171901309154</v>
       </c>
       <c r="CW214" s="16">
-        <v>0.77445352593956829</v>
+        <v>0.774036027696971</v>
       </c>
       <c r="CX214" s="16">
-        <v>0.97747979123026674</v>
+        <v>0.93878261767777349</v>
       </c>
       <c r="CY214" s="16">
-        <v>1.4696099669523424</v>
+        <v>1.4341549649127423</v>
       </c>
       <c r="CZ214" s="16">
-        <v>0.45773149857325712</v>
+        <v>0.46017225054154604</v>
       </c>
       <c r="DA214" s="16">
-        <v>0.69005043659532039</v>
+        <v>0.66265184539923039</v>
       </c>
       <c r="DB214" s="8"/>
       <c r="DC214" s="8"/>
@@ -55471,28 +55473,28 @@
         <v>5.3748160410948813</v>
       </c>
       <c r="CT215" s="16">
-        <v>1.5172522133520636</v>
+        <v>1.5172551756247832</v>
       </c>
       <c r="CU215" s="16">
-        <v>6.1144151405015199</v>
+        <v>6.1112195264230094</v>
       </c>
       <c r="CV215" s="16">
-        <v>1.6484765818894207</v>
+        <v>1.6492907193366961</v>
       </c>
       <c r="CW215" s="16">
-        <v>4.6797606588783704</v>
+        <v>4.747171040724063</v>
       </c>
       <c r="CX215" s="16">
-        <v>1.4357839057560262</v>
+        <v>1.4371055769705192</v>
       </c>
       <c r="CY215" s="16">
-        <v>5.3478961814554467</v>
+        <v>5.3808553609680025</v>
       </c>
       <c r="CZ215" s="16">
-        <v>1.4873910556547973</v>
+        <v>1.4920555524418073</v>
       </c>
       <c r="DA215" s="16">
-        <v>4.4179416928518034</v>
+        <v>4.4737680335472874</v>
       </c>
       <c r="DB215" s="8"/>
       <c r="DC215" s="8"/>
@@ -55862,28 +55864,28 @@
         <v>13.856745288331563</v>
       </c>
       <c r="CT216" s="16">
-        <v>7.9322867134132</v>
+        <v>7.9323022003548749</v>
       </c>
       <c r="CU216" s="16">
-        <v>8.3366829088743017</v>
+        <v>8.3305611993806608</v>
       </c>
       <c r="CV216" s="16">
-        <v>13.868654201654543</v>
+        <v>13.875503550230631</v>
       </c>
       <c r="CW216" s="16">
-        <v>13.810670074341497</v>
+        <v>13.804405558865481</v>
       </c>
       <c r="CX216" s="16">
-        <v>7.007987167986653</v>
+        <v>7.02525627282761</v>
       </c>
       <c r="CY216" s="16">
-        <v>7.4689187839796753</v>
+        <v>7.5950746176501962</v>
       </c>
       <c r="CZ216" s="16">
-        <v>11.757939180110169</v>
+        <v>11.818804596260618</v>
       </c>
       <c r="DA216" s="16">
-        <v>12.090085641253239</v>
+        <v>12.074398697284028</v>
       </c>
       <c r="DB216" s="8"/>
       <c r="DC216" s="8"/>
@@ -56253,28 +56255,28 @@
         <v>1.0579984983435897</v>
       </c>
       <c r="CT217" s="16">
-        <v>0.7670042625689808</v>
+        <v>0.7670057600627942</v>
       </c>
       <c r="CU217" s="16">
-        <v>0.86344266876931164</v>
+        <v>0.86299140246093997</v>
       </c>
       <c r="CV217" s="16">
-        <v>1.4700854715651697</v>
+        <v>1.4708115065275378</v>
       </c>
       <c r="CW217" s="16">
-        <v>1.0171985995529602</v>
+        <v>1.0235197973370458</v>
       </c>
       <c r="CX217" s="16">
-        <v>0.67597140205598272</v>
+        <v>0.68576819408471457</v>
       </c>
       <c r="CY217" s="16">
-        <v>0.79956061598065675</v>
+        <v>0.8004031086900868</v>
       </c>
       <c r="CZ217" s="16">
-        <v>1.4093938168802942</v>
+        <v>1.4118189684480931</v>
       </c>
       <c r="DA217" s="16">
-        <v>1.0330872920252945</v>
+        <v>1.0380030340360229</v>
       </c>
       <c r="DB217" s="8"/>
       <c r="DC217" s="8"/>
@@ -56644,28 +56646,28 @@
         <v>0.57063319521512046</v>
       </c>
       <c r="CT218" s="16">
-        <v>0.73361057964985621</v>
+        <v>0.73361201194607417</v>
       </c>
       <c r="CU218" s="16">
-        <v>1.0918449049174601</v>
+        <v>1.0912742673553175</v>
       </c>
       <c r="CV218" s="16">
-        <v>1.6269415342597224</v>
+        <v>1.6277450361366192</v>
       </c>
       <c r="CW218" s="16">
-        <v>0.56956669494418166</v>
+        <v>0.56336557261162323</v>
       </c>
       <c r="CX218" s="16">
-        <v>0.70909661169880767</v>
+        <v>0.71084333153795332</v>
       </c>
       <c r="CY218" s="16">
-        <v>0.98285542862863018</v>
+        <v>0.98496197177206302</v>
       </c>
       <c r="CZ218" s="16">
-        <v>1.5961331937642975</v>
+        <v>1.6094652272717442</v>
       </c>
       <c r="DA218" s="16">
-        <v>0.54922105962147016</v>
+        <v>0.55532377743785921</v>
       </c>
       <c r="DB218" s="8"/>
       <c r="DC218" s="8"/>
@@ -57035,28 +57037,28 @@
         <v>2.3142753255001822</v>
       </c>
       <c r="CT219" s="16">
-        <v>1.0650276772288658</v>
+        <v>1.0650297565815317</v>
       </c>
       <c r="CU219" s="16">
-        <v>1.9927500956769661</v>
+        <v>1.9917086125400891</v>
       </c>
       <c r="CV219" s="16">
-        <v>3.1038908623317152</v>
+        <v>3.1054237890417715</v>
       </c>
       <c r="CW219" s="16">
-        <v>2.1154449146234917</v>
+        <v>2.0792712431241016</v>
       </c>
       <c r="CX219" s="16">
-        <v>1.0705151822539212</v>
+        <v>1.0716860190287489</v>
       </c>
       <c r="CY219" s="16">
-        <v>1.9552955878879328</v>
+        <v>1.9604455072938038</v>
       </c>
       <c r="CZ219" s="16">
-        <v>3.1223223188777691</v>
+        <v>3.1082132830881744</v>
       </c>
       <c r="DA219" s="16">
-        <v>2.1586266695972571</v>
+        <v>2.1215685849495172</v>
       </c>
       <c r="DB219" s="8"/>
       <c r="DC219" s="8"/>
@@ -57426,28 +57428,28 @@
         <v>0.94162780819608516</v>
       </c>
       <c r="CT220" s="16">
-        <v>1.8435995714402071</v>
+        <v>1.8428210630484456</v>
       </c>
       <c r="CU220" s="16">
-        <v>1.1930052716003523</v>
+        <v>1.1923817639754337</v>
       </c>
       <c r="CV220" s="16">
-        <v>3.2015795358444712</v>
+        <v>3.2306924167420621</v>
       </c>
       <c r="CW220" s="16">
-        <v>0.78178776611724043</v>
+        <v>0.78297136297147152</v>
       </c>
       <c r="CX220" s="16">
-        <v>1.1099925573434977</v>
+        <v>1.1062229164037147</v>
       </c>
       <c r="CY220" s="16">
-        <v>0.65920122860623687</v>
+        <v>0.68024566063772884</v>
       </c>
       <c r="CZ220" s="16">
-        <v>2.3256738073180778</v>
+        <v>2.4289269521712047</v>
       </c>
       <c r="DA220" s="16">
-        <v>0.48974039163778915</v>
+        <v>0.47037753330321092</v>
       </c>
       <c r="DB220" s="8"/>
       <c r="DC220" s="8"/>
@@ -57817,28 +57819,28 @@
         <v>0.84729028754472713</v>
       </c>
       <c r="CT221" s="16">
-        <v>0.52066257091990054</v>
+        <v>0.5206635874579002</v>
       </c>
       <c r="CU221" s="16">
-        <v>1.1106944396055047</v>
+        <v>1.1101139505960791</v>
       </c>
       <c r="CV221" s="16">
-        <v>0.48383042207559041</v>
+        <v>0.48423949617104567</v>
       </c>
       <c r="CW221" s="16">
-        <v>0.80809116802959524</v>
+        <v>0.80470657131078616</v>
       </c>
       <c r="CX221" s="16">
-        <v>0.47133303146621286</v>
+        <v>0.47292408127617491</v>
       </c>
       <c r="CY221" s="16">
-        <v>1.0639680845147916</v>
+        <v>1.079099155328046</v>
       </c>
       <c r="CZ221" s="16">
-        <v>0.48201165631564341</v>
+        <v>0.48953848676921219</v>
       </c>
       <c r="DA221" s="16">
-        <v>0.84477481114205855</v>
+        <v>0.87101476714937909</v>
       </c>
       <c r="DB221" s="8"/>
       <c r="DC221" s="8"/>
@@ -58208,28 +58210,28 @@
         <v>4.123633654853287</v>
       </c>
       <c r="CT222" s="16">
-        <v>10.831855161975662</v>
+        <v>10.830940075481035</v>
       </c>
       <c r="CU222" s="16">
-        <v>10.722842128972204</v>
+        <v>10.717237984588547</v>
       </c>
       <c r="CV222" s="16">
-        <v>13.8011258573354</v>
+        <v>13.807947842723314</v>
       </c>
       <c r="CW222" s="16">
-        <v>3.8561329141166825</v>
+        <v>3.8478140101105023</v>
       </c>
       <c r="CX222" s="16">
-        <v>10.135140746249899</v>
+        <v>10.173671160412304</v>
       </c>
       <c r="CY222" s="16">
-        <v>10.2760437834828</v>
+        <v>10.28156544832636</v>
       </c>
       <c r="CZ222" s="16">
-        <v>13.617440163580161</v>
+        <v>13.642381912841142</v>
       </c>
       <c r="DA222" s="16">
-        <v>4.2074484933341418</v>
+        <v>4.2066916566209231</v>
       </c>
       <c r="DB222" s="8"/>
       <c r="DC222" s="8"/>
@@ -58599,28 +58601,28 @@
         <v>0.88592261756152546</v>
       </c>
       <c r="CT223" s="16">
-        <v>1.5267802309896399</v>
+        <v>1.5267832118647953</v>
       </c>
       <c r="CU223" s="16">
-        <v>1.9214047889446375</v>
+        <v>1.9204005934405743</v>
       </c>
       <c r="CV223" s="16">
-        <v>1.4338664521985809</v>
+        <v>1.4345745995789878</v>
       </c>
       <c r="CW223" s="16">
-        <v>1.0098825340581845</v>
+        <v>0.98799913743785051</v>
       </c>
       <c r="CX223" s="16">
-        <v>1.5991689934415263</v>
+        <v>1.5914429671395585</v>
       </c>
       <c r="CY223" s="16">
-        <v>1.8030354194151048</v>
+        <v>1.8025694503664516</v>
       </c>
       <c r="CZ223" s="16">
-        <v>1.2982642446443555</v>
+        <v>1.2854165068858665</v>
       </c>
       <c r="DA223" s="16">
-        <v>0.92408077345989981</v>
+        <v>0.90437755372875117</v>
       </c>
       <c r="DB223" s="8"/>
       <c r="DC223" s="8"/>
@@ -58990,28 +58992,28 @@
         <v>1.420537998831102</v>
       </c>
       <c r="CT224" s="16">
-        <v>0.9973091875447796</v>
+        <v>0.99731113468433441</v>
       </c>
       <c r="CU224" s="16">
-        <v>0.61344841746488021</v>
+        <v>0.61312780717685689</v>
       </c>
       <c r="CV224" s="16">
-        <v>1.4212674819823792</v>
+        <v>1.4219694070763653</v>
       </c>
       <c r="CW224" s="16">
-        <v>1.6712436038530467</v>
+        <v>1.70697718726321</v>
       </c>
       <c r="CX224" s="16">
-        <v>1.0101811858583836</v>
+        <v>1.0086139289808982</v>
       </c>
       <c r="CY224" s="16">
-        <v>0.55079878061840526</v>
+        <v>0.50576830482571</v>
       </c>
       <c r="CZ224" s="16">
-        <v>1.1709029552649091</v>
+        <v>1.2161598677032881</v>
       </c>
       <c r="DA224" s="16">
-        <v>1.3408266026155322</v>
+        <v>1.3393090265627707</v>
       </c>
       <c r="DB224" s="8"/>
       <c r="DC224" s="8"/>
@@ -59381,28 +59383,28 @@
         <v>1.2610759037861727</v>
       </c>
       <c r="CT225" s="16">
-        <v>1.67042559424883</v>
+        <v>1.6704288555761997</v>
       </c>
       <c r="CU225" s="16">
-        <v>1.0346634752812951</v>
+        <v>1.0341227227984897</v>
       </c>
       <c r="CV225" s="16">
-        <v>1.9102326683007758</v>
+        <v>1.9111760799120525</v>
       </c>
       <c r="CW225" s="16">
-        <v>1.2607594181452704</v>
+        <v>1.2683107009668979</v>
       </c>
       <c r="CX225" s="16">
-        <v>1.6888920898775646</v>
+        <v>1.6858783654326903</v>
       </c>
       <c r="CY225" s="16">
-        <v>1.1081836564163459</v>
+        <v>1.1081330420892159</v>
       </c>
       <c r="CZ225" s="16">
-        <v>2.0435248592748896</v>
+        <v>2.0534462665079465</v>
       </c>
       <c r="DA225" s="16">
-        <v>1.2500456340044459</v>
+        <v>1.2569603478852309</v>
       </c>
       <c r="DB225" s="8"/>
       <c r="DC225" s="8"/>
@@ -59772,28 +59774,28 @@
         <v>0.65706814705963945</v>
       </c>
       <c r="CT226" s="16">
-        <v>0.48274952407792515</v>
+        <v>0.48275046659475462</v>
       </c>
       <c r="CU226" s="16">
-        <v>0.42428972262345332</v>
+        <v>0.42406797349784986</v>
       </c>
       <c r="CV226" s="16">
-        <v>0.4759672727550523</v>
+        <v>0.47499208667736342</v>
       </c>
       <c r="CW226" s="16">
-        <v>0.70819366294334962</v>
+        <v>0.71513667754710031</v>
       </c>
       <c r="CX226" s="16">
-        <v>0.48445913592765055</v>
+        <v>0.48008845574554698</v>
       </c>
       <c r="CY226" s="16">
-        <v>0.39990856568465244</v>
+        <v>0.39393468026226053</v>
       </c>
       <c r="CZ226" s="16">
-        <v>0.46287990217420905</v>
+        <v>0.46063596222208253</v>
       </c>
       <c r="DA226" s="16">
-        <v>0.68167390750775114</v>
+        <v>0.71852711362783184</v>
       </c>
       <c r="DB226" s="8"/>
       <c r="DC226" s="8"/>
@@ -60163,28 +60165,28 @@
         <v>1.0365733646502839</v>
       </c>
       <c r="CT227" s="16">
-        <v>2.3755322893638331</v>
+        <v>2.3755369273366322</v>
       </c>
       <c r="CU227" s="16">
-        <v>2.2036018113150329</v>
+        <v>2.2024501294599661</v>
       </c>
       <c r="CV227" s="16">
-        <v>1.7983036788817439</v>
+        <v>1.799191811829846</v>
       </c>
       <c r="CW227" s="16">
-        <v>1.0260278384015882</v>
+        <v>1.0267940692874458</v>
       </c>
       <c r="CX227" s="16">
-        <v>2.2431385260129861</v>
+        <v>2.2422716613247395</v>
       </c>
       <c r="CY227" s="16">
-        <v>2.2946437766620313</v>
+        <v>2.2885016744840172</v>
       </c>
       <c r="CZ227" s="16">
-        <v>1.9798276467656977</v>
+        <v>1.9758896446502034</v>
       </c>
       <c r="DA227" s="16">
-        <v>1.1567801425926809</v>
+        <v>1.1900574564113471</v>
       </c>
       <c r="DB227" s="8"/>
       <c r="DC227" s="8"/>
@@ -61316,7 +61318,7 @@
     </row>
     <row r="236" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A236" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="238" spans="1:179" x14ac:dyDescent="0.2">
@@ -61326,7 +61328,7 @@
     </row>
     <row r="239" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A239" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="240" spans="1:179" x14ac:dyDescent="0.2">
@@ -62106,28 +62108,28 @@
         <v>51.118081220416357</v>
       </c>
       <c r="CT245" s="16">
-        <v>52.32165609297661</v>
+        <v>52.324577050136782</v>
       </c>
       <c r="CU245" s="16">
-        <v>49.057062949415247</v>
+        <v>49.035391961666413</v>
       </c>
       <c r="CV245" s="16">
-        <v>38.091435455446096</v>
+        <v>38.126261801168333</v>
       </c>
       <c r="CW245" s="16">
-        <v>52.062902220126503</v>
+        <v>52.031928629963964</v>
       </c>
       <c r="CX245" s="16">
-        <v>55.560300186104797</v>
+        <v>55.574808090101669</v>
       </c>
       <c r="CY245" s="16">
-        <v>51.899207283243953</v>
+        <v>51.754839015037248</v>
       </c>
       <c r="CZ245" s="16">
-        <v>41.75044313904634</v>
+        <v>41.574489432008974</v>
       </c>
       <c r="DA245" s="16">
-        <v>54.449861061619231</v>
+        <v>54.394058774004726</v>
       </c>
       <c r="DB245" s="8"/>
       <c r="DC245" s="8"/>
@@ -62497,28 +62499,28 @@
         <v>3.9158793281185691</v>
       </c>
       <c r="CT246" s="16">
-        <v>2.9494346326027645</v>
+        <v>2.9494182581126198</v>
       </c>
       <c r="CU246" s="16">
-        <v>3.6760908864827253</v>
+        <v>3.7208575696866162</v>
       </c>
       <c r="CV246" s="16">
-        <v>6.4869131098733215</v>
+        <v>6.4056249882535026</v>
       </c>
       <c r="CW246" s="16">
-        <v>3.9714428836524931</v>
+        <v>3.9328904759392782</v>
       </c>
       <c r="CX246" s="16">
-        <v>2.8046581263439148</v>
+        <v>2.8047609093559873</v>
       </c>
       <c r="CY246" s="16">
-        <v>3.5907903149263212</v>
+        <v>3.620134682594673</v>
       </c>
       <c r="CZ246" s="16">
-        <v>5.994422444687693</v>
+        <v>5.9197759820029079</v>
       </c>
       <c r="DA246" s="16">
-        <v>3.7787617691763877</v>
+        <v>3.7442666672916758</v>
       </c>
       <c r="DB246" s="8"/>
       <c r="DC246" s="8"/>
@@ -62888,28 +62890,28 @@
         <v>0.21486419243201019</v>
       </c>
       <c r="CT247" s="16">
-        <v>0.22008686435056926</v>
+        <v>0.22008564248582563</v>
       </c>
       <c r="CU247" s="16">
-        <v>0.310902105146596</v>
+        <v>0.3107638387756318</v>
       </c>
       <c r="CV247" s="16">
-        <v>0.7465850016667902</v>
+        <v>0.74672597791782758</v>
       </c>
       <c r="CW247" s="16">
-        <v>0.20658763635255936</v>
+        <v>0.20893864186340719</v>
       </c>
       <c r="CX247" s="16">
-        <v>0.24504727012658439</v>
+        <v>0.24519726892564656</v>
       </c>
       <c r="CY247" s="16">
-        <v>0.32045248282709965</v>
+        <v>0.31964127483847038</v>
       </c>
       <c r="CZ247" s="16">
-        <v>0.81274620658442231</v>
+        <v>0.81817182793495136</v>
       </c>
       <c r="DA247" s="16">
-        <v>0.22054421231144089</v>
+        <v>0.22264968746739427</v>
       </c>
       <c r="DB247" s="8"/>
       <c r="DC247" s="8"/>
@@ -63279,28 +63281,28 @@
         <v>0.99354292357612795</v>
       </c>
       <c r="CT248" s="16">
-        <v>0.81902250684641875</v>
+        <v>0.80711597965485682</v>
       </c>
       <c r="CU248" s="16">
-        <v>1.0502043675933512</v>
+        <v>1.049737313995855</v>
       </c>
       <c r="CV248" s="16">
-        <v>1.1622966504522287</v>
+        <v>1.1687748331840191</v>
       </c>
       <c r="CW248" s="16">
-        <v>0.90387970570914955</v>
+        <v>0.9034280368237857</v>
       </c>
       <c r="CX248" s="16">
-        <v>0.95231856258790981</v>
+        <v>0.92579049274043812</v>
       </c>
       <c r="CY248" s="16">
-        <v>1.0978100520028762</v>
+        <v>1.0975667331878478</v>
       </c>
       <c r="CZ248" s="16">
-        <v>1.2899768815753923</v>
+        <v>1.2967598537581095</v>
       </c>
       <c r="DA248" s="16">
-        <v>0.84739447627534581</v>
+        <v>0.83830434190571257</v>
       </c>
       <c r="DB248" s="8"/>
       <c r="DC248" s="8"/>
@@ -63670,28 +63672,28 @@
         <v>1.0005988668666519</v>
       </c>
       <c r="CT249" s="16">
-        <v>1.2516876157865104</v>
+        <v>1.251680666744039</v>
       </c>
       <c r="CU249" s="16">
-        <v>1.2010965137790315</v>
+        <v>1.2005623544620345</v>
       </c>
       <c r="CV249" s="16">
-        <v>1.9848741253221829</v>
+        <v>1.9855848693387963</v>
       </c>
       <c r="CW249" s="16">
-        <v>0.98730030359735055</v>
+        <v>0.98985806185977987</v>
       </c>
       <c r="CX249" s="16">
-        <v>1.1396206989594111</v>
+        <v>1.1514162317173737</v>
       </c>
       <c r="CY249" s="16">
-        <v>1.1773141067162798</v>
+        <v>1.1771885330096759</v>
       </c>
       <c r="CZ249" s="16">
-        <v>1.8164793964617991</v>
+        <v>1.81075756685946</v>
       </c>
       <c r="DA249" s="16">
-        <v>0.90157809810824474</v>
+        <v>0.91150241288326073</v>
       </c>
       <c r="DB249" s="8"/>
       <c r="DC249" s="8"/>
@@ -64061,28 +64063,28 @@
         <v>0.52134150218670283</v>
       </c>
       <c r="CT250" s="16">
-        <v>0.22386765855822557</v>
+        <v>0.22386641570350069</v>
       </c>
       <c r="CU250" s="16">
-        <v>0.10510409385679499</v>
+        <v>0.10505735129252641</v>
       </c>
       <c r="CV250" s="16">
-        <v>0.23376880724562563</v>
+        <v>0.23381294937275302</v>
       </c>
       <c r="CW250" s="16">
-        <v>0.60638135028659979</v>
+        <v>0.60958581283223112</v>
       </c>
       <c r="CX250" s="16">
-        <v>0.28757367471845907</v>
+        <v>0.28528331151091046</v>
       </c>
       <c r="CY250" s="16">
-        <v>0.15897032463678876</v>
+        <v>0.15926536100549224</v>
       </c>
       <c r="CZ250" s="16">
-        <v>0.24638182099338507</v>
+        <v>0.24484082118050032</v>
       </c>
       <c r="DA250" s="16">
-        <v>0.64561308436536735</v>
+        <v>0.65479210530929843</v>
       </c>
       <c r="DB250" s="8"/>
       <c r="DC250" s="8"/>
@@ -64452,28 +64454,28 @@
         <v>1.4249813014975274</v>
       </c>
       <c r="CT251" s="16">
-        <v>0.66982751584211786</v>
+        <v>0.68158178293169802</v>
       </c>
       <c r="CU251" s="16">
-        <v>1.0901151061236001</v>
+        <v>1.0896303031674222</v>
       </c>
       <c r="CV251" s="16">
-        <v>0.73515628454178061</v>
+        <v>0.73529510272951526</v>
       </c>
       <c r="CW251" s="16">
-        <v>1.3773336801357139</v>
+        <v>1.3810456544126719</v>
       </c>
       <c r="CX251" s="16">
-        <v>0.70055863919678263</v>
+        <v>0.69668399394107294</v>
       </c>
       <c r="CY251" s="16">
-        <v>1.1730501882094009</v>
+        <v>1.183287060946598</v>
       </c>
       <c r="CZ251" s="16">
-        <v>0.74827234124641406</v>
+        <v>0.74565387068335509</v>
       </c>
       <c r="DA251" s="16">
-        <v>1.5384943470626324</v>
+        <v>1.5420009062873614</v>
       </c>
       <c r="DB251" s="8"/>
       <c r="DC251" s="8"/>
@@ -64843,28 +64845,28 @@
         <v>0.53250021079429732</v>
       </c>
       <c r="CT252" s="16">
-        <v>0.61882979920552506</v>
+        <v>0.61882636362423216</v>
       </c>
       <c r="CU252" s="16">
-        <v>0.90703712271398895</v>
+        <v>0.90663373936851976</v>
       </c>
       <c r="CV252" s="16">
-        <v>1.2649904073596301</v>
+        <v>1.2652020261409396</v>
       </c>
       <c r="CW252" s="16">
-        <v>0.53649384592224458</v>
+        <v>0.55120961069566454</v>
       </c>
       <c r="CX252" s="16">
-        <v>0.64731536720836358</v>
+        <v>0.63015579256484244</v>
       </c>
       <c r="CY252" s="16">
-        <v>0.91252025950495186</v>
+        <v>0.87180914905018148</v>
       </c>
       <c r="CZ252" s="16">
-        <v>1.3577387727225916</v>
+        <v>1.3573702153829619</v>
       </c>
       <c r="DA252" s="16">
-        <v>0.55994405002243619</v>
+        <v>0.57687676907076446</v>
       </c>
       <c r="DB252" s="8"/>
       <c r="DC252" s="8"/>
@@ -65234,28 +65236,28 @@
         <v>0.84771099943415118</v>
       </c>
       <c r="CT253" s="16">
-        <v>0.90461770081898452</v>
+        <v>0.90461267861796224</v>
       </c>
       <c r="CU253" s="16">
-        <v>1.3206093741700546</v>
+        <v>1.3200220643300598</v>
       </c>
       <c r="CV253" s="16">
-        <v>0.45852346688201501</v>
+        <v>0.45861004901161762</v>
       </c>
       <c r="CW253" s="16">
-        <v>0.77757331884606573</v>
+        <v>0.77700888172504234</v>
       </c>
       <c r="CX253" s="16">
-        <v>1.0900666843403055</v>
+        <v>1.0484814448626987</v>
       </c>
       <c r="CY253" s="16">
-        <v>1.2928897325172997</v>
+        <v>1.2622403843517145</v>
       </c>
       <c r="CZ253" s="16">
-        <v>0.41932706949976278</v>
+        <v>0.4212582690951262</v>
       </c>
       <c r="DA253" s="16">
-        <v>0.68435382212084139</v>
+        <v>0.65543741324507121</v>
       </c>
       <c r="DB253" s="8"/>
       <c r="DC253" s="8"/>
@@ -65625,28 +65627,28 @@
         <v>5.5060541989283482</v>
       </c>
       <c r="CT254" s="16">
-        <v>1.0208257012247124</v>
+        <v>1.0208200338672468</v>
       </c>
       <c r="CU254" s="16">
-        <v>6.0265448080010851</v>
+        <v>6.0238646444825319</v>
       </c>
       <c r="CV254" s="16">
-        <v>3.0625569117541862</v>
+        <v>3.063135208654129</v>
       </c>
       <c r="CW254" s="16">
-        <v>4.8903846703891771</v>
+        <v>4.959774235455491</v>
       </c>
       <c r="CX254" s="16">
-        <v>0.96690534284837104</v>
+        <v>0.96774375864399498</v>
       </c>
       <c r="CY254" s="16">
-        <v>5.1508684124267949</v>
+        <v>5.1802822187213993</v>
       </c>
       <c r="CZ254" s="16">
-        <v>2.7849431028499629</v>
+        <v>2.7921322863368481</v>
       </c>
       <c r="DA254" s="16">
-        <v>4.4900361519264704</v>
+        <v>4.5443190043326753</v>
       </c>
       <c r="DB254" s="8"/>
       <c r="DC254" s="8"/>
@@ -66016,28 +66018,28 @@
         <v>14.042282231075887</v>
       </c>
       <c r="CT255" s="16">
-        <v>10.966947363246902</v>
+        <v>10.966886477621728</v>
       </c>
       <c r="CU255" s="16">
-        <v>9.7832106495509183</v>
+        <v>9.7767849160200662</v>
       </c>
       <c r="CV255" s="16">
-        <v>14.413513271715928</v>
+        <v>14.416234948498596</v>
       </c>
       <c r="CW255" s="16">
-        <v>14.228368960750931</v>
+        <v>14.219147435786352</v>
       </c>
       <c r="CX255" s="16">
-        <v>9.7271780124133898</v>
+        <v>9.7504813454799368</v>
       </c>
       <c r="CY255" s="16">
-        <v>8.9151647998211772</v>
+        <v>9.0619523908994335</v>
       </c>
       <c r="CZ255" s="16">
-        <v>12.388940885376556</v>
+        <v>12.445877116606665</v>
       </c>
       <c r="DA255" s="16">
-        <v>12.510385500182888</v>
+        <v>12.487502531993004</v>
       </c>
       <c r="DB255" s="8"/>
       <c r="DC255" s="8"/>
@@ -66407,28 +66409,28 @@
         <v>1.6332570331067386</v>
       </c>
       <c r="CT256" s="16">
-        <v>1.0193636103322175</v>
+        <v>1.0193579510918984</v>
       </c>
       <c r="CU256" s="16">
-        <v>1.268216198536088</v>
+        <v>1.2676521893239698</v>
       </c>
       <c r="CV256" s="16">
-        <v>2.2751622176850592</v>
+        <v>2.275591832315992</v>
       </c>
       <c r="CW256" s="16">
-        <v>1.5800697073997612</v>
+        <v>1.5881456145616253</v>
       </c>
       <c r="CX256" s="16">
-        <v>0.92568206235887041</v>
+        <v>0.93945960448083499</v>
       </c>
       <c r="CY256" s="16">
-        <v>1.2839385039309188</v>
+        <v>1.2847421921254352</v>
       </c>
       <c r="CZ256" s="16">
-        <v>2.2914867743313327</v>
+        <v>2.2941690740738414</v>
       </c>
       <c r="DA256" s="16">
-        <v>1.7020806813333338</v>
+        <v>1.7076590855501914</v>
       </c>
       <c r="DB256" s="8"/>
       <c r="DC256" s="8"/>
@@ -66798,28 +66800,28 @@
         <v>0.54170814290398384</v>
       </c>
       <c r="CT257" s="16">
-        <v>0.65701030712339237</v>
+        <v>0.65700665957389937</v>
       </c>
       <c r="CU257" s="16">
-        <v>1.0320691290596604</v>
+        <v>1.0316101406813347</v>
       </c>
       <c r="CV257" s="16">
-        <v>1.4300098887725858</v>
+        <v>1.4302799148682288</v>
       </c>
       <c r="CW257" s="16">
-        <v>0.5555359841270735</v>
+        <v>0.54937078673984363</v>
       </c>
       <c r="CX257" s="16">
-        <v>0.64325582624679345</v>
+        <v>0.64480530523923607</v>
       </c>
       <c r="CY257" s="16">
-        <v>0.98006940428513323</v>
+        <v>0.98169231209847918</v>
       </c>
       <c r="CZ257" s="16">
-        <v>1.4082340960601136</v>
+        <v>1.4192105898161704</v>
       </c>
       <c r="DA257" s="16">
-        <v>0.53007768410147871</v>
+        <v>0.5352799369981015</v>
       </c>
       <c r="DB257" s="8"/>
       <c r="DC257" s="8"/>
@@ -67189,28 +67191,28 @@
         <v>2.4175163770886319</v>
       </c>
       <c r="CT258" s="16">
-        <v>0.9832121533342435</v>
+        <v>0.98320669479736422</v>
       </c>
       <c r="CU258" s="16">
-        <v>2.0677631053365326</v>
+        <v>2.0668435165146635</v>
       </c>
       <c r="CV258" s="16">
-        <v>3.2684409488186796</v>
+        <v>3.2690581224166926</v>
       </c>
       <c r="CW258" s="16">
-        <v>2.2252803027002441</v>
+        <v>2.1867621999330034</v>
       </c>
       <c r="CX258" s="16">
-        <v>0.9964710921086648</v>
+        <v>0.99750626339822102</v>
       </c>
       <c r="CY258" s="16">
-        <v>2.0466818834289335</v>
+        <v>2.0511437946304127</v>
       </c>
       <c r="CZ258" s="16">
-        <v>3.2326788131240582</v>
+        <v>3.2162920081318402</v>
       </c>
       <c r="DA258" s="16">
-        <v>2.3153252455536508</v>
+        <v>2.2743473558526595</v>
       </c>
       <c r="DB258" s="8"/>
       <c r="DC258" s="8"/>
@@ -67580,28 +67582,28 @@
         <v>1.4050216551691643</v>
       </c>
       <c r="CT259" s="16">
-        <v>3.0392906137300426</v>
+        <v>3.0379843957964887</v>
       </c>
       <c r="CU259" s="16">
-        <v>2.0868692319323103</v>
+        <v>2.0859411461059056</v>
       </c>
       <c r="CV259" s="16">
-        <v>3.5641442710214646</v>
+        <v>3.595457489611066</v>
       </c>
       <c r="CW259" s="16">
-        <v>1.3032967077154436</v>
+        <v>1.3050242442545872</v>
       </c>
       <c r="CX259" s="16">
-        <v>1.8523379862531311</v>
+        <v>1.8459342557646956</v>
       </c>
       <c r="CY259" s="16">
-        <v>1.2279995771959022</v>
+        <v>1.2666062941686298</v>
       </c>
       <c r="CZ259" s="16">
-        <v>2.6203420056403948</v>
+        <v>2.7351974542767348</v>
       </c>
       <c r="DA259" s="16">
-        <v>0.79550880454614925</v>
+        <v>0.77749730697920261</v>
       </c>
       <c r="DB259" s="8"/>
       <c r="DC259" s="8"/>
@@ -67971,28 +67973,28 @@
         <v>0.89013002576867239</v>
       </c>
       <c r="CT260" s="16">
-        <v>0.46940923500310178</v>
+        <v>0.46940662896572516</v>
       </c>
       <c r="CU260" s="16">
-        <v>1.3253839691410354</v>
+        <v>1.3247945359126538</v>
       </c>
       <c r="CV260" s="16">
-        <v>0.52518466335966851</v>
+        <v>0.52546844108970348</v>
       </c>
       <c r="CW260" s="16">
-        <v>0.84761719745297759</v>
+        <v>0.84429630507444275</v>
       </c>
       <c r="CX260" s="16">
-        <v>0.44482652634705672</v>
+        <v>0.44630105500562944</v>
       </c>
       <c r="CY260" s="16">
-        <v>1.2902636505055467</v>
+        <v>1.3077339852282484</v>
       </c>
       <c r="CZ260" s="16">
-        <v>0.52892693906740096</v>
+        <v>0.53684461010635043</v>
       </c>
       <c r="DA260" s="16">
-        <v>0.90160509098601571</v>
+        <v>0.92954504387869652</v>
       </c>
       <c r="DB260" s="8"/>
       <c r="DC260" s="8"/>
@@ -68362,28 +68364,28 @@
         <v>6.6294908932976275</v>
       </c>
       <c r="CT261" s="16">
-        <v>14.148801807550932</v>
+        <v>14.14750033662671</v>
       </c>
       <c r="CU261" s="16">
-        <v>10.462515550460795</v>
+        <v>10.457862593686389</v>
       </c>
       <c r="CV261" s="16">
-        <v>12.128444755626091</v>
+        <v>12.130740207154442</v>
       </c>
       <c r="CW261" s="16">
-        <v>6.13547314085561</v>
+        <v>6.1209352489981956</v>
       </c>
       <c r="CX261" s="16">
-        <v>13.130832436787626</v>
+        <v>13.180048134769514</v>
       </c>
       <c r="CY261" s="16">
-        <v>10.139728613770698</v>
+        <v>10.140613832845288</v>
       </c>
       <c r="CZ261" s="16">
-        <v>11.961404465054461</v>
+        <v>11.976688099823006</v>
       </c>
       <c r="DA261" s="16">
-        <v>6.7120538338095157</v>
+        <v>6.7072237383376283</v>
       </c>
       <c r="DB261" s="8"/>
       <c r="DC261" s="8"/>
@@ -68753,28 +68755,28 @@
         <v>1.0490521814095208</v>
       </c>
       <c r="CT262" s="16">
-        <v>1.3719658746929528</v>
+        <v>1.3719582578970266</v>
       </c>
       <c r="CU262" s="16">
-        <v>2.4237517920948655</v>
+        <v>2.4226738857093397</v>
       </c>
       <c r="CV262" s="16">
-        <v>1.6016660894715156</v>
+        <v>1.6019685290868353</v>
       </c>
       <c r="CW262" s="16">
-        <v>1.1841486817991262</v>
+        <v>1.158242747437449</v>
       </c>
       <c r="CX262" s="16">
-        <v>1.5019299615480894</v>
+        <v>1.4945939670294068</v>
       </c>
       <c r="CY262" s="16">
-        <v>2.292511961756535</v>
+        <v>2.2908886119695056</v>
       </c>
       <c r="CZ262" s="16">
-        <v>1.4519672940482502</v>
+        <v>1.4368037282713864</v>
       </c>
       <c r="DA262" s="16">
-        <v>1.0865540112263645</v>
+        <v>1.0628124923769069</v>
       </c>
       <c r="DB262" s="8"/>
       <c r="DC262" s="8"/>
@@ -69144,28 +69146,28 @@
         <v>1.7119128773506183</v>
       </c>
       <c r="CT263" s="16">
-        <v>1.2287102339379563</v>
+        <v>1.2287034124599028</v>
       </c>
       <c r="CU263" s="16">
-        <v>0.60334126848327529</v>
+        <v>0.60307294669881273</v>
       </c>
       <c r="CV263" s="16">
-        <v>1.7075087445125128</v>
+        <v>1.7078311701986406</v>
       </c>
       <c r="CW263" s="16">
-        <v>1.9824895658350545</v>
+        <v>2.0265095146110812</v>
       </c>
       <c r="CX263" s="16">
-        <v>1.300619202320568</v>
+        <v>1.2984219068489096</v>
       </c>
       <c r="CY263" s="16">
-        <v>0.56800304464839135</v>
+        <v>0.52192559148007844</v>
       </c>
       <c r="CZ263" s="16">
-        <v>1.5438471638443503</v>
+        <v>1.6033412715017532</v>
       </c>
       <c r="DA263" s="16">
-        <v>1.5835151768852824</v>
+        <v>1.5999364917345584</v>
       </c>
       <c r="DB263" s="8"/>
       <c r="DC263" s="8"/>
@@ -69535,28 +69537,28 @@
         <v>1.6925598997690177</v>
       </c>
       <c r="CT264" s="16">
-        <v>1.9437018000465129</v>
+        <v>1.943691009122172</v>
       </c>
       <c r="CU264" s="16">
-        <v>1.2728359598954542</v>
+        <v>1.2722698961535428</v>
       </c>
       <c r="CV264" s="16">
-        <v>2.3293229661053876</v>
+        <v>2.3297628078092578</v>
       </c>
       <c r="CW264" s="16">
-        <v>1.6999375146785285</v>
+        <v>1.7103722064705909</v>
       </c>
       <c r="CX264" s="16">
-        <v>2.0022991983923726</v>
+        <v>1.9985353807607731</v>
       </c>
       <c r="CY264" s="16">
-        <v>1.41150644197237</v>
+        <v>1.4108004566419796</v>
       </c>
       <c r="CZ264" s="16">
-        <v>2.5756992992178511</v>
+        <v>2.5871959591720235</v>
       </c>
       <c r="DA264" s="16">
-        <v>1.6870652245895617</v>
+        <v>1.69612044281114</v>
       </c>
       <c r="DB264" s="8"/>
       <c r="DC264" s="8"/>
@@ -69926,28 +69928,28 @@
         <v>0.7221600306708581</v>
       </c>
       <c r="CT265" s="16">
-        <v>0.57345396282163952</v>
+        <v>0.57345077915512965</v>
       </c>
       <c r="CU265" s="16">
-        <v>0.41135773106100476</v>
+        <v>0.41117478942214053</v>
       </c>
       <c r="CV265" s="16">
-        <v>0.55248821249969049</v>
+        <v>0.55119166549877463</v>
       </c>
       <c r="CW265" s="16">
-        <v>0.77184002083078118</v>
+        <v>0.77924129425308453</v>
       </c>
       <c r="CX265" s="16">
-        <v>0.58595071274706068</v>
+        <v>0.58041264692178207</v>
       </c>
       <c r="CY265" s="16">
-        <v>0.39813341753063575</v>
+        <v>0.39164352348628567</v>
       </c>
       <c r="CZ265" s="16">
-        <v>0.52420725529759971</v>
+        <v>0.52127586362190859</v>
       </c>
       <c r="DA265" s="16">
-        <v>0.74056238124702389</v>
+        <v>0.78221413072576862</v>
       </c>
       <c r="DB265" s="8"/>
       <c r="DC265" s="8"/>
@@ -70317,28 +70319,28 @@
         <v>1.1893539081385216</v>
       </c>
       <c r="CT266" s="16">
-        <v>2.5982769499676825</v>
+        <v>2.598262525013205</v>
       </c>
       <c r="CU266" s="16">
-        <v>2.5179180871655764</v>
+        <v>2.5167983025435543</v>
       </c>
       <c r="CV266" s="16">
-        <v>1.9770137498675615</v>
+        <v>1.9773870656803403</v>
       </c>
       <c r="CW266" s="16">
-        <v>1.1656626008366109</v>
+        <v>1.1662843603084576</v>
       </c>
       <c r="CX266" s="16">
-        <v>2.4942524300415125</v>
+        <v>2.4931788399364381</v>
       </c>
       <c r="CY266" s="16">
-        <v>2.6721255441419829</v>
+        <v>2.6640026016829084</v>
       </c>
       <c r="CZ266" s="16">
-        <v>2.2515338332698773</v>
+        <v>2.2458940993551137</v>
       </c>
       <c r="DA266" s="16">
-        <v>1.3186852925503172</v>
+        <v>1.3556533609642119</v>
       </c>
       <c r="DB266" s="8"/>
       <c r="DC266" s="8"/>

--- a/Data/National Accounts/PSA-10MFG_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-10MFG_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2659EF9-FEF4-401D-A1EE-479576852F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0C883D-115D-46FF-A3F5-C4071AC207BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="MFG" sheetId="10" r:id="rId1"/>
@@ -353,7 +353,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">MFG!$A$1:$DA$271</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">MFG!$A$1:$DB$271</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -527,7 +527,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="74">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -742,23 +742,27 @@
     <t>Table 11.7 Gross Value Added in Manufacturing, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>Q1 2000 to Q1 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>As of May 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -805,6 +809,18 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Microsoft Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Microsoft Sans Serif"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -849,7 +865,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -901,6 +917,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma 2" xfId="3" xr:uid="{0662CF8E-D90D-4FC2-9E33-010BFB9B5552}"/>
@@ -1243,12 +1261,12 @@
   <sheetPr transitionEvaluation="1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:FW272"/>
+  <dimension ref="A1:FW273"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.140625" style="3" customWidth="1"/>
-    <col min="2" max="105" width="13" style="3" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="3"/>
+    <col min="2" max="106" width="13" style="3" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1439,6 +1457,9 @@
       <c r="CY9" s="21"/>
       <c r="CZ9" s="21"/>
       <c r="DA9" s="21"/>
+      <c r="DB9" s="21">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1755,6 +1776,9 @@
       </c>
       <c r="DA10" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2076,7 +2100,9 @@
       <c r="DA12" s="18">
         <v>843036.00159373693</v>
       </c>
-      <c r="DB12" s="8"/>
+      <c r="DB12" s="25">
+        <v>734116.88930629659</v>
+      </c>
       <c r="DC12" s="8"/>
       <c r="DD12" s="8"/>
       <c r="DE12" s="8"/>
@@ -2467,7 +2493,9 @@
       <c r="DA13" s="18">
         <v>58143.645237766279</v>
       </c>
-      <c r="DB13" s="8"/>
+      <c r="DB13" s="25">
+        <v>36777.229767239587</v>
+      </c>
       <c r="DC13" s="8"/>
       <c r="DD13" s="8"/>
       <c r="DE13" s="8"/>
@@ -2858,7 +2886,9 @@
       <c r="DA14" s="18">
         <v>3830.2896871736684</v>
       </c>
-      <c r="DB14" s="8"/>
+      <c r="DB14" s="25">
+        <v>2912.0358306131538</v>
+      </c>
       <c r="DC14" s="8"/>
       <c r="DD14" s="8"/>
       <c r="DE14" s="8"/>
@@ -3249,7 +3279,9 @@
       <c r="DA15" s="18">
         <v>9878.8490943499964</v>
       </c>
-      <c r="DB15" s="8"/>
+      <c r="DB15" s="25">
+        <v>10693.663870245775</v>
+      </c>
       <c r="DC15" s="8"/>
       <c r="DD15" s="8"/>
       <c r="DE15" s="8"/>
@@ -3640,7 +3672,9 @@
       <c r="DA16" s="18">
         <v>8000.6917150929221</v>
       </c>
-      <c r="DB16" s="8"/>
+      <c r="DB16" s="25">
+        <v>13487.781100079934</v>
+      </c>
       <c r="DC16" s="8"/>
       <c r="DD16" s="8"/>
       <c r="DE16" s="8"/>
@@ -4031,7 +4065,9 @@
       <c r="DA17" s="18">
         <v>7279.3142165950012</v>
       </c>
-      <c r="DB17" s="8"/>
+      <c r="DB17" s="25">
+        <v>2835.9380110995571</v>
+      </c>
       <c r="DC17" s="8"/>
       <c r="DD17" s="8"/>
       <c r="DE17" s="8"/>
@@ -4422,7 +4458,9 @@
       <c r="DA18" s="18">
         <v>13349.035817676442</v>
       </c>
-      <c r="DB18" s="8"/>
+      <c r="DB18" s="25">
+        <v>6130.7905009889</v>
+      </c>
       <c r="DC18" s="8"/>
       <c r="DD18" s="8"/>
       <c r="DE18" s="8"/>
@@ -4813,7 +4851,9 @@
       <c r="DA19" s="18">
         <v>6865.8499506906701</v>
       </c>
-      <c r="DB19" s="8"/>
+      <c r="DB19" s="25">
+        <v>6062.2502697910786</v>
+      </c>
       <c r="DC19" s="8"/>
       <c r="DD19" s="8"/>
       <c r="DE19" s="8"/>
@@ -5204,7 +5244,9 @@
       <c r="DA20" s="18">
         <v>9245.4713167641967</v>
       </c>
-      <c r="DB20" s="8"/>
+      <c r="DB20" s="25">
+        <v>9445.6725881404673</v>
+      </c>
       <c r="DC20" s="8"/>
       <c r="DD20" s="8"/>
       <c r="DE20" s="8"/>
@@ -5595,7 +5637,9 @@
       <c r="DA21" s="18">
         <v>62419.04300002128</v>
       </c>
-      <c r="DB21" s="8"/>
+      <c r="DB21" s="25">
+        <v>13367.970357167935</v>
+      </c>
       <c r="DC21" s="8"/>
       <c r="DD21" s="8"/>
       <c r="DE21" s="8"/>
@@ -5986,7 +6030,9 @@
       <c r="DA22" s="18">
         <v>168464.79429278313</v>
       </c>
-      <c r="DB22" s="8"/>
+      <c r="DB22" s="25">
+        <v>76710.231493798841</v>
+      </c>
       <c r="DC22" s="8"/>
       <c r="DD22" s="8"/>
       <c r="DE22" s="8"/>
@@ -6377,7 +6423,9 @@
       <c r="DA23" s="18">
         <v>14482.457635219325</v>
       </c>
-      <c r="DB23" s="8"/>
+      <c r="DB23" s="25">
+        <v>7785.5909631948307</v>
+      </c>
       <c r="DC23" s="8"/>
       <c r="DD23" s="8"/>
       <c r="DE23" s="8"/>
@@ -6768,7 +6816,9 @@
       <c r="DA24" s="18">
         <v>7748.0053688307962</v>
       </c>
-      <c r="DB24" s="8"/>
+      <c r="DB24" s="25">
+        <v>7605.2357446655224</v>
+      </c>
       <c r="DC24" s="8"/>
       <c r="DD24" s="8"/>
       <c r="DE24" s="8"/>
@@ -7159,7 +7209,9 @@
       <c r="DA25" s="18">
         <v>29600.614010033132</v>
       </c>
-      <c r="DB25" s="8"/>
+      <c r="DB25" s="25">
+        <v>12595.58537045218</v>
+      </c>
       <c r="DC25" s="8"/>
       <c r="DD25" s="8"/>
       <c r="DE25" s="8"/>
@@ -7550,7 +7602,9 @@
       <c r="DA26" s="18">
         <v>6562.8157869009738</v>
       </c>
-      <c r="DB26" s="8"/>
+      <c r="DB26" s="25">
+        <v>13644.440295085937</v>
+      </c>
       <c r="DC26" s="8"/>
       <c r="DD26" s="8"/>
       <c r="DE26" s="8"/>
@@ -7941,7 +7995,9 @@
       <c r="DA27" s="18">
         <v>12152.598837638405</v>
       </c>
-      <c r="DB27" s="8"/>
+      <c r="DB27" s="25">
+        <v>6012.6311679919454</v>
+      </c>
       <c r="DC27" s="8"/>
       <c r="DD27" s="8"/>
       <c r="DE27" s="8"/>
@@ -8332,7 +8388,9 @@
       <c r="DA28" s="18">
         <v>58692.731816551561</v>
       </c>
-      <c r="DB28" s="8"/>
+      <c r="DB28" s="25">
+        <v>134820.60500808683</v>
+      </c>
       <c r="DC28" s="8"/>
       <c r="DD28" s="8"/>
       <c r="DE28" s="8"/>
@@ -8723,7 +8781,9 @@
       <c r="DA29" s="18">
         <v>12618.084127551199</v>
       </c>
-      <c r="DB29" s="8"/>
+      <c r="DB29" s="25">
+        <v>16735.964069887654</v>
+      </c>
       <c r="DC29" s="8"/>
       <c r="DD29" s="8"/>
       <c r="DE29" s="8"/>
@@ -9114,7 +9174,9 @@
       <c r="DA30" s="18">
         <v>18686.348306944376</v>
       </c>
-      <c r="DB30" s="8"/>
+      <c r="DB30" s="25">
+        <v>10712.777744200954</v>
+      </c>
       <c r="DC30" s="8"/>
       <c r="DD30" s="8"/>
       <c r="DE30" s="8"/>
@@ -9505,7 +9567,9 @@
       <c r="DA31" s="18">
         <v>17537.400557122703</v>
       </c>
-      <c r="DB31" s="8"/>
+      <c r="DB31" s="25">
+        <v>19434.423989880277</v>
+      </c>
       <c r="DC31" s="8"/>
       <c r="DD31" s="8"/>
       <c r="DE31" s="8"/>
@@ -9896,7 +9960,9 @@
       <c r="DA32" s="18">
         <v>10025.05594074243</v>
       </c>
-      <c r="DB32" s="8"/>
+      <c r="DB32" s="25">
+        <v>5416.5066899102567</v>
+      </c>
       <c r="DC32" s="8"/>
       <c r="DD32" s="8"/>
       <c r="DE32" s="8"/>
@@ -10287,7 +10353,9 @@
       <c r="DA33" s="18">
         <v>16603.955991284784</v>
       </c>
-      <c r="DB33" s="8"/>
+      <c r="DB33" s="25">
+        <v>28026.864613343947</v>
+      </c>
       <c r="DC33" s="8"/>
       <c r="DD33" s="8"/>
       <c r="DE33" s="8"/>
@@ -10858,7 +10926,9 @@
       <c r="DA35" s="19">
         <v>1395223.0543014701</v>
       </c>
-      <c r="DB35" s="8"/>
+      <c r="DB35" s="26">
+        <v>1175331.0787521622</v>
+      </c>
       <c r="DC35" s="8"/>
       <c r="DD35" s="8"/>
       <c r="DE35" s="8"/>
@@ -11039,6 +11109,7 @@
       <c r="CY36" s="10"/>
       <c r="CZ36" s="10"/>
       <c r="DA36" s="10"/>
+      <c r="DB36" s="10"/>
     </row>
     <row r="37" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
@@ -11593,6 +11664,9 @@
       <c r="CY48" s="21"/>
       <c r="CZ48" s="21"/>
       <c r="DA48" s="21"/>
+      <c r="DB48" s="21">
+        <v>2026</v>
+      </c>
     </row>
     <row r="49" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
@@ -11909,6 +11983,9 @@
       </c>
       <c r="DA49" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB49" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -12230,7 +12307,9 @@
       <c r="DA51" s="18">
         <v>629127.06621503388</v>
       </c>
-      <c r="DB51" s="8"/>
+      <c r="DB51" s="25">
+        <v>592865.62454089522</v>
+      </c>
       <c r="DC51" s="8"/>
       <c r="DD51" s="8"/>
       <c r="DE51" s="8"/>
@@ -12621,7 +12700,9 @@
       <c r="DA52" s="18">
         <v>43306.558778910614</v>
       </c>
-      <c r="DB52" s="8"/>
+      <c r="DB52" s="25">
+        <v>31315.372210053894</v>
+      </c>
       <c r="DC52" s="8"/>
       <c r="DD52" s="8"/>
       <c r="DE52" s="8"/>
@@ -13012,7 +13093,9 @@
       <c r="DA53" s="18">
         <v>2575.1883170188926</v>
       </c>
-      <c r="DB53" s="8"/>
+      <c r="DB53" s="25">
+        <v>2800.588351920866</v>
+      </c>
       <c r="DC53" s="8"/>
       <c r="DD53" s="8"/>
       <c r="DE53" s="8"/>
@@ -13403,7 +13486,9 @@
       <c r="DA54" s="18">
         <v>9695.9109708965771</v>
       </c>
-      <c r="DB54" s="8"/>
+      <c r="DB54" s="25">
+        <v>11770.974072405057</v>
+      </c>
       <c r="DC54" s="8"/>
       <c r="DD54" s="8"/>
       <c r="DE54" s="8"/>
@@ -13794,7 +13879,9 @@
       <c r="DA55" s="18">
         <v>10542.527102964159</v>
       </c>
-      <c r="DB55" s="8"/>
+      <c r="DB55" s="25">
+        <v>14455.424585020897</v>
+      </c>
       <c r="DC55" s="8"/>
       <c r="DD55" s="8"/>
       <c r="DE55" s="8"/>
@@ -14185,7 +14272,9 @@
       <c r="DA56" s="18">
         <v>7573.3902834049368</v>
       </c>
-      <c r="DB56" s="8"/>
+      <c r="DB56" s="25">
+        <v>3329.0114480924503</v>
+      </c>
       <c r="DC56" s="8"/>
       <c r="DD56" s="8"/>
       <c r="DE56" s="8"/>
@@ -14576,7 +14665,9 @@
       <c r="DA57" s="18">
         <v>17834.935067156912</v>
       </c>
-      <c r="DB57" s="8"/>
+      <c r="DB57" s="25">
+        <v>8390.6400746806685</v>
+      </c>
       <c r="DC57" s="8"/>
       <c r="DD57" s="8"/>
       <c r="DE57" s="8"/>
@@ -14967,7 +15058,9 @@
       <c r="DA58" s="18">
         <v>6672.2137945430113</v>
       </c>
-      <c r="DB58" s="8"/>
+      <c r="DB58" s="25">
+        <v>6552.2422703734519</v>
+      </c>
       <c r="DC58" s="8"/>
       <c r="DD58" s="8"/>
       <c r="DE58" s="8"/>
@@ -15358,7 +15451,9 @@
       <c r="DA59" s="18">
         <v>7580.853978844998</v>
       </c>
-      <c r="DB59" s="8"/>
+      <c r="DB59" s="25">
+        <v>9856.8296163057457</v>
+      </c>
       <c r="DC59" s="8"/>
       <c r="DD59" s="8"/>
       <c r="DE59" s="8"/>
@@ -15749,7 +15844,9 @@
       <c r="DA60" s="18">
         <v>52560.043276405631</v>
       </c>
-      <c r="DB60" s="8"/>
+      <c r="DB60" s="25">
+        <v>7976.5718642711436</v>
+      </c>
       <c r="DC60" s="8"/>
       <c r="DD60" s="8"/>
       <c r="DE60" s="8"/>
@@ -16140,7 +16237,9 @@
       <c r="DA61" s="18">
         <v>144431.68995618518</v>
       </c>
-      <c r="DB61" s="8"/>
+      <c r="DB61" s="25">
+        <v>99771.208822483721</v>
+      </c>
       <c r="DC61" s="8"/>
       <c r="DD61" s="8"/>
       <c r="DE61" s="8"/>
@@ -16531,7 +16630,9 @@
       <c r="DA62" s="18">
         <v>19750.95396082248</v>
       </c>
-      <c r="DB62" s="8"/>
+      <c r="DB62" s="25">
+        <v>9975.5671724332387</v>
+      </c>
       <c r="DC62" s="8"/>
       <c r="DD62" s="8"/>
       <c r="DE62" s="8"/>
@@ -16922,7 +17023,9 @@
       <c r="DA63" s="18">
         <v>6191.1007186748702</v>
       </c>
-      <c r="DB63" s="8"/>
+      <c r="DB63" s="25">
+        <v>6549.0212912793831</v>
+      </c>
       <c r="DC63" s="8"/>
       <c r="DD63" s="8"/>
       <c r="DE63" s="8"/>
@@ -17313,7 +17416,9 @@
       <c r="DA64" s="18">
         <v>26305.326570432677</v>
       </c>
-      <c r="DB64" s="8"/>
+      <c r="DB64" s="25">
+        <v>11082.136847150443</v>
+      </c>
       <c r="DC64" s="8"/>
       <c r="DD64" s="8"/>
       <c r="DE64" s="8"/>
@@ -17704,7 +17809,9 @@
       <c r="DA65" s="18">
         <v>8992.610787920843</v>
       </c>
-      <c r="DB65" s="8"/>
+      <c r="DB65" s="25">
+        <v>20672.889994893281</v>
+      </c>
       <c r="DC65" s="8"/>
       <c r="DD65" s="8"/>
       <c r="DE65" s="8"/>
@@ -18095,7 +18202,9 @@
       <c r="DA66" s="18">
         <v>10751.209958423067</v>
       </c>
-      <c r="DB66" s="8"/>
+      <c r="DB66" s="25">
+        <v>5232.4658827454568</v>
+      </c>
       <c r="DC66" s="8"/>
       <c r="DD66" s="8"/>
       <c r="DE66" s="8"/>
@@ -18486,7 +18595,9 @@
       <c r="DA67" s="18">
         <v>77576.413455007772</v>
       </c>
-      <c r="DB67" s="8"/>
+      <c r="DB67" s="25">
+        <v>157834.99214555701</v>
+      </c>
       <c r="DC67" s="8"/>
       <c r="DD67" s="8"/>
       <c r="DE67" s="8"/>
@@ -18877,7 +18988,9 @@
       <c r="DA68" s="18">
         <v>12292.594454917213</v>
       </c>
-      <c r="DB68" s="8"/>
+      <c r="DB68" s="25">
+        <v>14954.935641446209</v>
+      </c>
       <c r="DC68" s="8"/>
       <c r="DD68" s="8"/>
       <c r="DE68" s="8"/>
@@ -19268,7 +19381,9 @@
       <c r="DA69" s="18">
         <v>18505.023781317446</v>
       </c>
-      <c r="DB69" s="8"/>
+      <c r="DB69" s="25">
+        <v>12646.634074472633</v>
+      </c>
       <c r="DC69" s="8"/>
       <c r="DD69" s="8"/>
       <c r="DE69" s="8"/>
@@ -19659,7 +19774,9 @@
       <c r="DA70" s="18">
         <v>19617.496877123624</v>
       </c>
-      <c r="DB70" s="8"/>
+      <c r="DB70" s="25">
+        <v>21353.364175182636</v>
+      </c>
       <c r="DC70" s="8"/>
       <c r="DD70" s="8"/>
       <c r="DE70" s="8"/>
@@ -20050,7 +20167,9 @@
       <c r="DA71" s="18">
         <v>9047.1660381157162</v>
       </c>
-      <c r="DB71" s="8"/>
+      <c r="DB71" s="25">
+        <v>6054.9187096154201</v>
+      </c>
       <c r="DC71" s="8"/>
       <c r="DD71" s="8"/>
       <c r="DE71" s="8"/>
@@ -20441,7 +20560,9 @@
       <c r="DA72" s="18">
         <v>15679.620918370609</v>
       </c>
-      <c r="DB72" s="8"/>
+      <c r="DB72" s="25">
+        <v>29236.411924553096</v>
+      </c>
       <c r="DC72" s="8"/>
       <c r="DD72" s="8"/>
       <c r="DE72" s="8"/>
@@ -21012,7 +21133,9 @@
       <c r="DA74" s="19">
         <v>1156609.895262491</v>
       </c>
-      <c r="DB74" s="8"/>
+      <c r="DB74" s="26">
+        <v>1084677.8257158317</v>
+      </c>
       <c r="DC74" s="8"/>
       <c r="DD74" s="8"/>
       <c r="DE74" s="8"/>
@@ -21193,6 +21316,7 @@
       <c r="CY75" s="10"/>
       <c r="CZ75" s="10"/>
       <c r="DA75" s="10"/>
+      <c r="DB75" s="10"/>
     </row>
     <row r="76" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
@@ -21304,7 +21428,7 @@
       <c r="CY77" s="7"/>
       <c r="CZ77" s="7"/>
       <c r="DA77" s="7"/>
-      <c r="DB77" s="8"/>
+      <c r="DB77" s="7"/>
       <c r="DC77" s="8"/>
       <c r="DD77" s="8"/>
       <c r="DE77" s="8"/>
@@ -21484,7 +21608,7 @@
       <c r="CY78" s="7"/>
       <c r="CZ78" s="7"/>
       <c r="DA78" s="7"/>
-      <c r="DB78" s="8"/>
+      <c r="DB78" s="7"/>
       <c r="DC78" s="8"/>
       <c r="DD78" s="8"/>
       <c r="DE78" s="8"/>
@@ -21567,6 +21691,7 @@
       <c r="CY79" s="4"/>
       <c r="CZ79" s="4"/>
       <c r="DA79" s="4"/>
+      <c r="DB79" s="4"/>
     </row>
     <row r="80" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
@@ -21576,6 +21701,7 @@
       <c r="CY80" s="4"/>
       <c r="CZ80" s="4"/>
       <c r="DA80" s="4"/>
+      <c r="DB80" s="4"/>
     </row>
     <row r="81" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
@@ -21585,12 +21711,14 @@
       <c r="CY81" s="4"/>
       <c r="CZ81" s="4"/>
       <c r="DA81" s="4"/>
+      <c r="DB81" s="4"/>
     </row>
     <row r="82" spans="1:175" x14ac:dyDescent="0.2">
       <c r="CX82" s="4"/>
       <c r="CY82" s="4"/>
       <c r="CZ82" s="4"/>
       <c r="DA82" s="4"/>
+      <c r="DB82" s="4"/>
     </row>
     <row r="83" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
@@ -21600,6 +21728,7 @@
       <c r="CY83" s="4"/>
       <c r="CZ83" s="4"/>
       <c r="DA83" s="4"/>
+      <c r="DB83" s="4"/>
     </row>
     <row r="84" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
@@ -21609,6 +21738,7 @@
       <c r="CY84" s="4"/>
       <c r="CZ84" s="4"/>
       <c r="DA84" s="4"/>
+      <c r="DB84" s="4"/>
     </row>
     <row r="85" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
@@ -21618,12 +21748,14 @@
       <c r="CY85" s="4"/>
       <c r="CZ85" s="4"/>
       <c r="DA85" s="4"/>
+      <c r="DB85" s="4"/>
     </row>
     <row r="86" spans="1:175" x14ac:dyDescent="0.2">
       <c r="CX86" s="4"/>
       <c r="CY86" s="4"/>
       <c r="CZ86" s="4"/>
       <c r="DA86" s="4"/>
+      <c r="DB86" s="4"/>
     </row>
     <row r="87" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="17"/>
@@ -21777,10 +21909,13 @@
       <c r="CU87" s="21"/>
       <c r="CV87" s="21"/>
       <c r="CW87" s="21"/>
-      <c r="CX87" s="22"/>
+      <c r="CX87" s="21" t="s">
+        <v>73</v>
+      </c>
       <c r="CY87" s="22"/>
       <c r="CZ87" s="22"/>
       <c r="DA87" s="22"/>
+      <c r="DB87" s="22"/>
     </row>
     <row r="88" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
@@ -22086,17 +22221,20 @@
       <c r="CW88" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX88" s="23"/>
+      <c r="CX88" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY88" s="23"/>
       <c r="CZ88" s="23"/>
       <c r="DA88" s="23"/>
+      <c r="DB88" s="23"/>
     </row>
     <row r="89" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6"/>
-      <c r="CX89" s="4"/>
       <c r="CY89" s="4"/>
       <c r="CZ89" s="4"/>
       <c r="DA89" s="4"/>
+      <c r="DB89" s="4"/>
     </row>
     <row r="90" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
@@ -22402,11 +22540,13 @@
       <c r="CW90" s="16">
         <v>6.526155231812524</v>
       </c>
-      <c r="CX90" s="20"/>
+      <c r="CX90" s="16">
+        <v>1.2101426619543645</v>
+      </c>
       <c r="CY90" s="20"/>
       <c r="CZ90" s="20"/>
       <c r="DA90" s="20"/>
-      <c r="DB90" s="8"/>
+      <c r="DB90" s="20"/>
       <c r="DC90" s="8"/>
       <c r="DD90" s="8"/>
       <c r="DE90" s="8"/>
@@ -22781,11 +22921,13 @@
       <c r="CW91" s="16">
         <v>-4.4279519440357404</v>
       </c>
-      <c r="CX91" s="20"/>
+      <c r="CX91" s="16">
+        <v>5.1010676245855819</v>
+      </c>
       <c r="CY91" s="20"/>
       <c r="CZ91" s="20"/>
       <c r="DA91" s="20"/>
-      <c r="DB91" s="8"/>
+      <c r="DB91" s="20"/>
       <c r="DC91" s="8"/>
       <c r="DD91" s="8"/>
       <c r="DE91" s="8"/>
@@ -23160,11 +23302,13 @@
       <c r="CW92" s="16">
         <v>11.343262491359795</v>
       </c>
-      <c r="CX92" s="20"/>
+      <c r="CX92" s="16">
+        <v>7.3918314957037552</v>
+      </c>
       <c r="CY92" s="20"/>
       <c r="CZ92" s="20"/>
       <c r="DA92" s="20"/>
-      <c r="DB92" s="8"/>
+      <c r="DB92" s="20"/>
       <c r="DC92" s="8"/>
       <c r="DD92" s="8"/>
       <c r="DE92" s="8"/>
@@ -23539,11 +23683,13 @@
       <c r="CW93" s="16">
         <v>-8.3408759391205507</v>
       </c>
-      <c r="CX93" s="20"/>
+      <c r="CX93" s="16">
+        <v>18.748634393338918</v>
+      </c>
       <c r="CY93" s="20"/>
       <c r="CZ93" s="20"/>
       <c r="DA93" s="20"/>
-      <c r="DB93" s="8"/>
+      <c r="DB93" s="20"/>
       <c r="DC93" s="8"/>
       <c r="DD93" s="8"/>
       <c r="DE93" s="8"/>
@@ -23918,11 +24064,13 @@
       <c r="CW94" s="16">
         <v>-5.0686588074935912</v>
       </c>
-      <c r="CX94" s="20"/>
+      <c r="CX94" s="16">
+        <v>16.506628039598652</v>
+      </c>
       <c r="CY94" s="20"/>
       <c r="CZ94" s="20"/>
       <c r="DA94" s="20"/>
-      <c r="DB94" s="8"/>
+      <c r="DB94" s="20"/>
       <c r="DC94" s="8"/>
       <c r="DD94" s="8"/>
       <c r="DE94" s="8"/>
@@ -24297,11 +24445,13 @@
       <c r="CW95" s="16">
         <v>9.9820267604848283</v>
       </c>
-      <c r="CX95" s="20"/>
+      <c r="CX95" s="16">
+        <v>7.6653112441018862</v>
+      </c>
       <c r="CY95" s="20"/>
       <c r="CZ95" s="20"/>
       <c r="DA95" s="20"/>
-      <c r="DB95" s="8"/>
+      <c r="DB95" s="20"/>
       <c r="DC95" s="8"/>
       <c r="DD95" s="8"/>
       <c r="DE95" s="8"/>
@@ -24676,11 +24826,13 @@
       <c r="CW96" s="16">
         <v>13.045945657276107</v>
       </c>
-      <c r="CX96" s="20"/>
+      <c r="CX96" s="16">
+        <v>12.378403677734269</v>
+      </c>
       <c r="CY96" s="20"/>
       <c r="CZ96" s="20"/>
       <c r="DA96" s="20"/>
-      <c r="DB96" s="8"/>
+      <c r="DB96" s="20"/>
       <c r="DC96" s="8"/>
       <c r="DD96" s="8"/>
       <c r="DE96" s="8"/>
@@ -25055,11 +25207,13 @@
       <c r="CW97" s="16">
         <v>4.8822318874847497</v>
       </c>
-      <c r="CX97" s="20"/>
+      <c r="CX97" s="16">
+        <v>-4.7468206419928265</v>
+      </c>
       <c r="CY97" s="20"/>
       <c r="CZ97" s="20"/>
       <c r="DA97" s="20"/>
-      <c r="DB97" s="8"/>
+      <c r="DB97" s="20"/>
       <c r="DC97" s="8"/>
       <c r="DD97" s="8"/>
       <c r="DE97" s="8"/>
@@ -25434,11 +25588,13 @@
       <c r="CW98" s="16">
         <v>-12.567821209987883</v>
       </c>
-      <c r="CX98" s="20"/>
+      <c r="CX98" s="16">
+        <v>-12.543896406199835</v>
+      </c>
       <c r="CY98" s="20"/>
       <c r="CZ98" s="20"/>
       <c r="DA98" s="20"/>
-      <c r="DB98" s="8"/>
+      <c r="DB98" s="20"/>
       <c r="DC98" s="8"/>
       <c r="DD98" s="8"/>
       <c r="DE98" s="8"/>
@@ -25813,11 +25969,13 @@
       <c r="CW99" s="16">
         <v>-3.7533444720508413</v>
       </c>
-      <c r="CX99" s="20"/>
+      <c r="CX99" s="16">
+        <v>-19.146453259209935</v>
+      </c>
       <c r="CY99" s="20"/>
       <c r="CZ99" s="20"/>
       <c r="DA99" s="20"/>
-      <c r="DB99" s="8"/>
+      <c r="DB99" s="20"/>
       <c r="DC99" s="8"/>
       <c r="DD99" s="8"/>
       <c r="DE99" s="8"/>
@@ -26192,11 +26350,13 @@
       <c r="CW100" s="16">
         <v>-10.670507425064983</v>
       </c>
-      <c r="CX100" s="20"/>
+      <c r="CX100" s="16">
+        <v>-5.0896885892715744</v>
+      </c>
       <c r="CY100" s="20"/>
       <c r="CZ100" s="20"/>
       <c r="DA100" s="20"/>
-      <c r="DB100" s="8"/>
+      <c r="DB100" s="20"/>
       <c r="DC100" s="8"/>
       <c r="DD100" s="8"/>
       <c r="DE100" s="8"/>
@@ -26571,11 +26731,13 @@
       <c r="CW101" s="16">
         <v>3.5736879222241384</v>
       </c>
-      <c r="CX101" s="20"/>
+      <c r="CX101" s="16">
+        <v>-1.3183230893037603</v>
+      </c>
       <c r="CY101" s="20"/>
       <c r="CZ101" s="20"/>
       <c r="DA101" s="20"/>
-      <c r="DB101" s="8"/>
+      <c r="DB101" s="20"/>
       <c r="DC101" s="8"/>
       <c r="DD101" s="8"/>
       <c r="DE101" s="8"/>
@@ -26950,11 +27112,13 @@
       <c r="CW102" s="16">
         <v>0.67068652832919895</v>
       </c>
-      <c r="CX102" s="20"/>
+      <c r="CX102" s="16">
+        <v>-7.0046863553614855</v>
+      </c>
       <c r="CY102" s="20"/>
       <c r="CZ102" s="20"/>
       <c r="DA102" s="20"/>
-      <c r="DB102" s="8"/>
+      <c r="DB102" s="20"/>
       <c r="DC102" s="8"/>
       <c r="DD102" s="8"/>
       <c r="DE102" s="8"/>
@@ -27329,11 +27493,13 @@
       <c r="CW103" s="16">
         <v>4.2060642924826652</v>
       </c>
-      <c r="CX103" s="20"/>
+      <c r="CX103" s="16">
+        <v>2.1581611922945569</v>
+      </c>
       <c r="CY103" s="20"/>
       <c r="CZ103" s="20"/>
       <c r="DA103" s="20"/>
-      <c r="DB103" s="8"/>
+      <c r="DB103" s="20"/>
       <c r="DC103" s="8"/>
       <c r="DD103" s="8"/>
       <c r="DE103" s="8"/>
@@ -27708,11 +27874,13 @@
       <c r="CW104" s="16">
         <v>-38.645311294591842</v>
       </c>
-      <c r="CX104" s="20"/>
+      <c r="CX104" s="16">
+        <v>7.2100134965853897</v>
+      </c>
       <c r="CY104" s="20"/>
       <c r="CZ104" s="20"/>
       <c r="DA104" s="20"/>
-      <c r="DB104" s="8"/>
+      <c r="DB104" s="20"/>
       <c r="DC104" s="8"/>
       <c r="DD104" s="8"/>
       <c r="DE104" s="8"/>
@@ -28087,11 +28255,13 @@
       <c r="CW105" s="16">
         <v>10.543964285724144</v>
       </c>
-      <c r="CX105" s="20"/>
+      <c r="CX105" s="16">
+        <v>10.508430628742872</v>
+      </c>
       <c r="CY105" s="20"/>
       <c r="CZ105" s="20"/>
       <c r="DA105" s="20"/>
-      <c r="DB105" s="8"/>
+      <c r="DB105" s="20"/>
       <c r="DC105" s="8"/>
       <c r="DD105" s="8"/>
       <c r="DE105" s="8"/>
@@ -28466,11 +28636,13 @@
       <c r="CW106" s="16">
         <v>11.65384241492022</v>
       </c>
-      <c r="CX106" s="20"/>
+      <c r="CX106" s="16">
+        <v>15.1863063613565</v>
+      </c>
       <c r="CY106" s="20"/>
       <c r="CZ106" s="20"/>
       <c r="DA106" s="20"/>
-      <c r="DB106" s="8"/>
+      <c r="DB106" s="20"/>
       <c r="DC106" s="8"/>
       <c r="DD106" s="8"/>
       <c r="DE106" s="8"/>
@@ -28845,11 +29017,13 @@
       <c r="CW107" s="16">
         <v>-6.5153569438053864</v>
       </c>
-      <c r="CX107" s="20"/>
+      <c r="CX107" s="16">
+        <v>-8.5924787919653625</v>
+      </c>
       <c r="CY107" s="20"/>
       <c r="CZ107" s="20"/>
       <c r="DA107" s="20"/>
-      <c r="DB107" s="8"/>
+      <c r="DB107" s="20"/>
       <c r="DC107" s="8"/>
       <c r="DD107" s="8"/>
       <c r="DE107" s="8"/>
@@ -29224,11 +29398,13 @@
       <c r="CW108" s="16">
         <v>-19.86907730907329</v>
       </c>
-      <c r="CX108" s="20"/>
+      <c r="CX108" s="16">
+        <v>-7.6792317704039021</v>
+      </c>
       <c r="CY108" s="20"/>
       <c r="CZ108" s="20"/>
       <c r="DA108" s="20"/>
-      <c r="DB108" s="8"/>
+      <c r="DB108" s="20"/>
       <c r="DC108" s="8"/>
       <c r="DD108" s="8"/>
       <c r="DE108" s="8"/>
@@ -29603,11 +29779,13 @@
       <c r="CW109" s="16">
         <v>1.2145586573577845</v>
       </c>
-      <c r="CX109" s="20"/>
+      <c r="CX109" s="16">
+        <v>0.19999784725411018</v>
+      </c>
       <c r="CY109" s="20"/>
       <c r="CZ109" s="20"/>
       <c r="DA109" s="20"/>
-      <c r="DB109" s="8"/>
+      <c r="DB109" s="20"/>
       <c r="DC109" s="8"/>
       <c r="DD109" s="8"/>
       <c r="DE109" s="8"/>
@@ -29982,11 +30160,13 @@
       <c r="CW110" s="16">
         <v>2.612713713973875</v>
       </c>
-      <c r="CX110" s="20"/>
+      <c r="CX110" s="16">
+        <v>-1.93358541956556</v>
+      </c>
       <c r="CY110" s="20"/>
       <c r="CZ110" s="20"/>
       <c r="DA110" s="20"/>
-      <c r="DB110" s="8"/>
+      <c r="DB110" s="20"/>
       <c r="DC110" s="8"/>
       <c r="DD110" s="8"/>
       <c r="DE110" s="8"/>
@@ -30361,11 +30541,13 @@
       <c r="CW111" s="16">
         <v>18.367273213253725</v>
       </c>
-      <c r="CX111" s="20"/>
+      <c r="CX111" s="16">
+        <v>8.6447047074317425</v>
+      </c>
       <c r="CY111" s="20"/>
       <c r="CZ111" s="20"/>
       <c r="DA111" s="20"/>
-      <c r="DB111" s="8"/>
+      <c r="DB111" s="20"/>
       <c r="DC111" s="8"/>
       <c r="DD111" s="8"/>
       <c r="DE111" s="8"/>
@@ -30537,11 +30719,11 @@
       <c r="CU112" s="8"/>
       <c r="CV112" s="8"/>
       <c r="CW112" s="8"/>
-      <c r="CX112" s="7"/>
+      <c r="CX112" s="8"/>
       <c r="CY112" s="7"/>
       <c r="CZ112" s="7"/>
       <c r="DA112" s="7"/>
-      <c r="DB112" s="8"/>
+      <c r="DB112" s="7"/>
       <c r="DC112" s="8"/>
       <c r="DD112" s="8"/>
       <c r="DE112" s="8"/>
@@ -30916,11 +31098,13 @@
       <c r="CW113" s="16">
         <v>2.128526213851444</v>
       </c>
-      <c r="CX113" s="20"/>
+      <c r="CX113" s="16">
+        <v>2.1603792704449063</v>
+      </c>
       <c r="CY113" s="20"/>
       <c r="CZ113" s="20"/>
       <c r="DA113" s="20"/>
-      <c r="DB113" s="8"/>
+      <c r="DB113" s="20"/>
       <c r="DC113" s="8"/>
       <c r="DD113" s="8"/>
       <c r="DE113" s="8"/>
@@ -31093,19 +31277,20 @@
       <c r="CU114" s="10"/>
       <c r="CV114" s="10"/>
       <c r="CW114" s="10"/>
-      <c r="CX114" s="24"/>
+      <c r="CX114" s="10"/>
       <c r="CY114" s="24"/>
       <c r="CZ114" s="24"/>
       <c r="DA114" s="24"/>
+      <c r="DB114" s="24"/>
     </row>
     <row r="115" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A115" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CX115" s="4"/>
       <c r="CY115" s="4"/>
       <c r="CZ115" s="4"/>
       <c r="DA115" s="4"/>
+      <c r="DB115" s="4"/>
     </row>
     <row r="116" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="8"/>
@@ -31208,11 +31393,11 @@
       <c r="CU116" s="8"/>
       <c r="CV116" s="8"/>
       <c r="CW116" s="8"/>
-      <c r="CX116" s="7"/>
+      <c r="CX116" s="8"/>
       <c r="CY116" s="7"/>
       <c r="CZ116" s="7"/>
       <c r="DA116" s="7"/>
-      <c r="DB116" s="8"/>
+      <c r="DB116" s="7"/>
       <c r="DC116" s="8"/>
       <c r="DD116" s="8"/>
       <c r="DE116" s="8"/>
@@ -31384,11 +31569,11 @@
       <c r="CU117" s="8"/>
       <c r="CV117" s="8"/>
       <c r="CW117" s="8"/>
-      <c r="CX117" s="7"/>
+      <c r="CX117" s="8"/>
       <c r="CY117" s="7"/>
       <c r="CZ117" s="7"/>
       <c r="DA117" s="7"/>
-      <c r="DB117" s="8"/>
+      <c r="DB117" s="7"/>
       <c r="DC117" s="8"/>
       <c r="DD117" s="8"/>
       <c r="DE117" s="8"/>
@@ -31463,67 +31648,67 @@
       <c r="A118" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="CX118" s="4"/>
       <c r="CY118" s="4"/>
       <c r="CZ118" s="4"/>
       <c r="DA118" s="4"/>
+      <c r="DB118" s="4"/>
     </row>
     <row r="119" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="CX119" s="4"/>
       <c r="CY119" s="4"/>
       <c r="CZ119" s="4"/>
       <c r="DA119" s="4"/>
+      <c r="DB119" s="4"/>
     </row>
     <row r="120" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="CX120" s="4"/>
       <c r="CY120" s="4"/>
       <c r="CZ120" s="4"/>
       <c r="DA120" s="4"/>
+      <c r="DB120" s="4"/>
     </row>
     <row r="121" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX121" s="4"/>
       <c r="CY121" s="4"/>
       <c r="CZ121" s="4"/>
       <c r="DA121" s="4"/>
+      <c r="DB121" s="4"/>
     </row>
     <row r="122" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="CX122" s="4"/>
       <c r="CY122" s="4"/>
       <c r="CZ122" s="4"/>
       <c r="DA122" s="4"/>
+      <c r="DB122" s="4"/>
     </row>
     <row r="123" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="CX123" s="4"/>
       <c r="CY123" s="4"/>
       <c r="CZ123" s="4"/>
       <c r="DA123" s="4"/>
+      <c r="DB123" s="4"/>
     </row>
     <row r="124" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="CX124" s="4"/>
       <c r="CY124" s="4"/>
       <c r="CZ124" s="4"/>
       <c r="DA124" s="4"/>
+      <c r="DB124" s="4"/>
     </row>
     <row r="125" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX125" s="4"/>
       <c r="CY125" s="4"/>
       <c r="CZ125" s="4"/>
       <c r="DA125" s="4"/>
+      <c r="DB125" s="4"/>
     </row>
     <row r="126" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="17"/>
@@ -31677,10 +31862,13 @@
       <c r="CU126" s="21"/>
       <c r="CV126" s="21"/>
       <c r="CW126" s="21"/>
-      <c r="CX126" s="22"/>
+      <c r="CX126" s="21" t="s">
+        <v>73</v>
+      </c>
       <c r="CY126" s="22"/>
       <c r="CZ126" s="22"/>
       <c r="DA126" s="22"/>
+      <c r="DB126" s="22"/>
     </row>
     <row r="127" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
@@ -31986,17 +32174,20 @@
       <c r="CW127" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX127" s="23"/>
+      <c r="CX127" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY127" s="23"/>
       <c r="CZ127" s="23"/>
       <c r="DA127" s="23"/>
+      <c r="DB127" s="23"/>
     </row>
     <row r="128" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="6"/>
-      <c r="CX128" s="4"/>
       <c r="CY128" s="4"/>
       <c r="CZ128" s="4"/>
       <c r="DA128" s="4"/>
+      <c r="DB128" s="4"/>
     </row>
     <row r="129" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
@@ -32302,11 +32493,13 @@
       <c r="CW129" s="16">
         <v>6.3910046320353615</v>
       </c>
-      <c r="CX129" s="20"/>
+      <c r="CX129" s="16">
+        <v>-1.1627576512698141</v>
+      </c>
       <c r="CY129" s="20"/>
       <c r="CZ129" s="20"/>
       <c r="DA129" s="20"/>
-      <c r="DB129" s="8"/>
+      <c r="DB129" s="20"/>
       <c r="DC129" s="8"/>
       <c r="DD129" s="8"/>
       <c r="DE129" s="8"/>
@@ -32681,11 +32874,13 @@
       <c r="CW130" s="16">
         <v>-3.1101492295421735</v>
       </c>
-      <c r="CX130" s="20"/>
+      <c r="CX130" s="16">
+        <v>3.4437017841743653</v>
+      </c>
       <c r="CY130" s="20"/>
       <c r="CZ130" s="20"/>
       <c r="DA130" s="20"/>
-      <c r="DB130" s="8"/>
+      <c r="DB130" s="20"/>
       <c r="DC130" s="8"/>
       <c r="DD130" s="8"/>
       <c r="DE130" s="8"/>
@@ -33060,11 +33255,13 @@
       <c r="CW131" s="16">
         <v>8.4492842348747814</v>
       </c>
-      <c r="CX131" s="20"/>
+      <c r="CX131" s="16">
+        <v>5.8220014116035799</v>
+      </c>
       <c r="CY131" s="20"/>
       <c r="CZ131" s="20"/>
       <c r="DA131" s="20"/>
-      <c r="DB131" s="8"/>
+      <c r="DB131" s="20"/>
       <c r="DC131" s="8"/>
       <c r="DD131" s="8"/>
       <c r="DE131" s="8"/>
@@ -33439,11 +33636,13 @@
       <c r="CW132" s="16">
         <v>-5.5653187306029821</v>
       </c>
-      <c r="CX132" s="20"/>
+      <c r="CX132" s="16">
+        <v>17.799109664809649</v>
+      </c>
       <c r="CY132" s="20"/>
       <c r="CZ132" s="20"/>
       <c r="DA132" s="20"/>
-      <c r="DB132" s="8"/>
+      <c r="DB132" s="20"/>
       <c r="DC132" s="8"/>
       <c r="DD132" s="8"/>
       <c r="DE132" s="8"/>
@@ -33818,11 +34017,13 @@
       <c r="CW133" s="16">
         <v>-6.2851820923144004</v>
       </c>
-      <c r="CX133" s="20"/>
+      <c r="CX133" s="16">
+        <v>16.316366258265276</v>
+      </c>
       <c r="CY133" s="20"/>
       <c r="CZ133" s="20"/>
       <c r="DA133" s="20"/>
-      <c r="DB133" s="8"/>
+      <c r="DB133" s="20"/>
       <c r="DC133" s="8"/>
       <c r="DD133" s="8"/>
       <c r="DE133" s="8"/>
@@ -34197,11 +34398,13 @@
       <c r="CW134" s="16">
         <v>9.3180688810494701</v>
       </c>
-      <c r="CX134" s="20"/>
+      <c r="CX134" s="16">
+        <v>8.1138275847741852</v>
+      </c>
       <c r="CY134" s="20"/>
       <c r="CZ134" s="20"/>
       <c r="DA134" s="20"/>
-      <c r="DB134" s="8"/>
+      <c r="DB134" s="20"/>
       <c r="DC134" s="8"/>
       <c r="DD134" s="8"/>
       <c r="DE134" s="8"/>
@@ -34576,11 +34779,13 @@
       <c r="CW135" s="16">
         <v>13.631819526107051</v>
       </c>
-      <c r="CX135" s="20"/>
+      <c r="CX135" s="16">
+        <v>11.583911325243974</v>
+      </c>
       <c r="CY135" s="20"/>
       <c r="CZ135" s="20"/>
       <c r="DA135" s="20"/>
-      <c r="DB135" s="8"/>
+      <c r="DB135" s="20"/>
       <c r="DC135" s="8"/>
       <c r="DD135" s="8"/>
       <c r="DE135" s="8"/>
@@ -34955,11 +35160,13 @@
       <c r="CW136" s="16">
         <v>6.5098165291881003</v>
       </c>
-      <c r="CX136" s="20"/>
+      <c r="CX136" s="16">
+        <v>-3.6649480562358008</v>
+      </c>
       <c r="CY136" s="20"/>
       <c r="CZ136" s="20"/>
       <c r="DA136" s="20"/>
-      <c r="DB136" s="8"/>
+      <c r="DB136" s="20"/>
       <c r="DC136" s="8"/>
       <c r="DD136" s="8"/>
       <c r="DE136" s="8"/>
@@ -35334,11 +35541,13 @@
       <c r="CW137" s="16">
         <v>-14.152310254201467</v>
       </c>
-      <c r="CX137" s="20"/>
+      <c r="CX137" s="16">
+        <v>-12.899866258741895</v>
+      </c>
       <c r="CY137" s="20"/>
       <c r="CZ137" s="20"/>
       <c r="DA137" s="20"/>
-      <c r="DB137" s="8"/>
+      <c r="DB137" s="20"/>
       <c r="DC137" s="8"/>
       <c r="DD137" s="8"/>
       <c r="DE137" s="8"/>
@@ -35713,11 +35922,13 @@
       <c r="CW138" s="16">
         <v>-6.7539873147461691</v>
       </c>
-      <c r="CX138" s="20"/>
+      <c r="CX138" s="16">
+        <v>-23.634319751473186</v>
+      </c>
       <c r="CY138" s="20"/>
       <c r="CZ138" s="20"/>
       <c r="DA138" s="20"/>
-      <c r="DB138" s="8"/>
+      <c r="DB138" s="20"/>
       <c r="DC138" s="8"/>
       <c r="DD138" s="8"/>
       <c r="DE138" s="8"/>
@@ -36092,11 +36303,13 @@
       <c r="CW139" s="16">
         <v>-10.623076904660138</v>
       </c>
-      <c r="CX139" s="20"/>
+      <c r="CX139" s="16">
+        <v>-5.1971267718641911</v>
+      </c>
       <c r="CY139" s="20"/>
       <c r="CZ139" s="20"/>
       <c r="DA139" s="20"/>
-      <c r="DB139" s="8"/>
+      <c r="DB139" s="20"/>
       <c r="DC139" s="8"/>
       <c r="DD139" s="8"/>
       <c r="DE139" s="8"/>
@@ -36471,11 +36684,13 @@
       <c r="CW140" s="16">
         <v>9.4294511471349409</v>
       </c>
-      <c r="CX140" s="20"/>
+      <c r="CX140" s="16">
+        <v>-1.6211349253856326</v>
+      </c>
       <c r="CY140" s="20"/>
       <c r="CZ140" s="20"/>
       <c r="DA140" s="20"/>
-      <c r="DB140" s="8"/>
+      <c r="DB140" s="20"/>
       <c r="DC140" s="8"/>
       <c r="DD140" s="8"/>
       <c r="DE140" s="8"/>
@@ -36850,11 +37065,13 @@
       <c r="CW141" s="16">
         <v>-0.83948547016981934</v>
       </c>
-      <c r="CX141" s="20"/>
+      <c r="CX141" s="16">
+        <v>-5.8998920166408482</v>
+      </c>
       <c r="CY141" s="20"/>
       <c r="CZ141" s="20"/>
       <c r="DA141" s="20"/>
-      <c r="DB141" s="8"/>
+      <c r="DB141" s="20"/>
       <c r="DC141" s="8"/>
       <c r="DD141" s="8"/>
       <c r="DE141" s="8"/>
@@ -37229,11 +37446,13 @@
       <c r="CW142" s="16">
         <v>5.8470122432635776</v>
       </c>
-      <c r="CX142" s="20"/>
+      <c r="CX142" s="16">
+        <v>2.93194964637091</v>
+      </c>
       <c r="CY142" s="20"/>
       <c r="CZ142" s="20"/>
       <c r="DA142" s="20"/>
-      <c r="DB142" s="8"/>
+      <c r="DB142" s="20"/>
       <c r="DC142" s="8"/>
       <c r="DD142" s="8"/>
       <c r="DE142" s="8"/>
@@ -37608,11 +37827,13 @@
       <c r="CW143" s="16">
         <v>-39.367750512562218</v>
       </c>
-      <c r="CX143" s="20"/>
+      <c r="CX143" s="16">
+        <v>3.7593603771671553</v>
+      </c>
       <c r="CY143" s="20"/>
       <c r="CZ143" s="20"/>
       <c r="DA143" s="20"/>
-      <c r="DB143" s="8"/>
+      <c r="DB143" s="20"/>
       <c r="DC143" s="8"/>
       <c r="DD143" s="8"/>
       <c r="DE143" s="8"/>
@@ -37987,11 +38208,13 @@
       <c r="CW144" s="16">
         <v>12.046660871218535</v>
       </c>
-      <c r="CX144" s="20"/>
+      <c r="CX144" s="16">
+        <v>8.6227549246004997</v>
+      </c>
       <c r="CY144" s="20"/>
       <c r="CZ144" s="20"/>
       <c r="DA144" s="20"/>
-      <c r="DB144" s="8"/>
+      <c r="DB144" s="20"/>
       <c r="DC144" s="8"/>
       <c r="DD144" s="8"/>
       <c r="DE144" s="8"/>
@@ -38366,11 +38589,13 @@
       <c r="CW145" s="16">
         <v>11.518874060795994</v>
       </c>
-      <c r="CX145" s="20"/>
+      <c r="CX145" s="16">
+        <v>10.950335066988728</v>
+      </c>
       <c r="CY145" s="20"/>
       <c r="CZ145" s="20"/>
       <c r="DA145" s="20"/>
-      <c r="DB145" s="8"/>
+      <c r="DB145" s="20"/>
       <c r="DC145" s="8"/>
       <c r="DD145" s="8"/>
       <c r="DE145" s="8"/>
@@ -38745,11 +38970,13 @@
       <c r="CW146" s="16">
         <v>-6.6142892322296518</v>
       </c>
-      <c r="CX146" s="20"/>
+      <c r="CX146" s="16">
+        <v>-7.294896098226971</v>
+      </c>
       <c r="CY146" s="20"/>
       <c r="CZ146" s="20"/>
       <c r="DA146" s="20"/>
-      <c r="DB146" s="8"/>
+      <c r="DB146" s="20"/>
       <c r="DC146" s="8"/>
       <c r="DD146" s="8"/>
       <c r="DE146" s="8"/>
@@ -39124,11 +39351,13 @@
       <c r="CW147" s="16">
         <v>-19.651557174121066</v>
       </c>
-      <c r="CX147" s="20"/>
+      <c r="CX147" s="16">
+        <v>-9.7595110409526313</v>
+      </c>
       <c r="CY147" s="20"/>
       <c r="CZ147" s="20"/>
       <c r="DA147" s="20"/>
-      <c r="DB147" s="8"/>
+      <c r="DB147" s="20"/>
       <c r="DC147" s="8"/>
       <c r="DD147" s="8"/>
       <c r="DE147" s="8"/>
@@ -39503,11 +39732,13 @@
       <c r="CW148" s="16">
         <v>0.92283124303132524</v>
       </c>
-      <c r="CX148" s="20"/>
+      <c r="CX148" s="16">
+        <v>-1.008754797264757</v>
+      </c>
       <c r="CY148" s="20"/>
       <c r="CZ148" s="20"/>
       <c r="DA148" s="20"/>
-      <c r="DB148" s="8"/>
+      <c r="DB148" s="20"/>
       <c r="DC148" s="8"/>
       <c r="DD148" s="8"/>
       <c r="DE148" s="8"/>
@@ -39882,11 +40113,13 @@
       <c r="CW149" s="16">
         <v>2.1591017776340919</v>
       </c>
-      <c r="CX149" s="20"/>
+      <c r="CX149" s="16">
+        <v>-3.3473487712047785</v>
+      </c>
       <c r="CY149" s="20"/>
       <c r="CZ149" s="20"/>
       <c r="DA149" s="20"/>
-      <c r="DB149" s="8"/>
+      <c r="DB149" s="20"/>
       <c r="DC149" s="8"/>
       <c r="DD149" s="8"/>
       <c r="DE149" s="8"/>
@@ -40261,11 +40494,13 @@
       <c r="CW150" s="16">
         <v>18.295322022049064</v>
       </c>
-      <c r="CX150" s="20"/>
+      <c r="CX150" s="16">
+        <v>8.6458048192394159</v>
+      </c>
       <c r="CY150" s="20"/>
       <c r="CZ150" s="20"/>
       <c r="DA150" s="20"/>
-      <c r="DB150" s="8"/>
+      <c r="DB150" s="20"/>
       <c r="DC150" s="8"/>
       <c r="DD150" s="8"/>
       <c r="DE150" s="8"/>
@@ -40437,11 +40672,11 @@
       <c r="CU151" s="8"/>
       <c r="CV151" s="8"/>
       <c r="CW151" s="8"/>
-      <c r="CX151" s="7"/>
+      <c r="CX151" s="8"/>
       <c r="CY151" s="7"/>
       <c r="CZ151" s="7"/>
       <c r="DA151" s="7"/>
-      <c r="DB151" s="8"/>
+      <c r="DB151" s="7"/>
       <c r="DC151" s="8"/>
       <c r="DD151" s="8"/>
       <c r="DE151" s="8"/>
@@ -40816,11 +41051,13 @@
       <c r="CW152" s="16">
         <v>1.7708419752965767</v>
       </c>
-      <c r="CX152" s="20"/>
+      <c r="CX152" s="16">
+        <v>0.49468271573576317</v>
+      </c>
       <c r="CY152" s="20"/>
       <c r="CZ152" s="20"/>
       <c r="DA152" s="20"/>
-      <c r="DB152" s="8"/>
+      <c r="DB152" s="20"/>
       <c r="DC152" s="8"/>
       <c r="DD152" s="8"/>
       <c r="DE152" s="8"/>
@@ -40993,19 +41230,20 @@
       <c r="CU153" s="10"/>
       <c r="CV153" s="10"/>
       <c r="CW153" s="10"/>
-      <c r="CX153" s="24"/>
+      <c r="CX153" s="10"/>
       <c r="CY153" s="24"/>
       <c r="CZ153" s="24"/>
       <c r="DA153" s="24"/>
+      <c r="DB153" s="24"/>
     </row>
     <row r="154" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A154" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CX154" s="4"/>
       <c r="CY154" s="4"/>
       <c r="CZ154" s="4"/>
       <c r="DA154" s="4"/>
+      <c r="DB154" s="4"/>
     </row>
     <row r="155" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B155" s="8"/>
@@ -41108,11 +41346,11 @@
       <c r="CU155" s="8"/>
       <c r="CV155" s="8"/>
       <c r="CW155" s="8"/>
-      <c r="CX155" s="7"/>
+      <c r="CX155" s="8"/>
       <c r="CY155" s="7"/>
       <c r="CZ155" s="7"/>
       <c r="DA155" s="7"/>
-      <c r="DB155" s="8"/>
+      <c r="DB155" s="7"/>
       <c r="DC155" s="8"/>
       <c r="DD155" s="8"/>
       <c r="DE155" s="8"/>
@@ -41546,6 +41784,9 @@
       <c r="CY164" s="21"/>
       <c r="CZ164" s="21"/>
       <c r="DA164" s="21"/>
+      <c r="DB164" s="21">
+        <v>2026</v>
+      </c>
     </row>
     <row r="165" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A165" s="5" t="s">
@@ -41862,6 +42103,9 @@
       </c>
       <c r="DA165" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB165" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="166" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -42183,7 +42427,9 @@
       <c r="DA167" s="16">
         <v>134.0009112412896</v>
       </c>
-      <c r="DB167" s="8"/>
+      <c r="DB167" s="16">
+        <v>123.82517368497858</v>
+      </c>
       <c r="DC167" s="8"/>
       <c r="DD167" s="8"/>
       <c r="DE167" s="8"/>
@@ -42574,7 +42820,9 @@
       <c r="DA168" s="16">
         <v>134.26059903443775</v>
       </c>
-      <c r="DB168" s="8"/>
+      <c r="DB168" s="16">
+        <v>117.44145820956311</v>
+      </c>
       <c r="DC168" s="8"/>
       <c r="DD168" s="8"/>
       <c r="DE168" s="8"/>
@@ -42965,7 +43213,9 @@
       <c r="DA169" s="16">
         <v>148.73823641789875</v>
       </c>
-      <c r="DB169" s="8"/>
+      <c r="DB169" s="16">
+        <v>103.97943091550204</v>
+      </c>
       <c r="DC169" s="8"/>
       <c r="DD169" s="8"/>
       <c r="DE169" s="8"/>
@@ -43356,7 +43606,9 @@
       <c r="DA170" s="16">
         <v>101.88675539619258</v>
       </c>
-      <c r="DB170" s="8"/>
+      <c r="DB170" s="16">
+        <v>90.847739570807121</v>
+      </c>
       <c r="DC170" s="8"/>
       <c r="DD170" s="8"/>
       <c r="DE170" s="8"/>
@@ -43747,7 +43999,9 @@
       <c r="DA171" s="16">
         <v>75.88969548718002</v>
       </c>
-      <c r="DB171" s="8"/>
+      <c r="DB171" s="16">
+        <v>93.306018240767131</v>
+      </c>
       <c r="DC171" s="8"/>
       <c r="DD171" s="8"/>
       <c r="DE171" s="8"/>
@@ -44138,7 +44392,9 @@
       <c r="DA172" s="16">
         <v>96.11698254275467</v>
       </c>
-      <c r="DB172" s="8"/>
+      <c r="DB172" s="16">
+        <v>85.188592929729083</v>
+      </c>
       <c r="DC172" s="8"/>
       <c r="DD172" s="8"/>
       <c r="DE172" s="8"/>
@@ -44529,7 +44785,9 @@
       <c r="DA173" s="16">
         <v>74.847683871071297</v>
       </c>
-      <c r="DB173" s="8"/>
+      <c r="DB173" s="16">
+        <v>73.067018087082303</v>
+      </c>
       <c r="DC173" s="8"/>
       <c r="DD173" s="8"/>
       <c r="DE173" s="8"/>
@@ -44920,7 +45178,9 @@
       <c r="DA174" s="16">
         <v>102.90212757130215</v>
       </c>
-      <c r="DB174" s="8"/>
+      <c r="DB174" s="16">
+        <v>92.521766131910056</v>
+      </c>
       <c r="DC174" s="8"/>
       <c r="DD174" s="8"/>
       <c r="DE174" s="8"/>
@@ -45311,7 +45571,9 @@
       <c r="DA175" s="16">
         <v>121.9581770413261</v>
       </c>
-      <c r="DB175" s="8"/>
+      <c r="DB175" s="16">
+        <v>95.828709187738028</v>
+      </c>
       <c r="DC175" s="8"/>
       <c r="DD175" s="8"/>
       <c r="DE175" s="8"/>
@@ -45702,7 +45964,9 @@
       <c r="DA176" s="16">
         <v>118.75759437976221</v>
       </c>
-      <c r="DB176" s="8"/>
+      <c r="DB176" s="16">
+        <v>167.59042085543135</v>
+      </c>
       <c r="DC176" s="8"/>
       <c r="DD176" s="8"/>
       <c r="DE176" s="8"/>
@@ -46093,7 +46357,9 @@
       <c r="DA177" s="16">
         <v>116.63977229920155</v>
       </c>
-      <c r="DB177" s="8"/>
+      <c r="DB177" s="16">
+        <v>76.886140199307647</v>
+      </c>
       <c r="DC177" s="8"/>
       <c r="DD177" s="8"/>
       <c r="DE177" s="8"/>
@@ -46484,7 +46750,9 @@
       <c r="DA178" s="16">
         <v>73.325357671059237</v>
       </c>
-      <c r="DB178" s="8"/>
+      <c r="DB178" s="16">
+        <v>78.046599542828517</v>
+      </c>
       <c r="DC178" s="8"/>
       <c r="DD178" s="8"/>
       <c r="DE178" s="8"/>
@@ -46875,7 +47143,9 @@
       <c r="DA179" s="16">
         <v>125.14746118504696</v>
       </c>
-      <c r="DB179" s="8"/>
+      <c r="DB179" s="16">
+        <v>116.12782134015329</v>
+      </c>
       <c r="DC179" s="8"/>
       <c r="DD179" s="8"/>
       <c r="DE179" s="8"/>
@@ -47266,7 +47536,9 @@
       <c r="DA180" s="16">
         <v>112.52707291345463</v>
       </c>
-      <c r="DB180" s="8"/>
+      <c r="DB180" s="16">
+        <v>113.65664893130148</v>
+      </c>
       <c r="DC180" s="8"/>
       <c r="DD180" s="8"/>
       <c r="DE180" s="8"/>
@@ -47657,7 +47929,9 @@
       <c r="DA181" s="16">
         <v>72.980093786738266</v>
       </c>
-      <c r="DB181" s="8"/>
+      <c r="DB181" s="16">
+        <v>66.001610314070518</v>
+      </c>
       <c r="DC181" s="8"/>
       <c r="DD181" s="8"/>
       <c r="DE181" s="8"/>
@@ -48048,7 +48322,9 @@
       <c r="DA182" s="16">
         <v>113.03470850848201</v>
       </c>
-      <c r="DB182" s="8"/>
+      <c r="DB182" s="16">
+        <v>114.91008833558105</v>
+      </c>
       <c r="DC182" s="8"/>
       <c r="DD182" s="8"/>
       <c r="DE182" s="8"/>
@@ -48439,7 +48715,9 @@
       <c r="DA183" s="16">
         <v>75.657959942414408</v>
       </c>
-      <c r="DB183" s="8"/>
+      <c r="DB183" s="16">
+        <v>85.41870416400053</v>
+      </c>
       <c r="DC183" s="8"/>
       <c r="DD183" s="8"/>
       <c r="DE183" s="8"/>
@@ -48830,7 +49108,9 @@
       <c r="DA184" s="16">
         <v>102.64785171126985</v>
       </c>
-      <c r="DB184" s="8"/>
+      <c r="DB184" s="16">
+        <v>111.90930185955123</v>
+      </c>
       <c r="DC184" s="8"/>
       <c r="DD184" s="8"/>
       <c r="DE184" s="8"/>
@@ -49221,7 +49501,9 @@
       <c r="DA185" s="16">
         <v>100.97986648258184</v>
       </c>
-      <c r="DB185" s="8"/>
+      <c r="DB185" s="16">
+        <v>84.70852940882358</v>
+      </c>
       <c r="DC185" s="8"/>
       <c r="DD185" s="8"/>
       <c r="DE185" s="8"/>
@@ -49612,7 +49894,9 @@
       <c r="DA186" s="16">
         <v>89.396729190121277</v>
       </c>
-      <c r="DB186" s="8"/>
+      <c r="DB186" s="16">
+        <v>91.013405805476793</v>
+      </c>
       <c r="DC186" s="8"/>
       <c r="DD186" s="8"/>
       <c r="DE186" s="8"/>
@@ -50003,7 +50287,9 @@
       <c r="DA187" s="16">
         <v>110.8087980093088</v>
       </c>
-      <c r="DB187" s="8"/>
+      <c r="DB187" s="16">
+        <v>89.456307337514815</v>
+      </c>
       <c r="DC187" s="8"/>
       <c r="DD187" s="8"/>
       <c r="DE187" s="8"/>
@@ -50394,7 +50680,9 @@
       <c r="DA188" s="16">
         <v>105.89513660901841</v>
       </c>
-      <c r="DB188" s="8"/>
+      <c r="DB188" s="16">
+        <v>95.862873616877181</v>
+      </c>
       <c r="DC188" s="8"/>
       <c r="DD188" s="8"/>
       <c r="DE188" s="8"/>
@@ -50965,7 +51253,9 @@
       <c r="DA190" s="16">
         <v>120.63039232297301</v>
       </c>
-      <c r="DB190" s="8"/>
+      <c r="DB190" s="16">
+        <v>108.35762019717734</v>
+      </c>
       <c r="DC190" s="8"/>
       <c r="DD190" s="8"/>
       <c r="DE190" s="8"/>
@@ -51146,6 +51436,7 @@
       <c r="CY191" s="10"/>
       <c r="CZ191" s="10"/>
       <c r="DA191" s="10"/>
+      <c r="DB191" s="10"/>
     </row>
     <row r="192" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A192" s="11" t="s">
@@ -51340,6 +51631,9 @@
       <c r="CY203" s="21"/>
       <c r="CZ203" s="21"/>
       <c r="DA203" s="21"/>
+      <c r="DB203" s="21">
+        <v>2026</v>
+      </c>
     </row>
     <row r="204" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A204" s="5" t="s">
@@ -51656,6 +51950,9 @@
       </c>
       <c r="DA204" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB204" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="205" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -51977,7 +52274,9 @@
       <c r="DA206" s="16">
         <v>60.423026912769153</v>
       </c>
-      <c r="DB206" s="8"/>
+      <c r="DB206" s="16">
+        <v>62.460433709087447</v>
+      </c>
       <c r="DC206" s="8"/>
       <c r="DD206" s="8"/>
       <c r="DE206" s="8"/>
@@ -52368,7 +52667,9 @@
       <c r="DA207" s="16">
         <v>4.1673369041967545</v>
       </c>
-      <c r="DB207" s="8"/>
+      <c r="DB207" s="16">
+        <v>3.1290953189364838</v>
+      </c>
       <c r="DC207" s="8"/>
       <c r="DD207" s="8"/>
       <c r="DE207" s="8"/>
@@ -52759,7 +53060,9 @@
       <c r="DA208" s="16">
         <v>0.27452884148988888</v>
       </c>
-      <c r="DB208" s="8"/>
+      <c r="DB208" s="16">
+        <v>0.24776302467087269</v>
+      </c>
       <c r="DC208" s="8"/>
       <c r="DD208" s="8"/>
       <c r="DE208" s="8"/>
@@ -53150,7 +53453,9 @@
       <c r="DA209" s="16">
         <v>0.70804801167050124</v>
       </c>
-      <c r="DB209" s="8"/>
+      <c r="DB209" s="16">
+        <v>0.90984268718556616</v>
+      </c>
       <c r="DC209" s="8"/>
       <c r="DD209" s="8"/>
       <c r="DE209" s="8"/>
@@ -53541,7 +53846,9 @@
       <c r="DA210" s="16">
         <v>0.57343459817602682</v>
       </c>
-      <c r="DB210" s="8"/>
+      <c r="DB210" s="16">
+        <v>1.1475729131913863</v>
+      </c>
       <c r="DC210" s="8"/>
       <c r="DD210" s="8"/>
       <c r="DE210" s="8"/>
@@ -53932,7 +54239,9 @@
       <c r="DA211" s="16">
         <v>0.52173121667914601</v>
       </c>
-      <c r="DB211" s="8"/>
+      <c r="DB211" s="16">
+        <v>0.24128843883805454</v>
+      </c>
       <c r="DC211" s="8"/>
       <c r="DD211" s="8"/>
       <c r="DE211" s="8"/>
@@ -54323,7 +54632,9 @@
       <c r="DA212" s="16">
         <v>0.9567671474837941</v>
       </c>
-      <c r="DB212" s="8"/>
+      <c r="DB212" s="16">
+        <v>0.52162242723113406</v>
+      </c>
       <c r="DC212" s="8"/>
       <c r="DD212" s="8"/>
       <c r="DE212" s="8"/>
@@ -54714,7 +55025,9 @@
       <c r="DA213" s="16">
         <v>0.49209693959136264</v>
       </c>
-      <c r="DB213" s="8"/>
+      <c r="DB213" s="16">
+        <v>0.51579085922132784</v>
+      </c>
       <c r="DC213" s="8"/>
       <c r="DD213" s="8"/>
       <c r="DE213" s="8"/>
@@ -55105,7 +55418,9 @@
       <c r="DA214" s="16">
         <v>0.66265184539923039</v>
       </c>
-      <c r="DB214" s="8"/>
+      <c r="DB214" s="16">
+        <v>0.80366058201820445</v>
+      </c>
       <c r="DC214" s="8"/>
       <c r="DD214" s="8"/>
       <c r="DE214" s="8"/>
@@ -55496,7 +55811,9 @@
       <c r="DA215" s="16">
         <v>4.4737680335472874</v>
       </c>
-      <c r="DB215" s="8"/>
+      <c r="DB215" s="16">
+        <v>1.1373791265147675</v>
+      </c>
       <c r="DC215" s="8"/>
       <c r="DD215" s="8"/>
       <c r="DE215" s="8"/>
@@ -55887,7 +56204,9 @@
       <c r="DA216" s="16">
         <v>12.074398697284028</v>
       </c>
-      <c r="DB216" s="8"/>
+      <c r="DB216" s="16">
+        <v>6.5266913196272629</v>
+      </c>
       <c r="DC216" s="8"/>
       <c r="DD216" s="8"/>
       <c r="DE216" s="8"/>
@@ -56278,7 +56597,9 @@
       <c r="DA217" s="16">
         <v>1.0380030340360229</v>
       </c>
-      <c r="DB217" s="8"/>
+      <c r="DB217" s="16">
+        <v>0.66241683759955694</v>
+      </c>
       <c r="DC217" s="8"/>
       <c r="DD217" s="8"/>
       <c r="DE217" s="8"/>
@@ -56669,7 +56990,9 @@
       <c r="DA218" s="16">
         <v>0.55532377743785921</v>
       </c>
-      <c r="DB218" s="8"/>
+      <c r="DB218" s="16">
+        <v>0.64707178106273922</v>
+      </c>
       <c r="DC218" s="8"/>
       <c r="DD218" s="8"/>
       <c r="DE218" s="8"/>
@@ -57060,7 +57383,9 @@
       <c r="DA219" s="16">
         <v>2.1215685849495172</v>
       </c>
-      <c r="DB219" s="8"/>
+      <c r="DB219" s="16">
+        <v>1.071662750875676</v>
+      </c>
       <c r="DC219" s="8"/>
       <c r="DD219" s="8"/>
       <c r="DE219" s="8"/>
@@ -57451,7 +57776,9 @@
       <c r="DA220" s="16">
         <v>0.47037753330321092</v>
       </c>
-      <c r="DB220" s="8"/>
+      <c r="DB220" s="16">
+        <v>1.1609018549541046</v>
+      </c>
       <c r="DC220" s="8"/>
       <c r="DD220" s="8"/>
       <c r="DE220" s="8"/>
@@ -57842,7 +58169,9 @@
       <c r="DA221" s="16">
         <v>0.87101476714937909</v>
       </c>
-      <c r="DB221" s="8"/>
+      <c r="DB221" s="16">
+        <v>0.5115691464889619</v>
+      </c>
       <c r="DC221" s="8"/>
       <c r="DD221" s="8"/>
       <c r="DE221" s="8"/>
@@ -58233,7 +58562,9 @@
       <c r="DA222" s="16">
         <v>4.2066916566209231</v>
       </c>
-      <c r="DB222" s="8"/>
+      <c r="DB222" s="16">
+        <v>11.470861908222881</v>
+      </c>
       <c r="DC222" s="8"/>
       <c r="DD222" s="8"/>
       <c r="DE222" s="8"/>
@@ -58624,7 +58955,9 @@
       <c r="DA223" s="16">
         <v>0.90437755372875117</v>
       </c>
-      <c r="DB223" s="8"/>
+      <c r="DB223" s="16">
+        <v>1.4239361463712903</v>
+      </c>
       <c r="DC223" s="8"/>
       <c r="DD223" s="8"/>
       <c r="DE223" s="8"/>
@@ -59015,7 +59348,9 @@
       <c r="DA224" s="16">
         <v>1.3393090265627707</v>
       </c>
-      <c r="DB224" s="8"/>
+      <c r="DB224" s="16">
+        <v>0.91146894163426762</v>
+      </c>
       <c r="DC224" s="8"/>
       <c r="DD224" s="8"/>
       <c r="DE224" s="8"/>
@@ -59406,7 +59741,9 @@
       <c r="DA225" s="16">
         <v>1.2569603478852309</v>
       </c>
-      <c r="DB225" s="8"/>
+      <c r="DB225" s="16">
+        <v>1.6535276179809371</v>
+      </c>
       <c r="DC225" s="8"/>
       <c r="DD225" s="8"/>
       <c r="DE225" s="8"/>
@@ -59797,7 +60134,9 @@
       <c r="DA226" s="16">
         <v>0.71852711362783184</v>
       </c>
-      <c r="DB226" s="8"/>
+      <c r="DB226" s="16">
+        <v>0.460849439603087</v>
+      </c>
       <c r="DC226" s="8"/>
       <c r="DD226" s="8"/>
       <c r="DE226" s="8"/>
@@ -60188,7 +60527,9 @@
       <c r="DA227" s="16">
         <v>1.1900574564113471</v>
       </c>
-      <c r="DB227" s="8"/>
+      <c r="DB227" s="16">
+        <v>2.3845931686839936</v>
+      </c>
       <c r="DC227" s="8"/>
       <c r="DD227" s="8"/>
       <c r="DE227" s="8"/>
@@ -60759,7 +61100,9 @@
       <c r="DA229" s="16">
         <v>100</v>
       </c>
-      <c r="DB229" s="8"/>
+      <c r="DB229" s="16">
+        <v>100</v>
+      </c>
       <c r="DC229" s="8"/>
       <c r="DD229" s="8"/>
       <c r="DE229" s="8"/>
@@ -60940,6 +61283,7 @@
       <c r="CY230" s="10"/>
       <c r="CZ230" s="10"/>
       <c r="DA230" s="10"/>
+      <c r="DB230" s="10"/>
     </row>
     <row r="231" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A231" s="11" t="s">
@@ -61494,6 +61838,9 @@
       <c r="CY242" s="21"/>
       <c r="CZ242" s="21"/>
       <c r="DA242" s="21"/>
+      <c r="DB242" s="21">
+        <v>2026</v>
+      </c>
     </row>
     <row r="243" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A243" s="5" t="s">
@@ -61810,6 +62157,9 @@
       </c>
       <c r="DA243" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB243" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="244" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -62131,7 +62481,9 @@
       <c r="DA245" s="16">
         <v>54.394058774004726</v>
       </c>
-      <c r="DB245" s="8"/>
+      <c r="DB245" s="16">
+        <v>54.658222975069513</v>
+      </c>
       <c r="DC245" s="8"/>
       <c r="DD245" s="8"/>
       <c r="DE245" s="8"/>
@@ -62522,7 +62874,9 @@
       <c r="DA246" s="16">
         <v>3.7442666672916758</v>
       </c>
-      <c r="DB246" s="8"/>
+      <c r="DB246" s="16">
+        <v>2.887066690921551</v>
+      </c>
       <c r="DC246" s="8"/>
       <c r="DD246" s="8"/>
       <c r="DE246" s="8"/>
@@ -62913,7 +63267,9 @@
       <c r="DA247" s="16">
         <v>0.22264968746739427</v>
       </c>
-      <c r="DB247" s="8"/>
+      <c r="DB247" s="16">
+        <v>0.25819540932097707</v>
+      </c>
       <c r="DC247" s="8"/>
       <c r="DD247" s="8"/>
       <c r="DE247" s="8"/>
@@ -63304,7 +63660,9 @@
       <c r="DA248" s="16">
         <v>0.83830434190571257</v>
       </c>
-      <c r="DB248" s="8"/>
+      <c r="DB248" s="16">
+        <v>1.0852046380349685</v>
+      </c>
       <c r="DC248" s="8"/>
       <c r="DD248" s="8"/>
       <c r="DE248" s="8"/>
@@ -63695,7 +64053,9 @@
       <c r="DA249" s="16">
         <v>0.91150241288326073</v>
       </c>
-      <c r="DB249" s="8"/>
+      <c r="DB249" s="16">
+        <v>1.3326929197138384</v>
+      </c>
       <c r="DC249" s="8"/>
       <c r="DD249" s="8"/>
       <c r="DE249" s="8"/>
@@ -64086,7 +64446,9 @@
       <c r="DA250" s="16">
         <v>0.65479210530929843</v>
       </c>
-      <c r="DB250" s="8"/>
+      <c r="DB250" s="16">
+        <v>0.30691246462012567</v>
+      </c>
       <c r="DC250" s="8"/>
       <c r="DD250" s="8"/>
       <c r="DE250" s="8"/>
@@ -64477,7 +64839,9 @@
       <c r="DA251" s="16">
         <v>1.5420009062873614</v>
       </c>
-      <c r="DB251" s="8"/>
+      <c r="DB251" s="16">
+        <v>0.77356057953367641</v>
+      </c>
       <c r="DC251" s="8"/>
       <c r="DD251" s="8"/>
       <c r="DE251" s="8"/>
@@ -64868,7 +65232,9 @@
       <c r="DA252" s="16">
         <v>0.57687676907076446</v>
       </c>
-      <c r="DB252" s="8"/>
+      <c r="DB252" s="16">
+        <v>0.60407266701974915</v>
+      </c>
       <c r="DC252" s="8"/>
       <c r="DD252" s="8"/>
       <c r="DE252" s="8"/>
@@ -65259,7 +65625,9 @@
       <c r="DA253" s="16">
         <v>0.65543741324507121</v>
       </c>
-      <c r="DB253" s="8"/>
+      <c r="DB253" s="16">
+        <v>0.90873339369694806</v>
+      </c>
       <c r="DC253" s="8"/>
       <c r="DD253" s="8"/>
       <c r="DE253" s="8"/>
@@ -65650,7 +66018,9 @@
       <c r="DA254" s="16">
         <v>4.5443190043326753</v>
       </c>
-      <c r="DB254" s="8"/>
+      <c r="DB254" s="16">
+        <v>0.73538627555209912</v>
+      </c>
       <c r="DC254" s="8"/>
       <c r="DD254" s="8"/>
       <c r="DE254" s="8"/>
@@ -66041,7 +66411,9 @@
       <c r="DA255" s="16">
         <v>12.487502531993004</v>
       </c>
-      <c r="DB255" s="8"/>
+      <c r="DB255" s="16">
+        <v>9.1982343933914059</v>
+      </c>
       <c r="DC255" s="8"/>
       <c r="DD255" s="8"/>
       <c r="DE255" s="8"/>
@@ -66432,7 +66804,9 @@
       <c r="DA256" s="16">
         <v>1.7076590855501914</v>
       </c>
-      <c r="DB256" s="8"/>
+      <c r="DB256" s="16">
+        <v>0.91968019774442034</v>
+      </c>
       <c r="DC256" s="8"/>
       <c r="DD256" s="8"/>
       <c r="DE256" s="8"/>
@@ -66823,7 +67197,9 @@
       <c r="DA257" s="16">
         <v>0.5352799369981015</v>
       </c>
-      <c r="DB257" s="8"/>
+      <c r="DB257" s="16">
+        <v>0.60377571441154565</v>
+      </c>
       <c r="DC257" s="8"/>
       <c r="DD257" s="8"/>
       <c r="DE257" s="8"/>
@@ -67214,7 +67590,9 @@
       <c r="DA258" s="16">
         <v>2.2743473558526595</v>
       </c>
-      <c r="DB258" s="8"/>
+      <c r="DB258" s="16">
+        <v>1.0216984789780137</v>
+      </c>
       <c r="DC258" s="8"/>
       <c r="DD258" s="8"/>
       <c r="DE258" s="8"/>
@@ -67605,7 +67983,9 @@
       <c r="DA259" s="16">
         <v>0.77749730697920261</v>
       </c>
-      <c r="DB259" s="8"/>
+      <c r="DB259" s="16">
+        <v>1.905901411900832</v>
+      </c>
       <c r="DC259" s="8"/>
       <c r="DD259" s="8"/>
       <c r="DE259" s="8"/>
@@ -67996,7 +68376,9 @@
       <c r="DA260" s="16">
         <v>0.92954504387869652</v>
       </c>
-      <c r="DB260" s="8"/>
+      <c r="DB260" s="16">
+        <v>0.48239816088176213</v>
+      </c>
       <c r="DC260" s="8"/>
       <c r="DD260" s="8"/>
       <c r="DE260" s="8"/>
@@ -68387,7 +68769,9 @@
       <c r="DA261" s="16">
         <v>6.7072237383376283</v>
       </c>
-      <c r="DB261" s="8"/>
+      <c r="DB261" s="16">
+        <v>14.551324679417505</v>
+      </c>
       <c r="DC261" s="8"/>
       <c r="DD261" s="8"/>
       <c r="DE261" s="8"/>
@@ -68778,7 +69162,9 @@
       <c r="DA262" s="16">
         <v>1.0628124923769069</v>
       </c>
-      <c r="DB262" s="8"/>
+      <c r="DB262" s="16">
+        <v>1.3787444794104387</v>
+      </c>
       <c r="DC262" s="8"/>
       <c r="DD262" s="8"/>
       <c r="DE262" s="8"/>
@@ -69169,7 +69555,9 @@
       <c r="DA263" s="16">
         <v>1.5999364917345584</v>
       </c>
-      <c r="DB263" s="8"/>
+      <c r="DB263" s="16">
+        <v>1.1659346005461579</v>
+      </c>
       <c r="DC263" s="8"/>
       <c r="DD263" s="8"/>
       <c r="DE263" s="8"/>
@@ -69560,7 +69948,9 @@
       <c r="DA264" s="16">
         <v>1.69612044281114</v>
       </c>
-      <c r="DB264" s="8"/>
+      <c r="DB264" s="16">
+        <v>1.9686365544617372</v>
+      </c>
       <c r="DC264" s="8"/>
       <c r="DD264" s="8"/>
       <c r="DE264" s="8"/>
@@ -69951,7 +70341,9 @@
       <c r="DA265" s="16">
         <v>0.78221413072576862</v>
       </c>
-      <c r="DB265" s="8"/>
+      <c r="DB265" s="16">
+        <v>0.55822277971060064</v>
+      </c>
       <c r="DC265" s="8"/>
       <c r="DD265" s="8"/>
       <c r="DE265" s="8"/>
@@ -70342,7 +70734,9 @@
       <c r="DA266" s="16">
         <v>1.3556533609642119</v>
       </c>
-      <c r="DB266" s="8"/>
+      <c r="DB266" s="16">
+        <v>2.6954005356621504</v>
+      </c>
       <c r="DC266" s="8"/>
       <c r="DD266" s="8"/>
       <c r="DE266" s="8"/>
@@ -70913,7 +71307,9 @@
       <c r="DA268" s="16">
         <v>100</v>
       </c>
-      <c r="DB268" s="8"/>
+      <c r="DB268" s="16">
+        <v>100</v>
+      </c>
       <c r="DC268" s="8"/>
       <c r="DD268" s="8"/>
       <c r="DE268" s="8"/>
@@ -71094,6 +71490,7 @@
       <c r="CY269" s="10"/>
       <c r="CZ269" s="10"/>
       <c r="DA269" s="10"/>
+      <c r="DB269" s="10"/>
     </row>
     <row r="270" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A270" s="11" t="s">
@@ -71374,7 +71771,7 @@
       <c r="CM272" s="8"/>
       <c r="CN272" s="8"/>
       <c r="CO272" s="8"/>
-      <c r="DB272" s="8"/>
+      <c r="DB272" s="7"/>
       <c r="DC272" s="8"/>
       <c r="DD272" s="8"/>
       <c r="DE272" s="8"/>
@@ -71445,18 +71842,21 @@
       <c r="FR272" s="8"/>
       <c r="FS272" s="8"/>
     </row>
+    <row r="273" spans="106:106" x14ac:dyDescent="0.2">
+      <c r="DB273" s="8"/>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.3" top="1" bottom="0.16700000000000001" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="33" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="6" manualBreakCount="6">
-    <brk id="39" max="81" man="1"/>
-    <brk id="78" max="81" man="1"/>
-    <brk id="117" max="81" man="1"/>
-    <brk id="156" max="81" man="1"/>
-    <brk id="194" max="81" man="1"/>
-    <brk id="233" max="81" man="1"/>
+    <brk id="39" max="105" man="1"/>
+    <brk id="78" max="105" man="1"/>
+    <brk id="117" max="105" man="1"/>
+    <brk id="156" max="105" man="1"/>
+    <brk id="194" max="105" man="1"/>
+    <brk id="233" max="105" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-10MFG_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-10MFG_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0C883D-115D-46FF-A3F5-C4071AC207BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048F1011-7525-4148-847A-9BD7E62490FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -353,7 +353,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">MFG!$A$1:$DB$271</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">MFG!$A$1:$DC$271</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -527,7 +527,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="74">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -742,13 +742,13 @@
     <t>Table 11.7 Gross Value Added in Manufacturing, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>As of August 2026</t>
   </si>
 </sst>
 </file>
@@ -1261,12 +1261,12 @@
   <sheetPr transitionEvaluation="1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:FW273"/>
+  <dimension ref="A1:FW272"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.140625" style="3" customWidth="1"/>
-    <col min="2" max="106" width="13" style="3" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="3"/>
+    <col min="2" max="107" width="13" style="3" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1281,7 +1281,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1291,7 +1291,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -1460,6 +1460,7 @@
       <c r="DB9" s="21">
         <v>2026</v>
       </c>
+      <c r="DC9" s="21"/>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1779,6 +1780,9 @@
       </c>
       <c r="DB10" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2101,9 +2105,11 @@
         <v>843036.00159373693</v>
       </c>
       <c r="DB12" s="25">
-        <v>734116.88930629659</v>
-      </c>
-      <c r="DC12" s="8"/>
+        <v>735300.34197586682</v>
+      </c>
+      <c r="DC12" s="18">
+        <v>533518.83097007731</v>
+      </c>
       <c r="DD12" s="8"/>
       <c r="DE12" s="8"/>
       <c r="DF12" s="8"/>
@@ -2494,9 +2500,11 @@
         <v>58143.645237766279</v>
       </c>
       <c r="DB13" s="25">
-        <v>36777.229767239587</v>
-      </c>
-      <c r="DC13" s="8"/>
+        <v>36818.422299499856</v>
+      </c>
+      <c r="DC13" s="18">
+        <v>36165.757475944985</v>
+      </c>
       <c r="DD13" s="8"/>
       <c r="DE13" s="8"/>
       <c r="DF13" s="8"/>
@@ -2887,9 +2895,11 @@
         <v>3830.2896871736684</v>
       </c>
       <c r="DB14" s="25">
-        <v>2912.0358306131538</v>
-      </c>
-      <c r="DC14" s="8"/>
+        <v>2912.9031592370748</v>
+      </c>
+      <c r="DC14" s="18">
+        <v>3311.9476895412531</v>
+      </c>
       <c r="DD14" s="8"/>
       <c r="DE14" s="8"/>
       <c r="DF14" s="8"/>
@@ -3280,9 +3290,11 @@
         <v>9878.8490943499964</v>
       </c>
       <c r="DB15" s="25">
-        <v>10693.663870245775</v>
-      </c>
-      <c r="DC15" s="8"/>
+        <v>10707.003995664047</v>
+      </c>
+      <c r="DC15" s="18">
+        <v>10447.393891527659</v>
+      </c>
       <c r="DD15" s="8"/>
       <c r="DE15" s="8"/>
       <c r="DF15" s="8"/>
@@ -3673,9 +3685,11 @@
         <v>8000.6917150929221</v>
       </c>
       <c r="DB16" s="25">
-        <v>13487.781100079934</v>
-      </c>
-      <c r="DC16" s="8"/>
+        <v>13268.052821711652</v>
+      </c>
+      <c r="DC16" s="18">
+        <v>11116.267281288005</v>
+      </c>
       <c r="DD16" s="8"/>
       <c r="DE16" s="8"/>
       <c r="DF16" s="8"/>
@@ -4066,9 +4080,11 @@
         <v>7279.3142165950012</v>
       </c>
       <c r="DB17" s="25">
-        <v>2835.9380110995571</v>
-      </c>
-      <c r="DC17" s="8"/>
+        <v>2879.2290532300058</v>
+      </c>
+      <c r="DC17" s="18">
+        <v>2296.2350581295741</v>
+      </c>
       <c r="DD17" s="8"/>
       <c r="DE17" s="8"/>
       <c r="DF17" s="8"/>
@@ -4459,9 +4475,11 @@
         <v>13349.035817676442</v>
       </c>
       <c r="DB18" s="25">
-        <v>6130.7905009889</v>
-      </c>
-      <c r="DC18" s="8"/>
+        <v>6053.7063409300572</v>
+      </c>
+      <c r="DC18" s="18">
+        <v>6266.787390077443</v>
+      </c>
       <c r="DD18" s="8"/>
       <c r="DE18" s="8"/>
       <c r="DF18" s="8"/>
@@ -4852,9 +4870,11 @@
         <v>6865.8499506906701</v>
       </c>
       <c r="DB19" s="25">
-        <v>6062.2502697910786</v>
-      </c>
-      <c r="DC19" s="8"/>
+        <v>5906.3073493793527</v>
+      </c>
+      <c r="DC19" s="18">
+        <v>6434.3193490647209</v>
+      </c>
       <c r="DD19" s="8"/>
       <c r="DE19" s="8"/>
       <c r="DF19" s="8"/>
@@ -5245,9 +5265,11 @@
         <v>9245.4713167641967</v>
       </c>
       <c r="DB20" s="25">
-        <v>9445.6725881404673</v>
-      </c>
-      <c r="DC20" s="8"/>
+        <v>9934.3095363892025</v>
+      </c>
+      <c r="DC20" s="18">
+        <v>13798.155929956105</v>
+      </c>
       <c r="DD20" s="8"/>
       <c r="DE20" s="8"/>
       <c r="DF20" s="8"/>
@@ -5638,9 +5660,11 @@
         <v>62419.04300002128</v>
       </c>
       <c r="DB21" s="25">
-        <v>13367.970357167935</v>
-      </c>
-      <c r="DC21" s="8"/>
+        <v>13378.863468816584</v>
+      </c>
+      <c r="DC21" s="18">
+        <v>86948.091077877209</v>
+      </c>
       <c r="DD21" s="8"/>
       <c r="DE21" s="8"/>
       <c r="DF21" s="8"/>
@@ -6031,9 +6055,11 @@
         <v>168464.79429278313</v>
       </c>
       <c r="DB22" s="25">
-        <v>76710.231493798841</v>
-      </c>
-      <c r="DC22" s="8"/>
+        <v>76768.267830188037</v>
+      </c>
+      <c r="DC22" s="18">
+        <v>61683.324484932731</v>
+      </c>
       <c r="DD22" s="8"/>
       <c r="DE22" s="8"/>
       <c r="DF22" s="8"/>
@@ -6424,9 +6450,11 @@
         <v>14482.457635219325</v>
       </c>
       <c r="DB23" s="25">
-        <v>7785.5909631948307</v>
-      </c>
-      <c r="DC23" s="8"/>
+        <v>7795.3851235944567</v>
+      </c>
+      <c r="DC23" s="18">
+        <v>8028.5922401744465</v>
+      </c>
       <c r="DD23" s="8"/>
       <c r="DE23" s="8"/>
       <c r="DF23" s="8"/>
@@ -6817,9 +6845,11 @@
         <v>7748.0053688307962</v>
       </c>
       <c r="DB24" s="25">
-        <v>7605.2357446655224</v>
-      </c>
-      <c r="DC24" s="8"/>
+        <v>7876.5108123989266</v>
+      </c>
+      <c r="DC24" s="18">
+        <v>9653.9953453518683</v>
+      </c>
       <c r="DD24" s="8"/>
       <c r="DE24" s="8"/>
       <c r="DF24" s="8"/>
@@ -7210,9 +7240,11 @@
         <v>29600.614010033132</v>
       </c>
       <c r="DB25" s="25">
-        <v>12595.58537045218</v>
-      </c>
-      <c r="DC25" s="8"/>
+        <v>12595.204850950664</v>
+      </c>
+      <c r="DC25" s="18">
+        <v>18398.379916509955</v>
+      </c>
       <c r="DD25" s="8"/>
       <c r="DE25" s="8"/>
       <c r="DF25" s="8"/>
@@ -7603,9 +7635,11 @@
         <v>6562.8157869009738</v>
       </c>
       <c r="DB26" s="25">
-        <v>13644.440295085937</v>
-      </c>
-      <c r="DC26" s="8"/>
+        <v>13737.23350865455</v>
+      </c>
+      <c r="DC26" s="18">
+        <v>7715.0960491086516</v>
+      </c>
       <c r="DD26" s="8"/>
       <c r="DE26" s="8"/>
       <c r="DF26" s="8"/>
@@ -7996,9 +8030,11 @@
         <v>12152.598837638405</v>
       </c>
       <c r="DB27" s="25">
-        <v>6012.6311679919454</v>
-      </c>
-      <c r="DC27" s="8"/>
+        <v>6125.5858084090105</v>
+      </c>
+      <c r="DC27" s="18">
+        <v>8995.0807246016375</v>
+      </c>
       <c r="DD27" s="8"/>
       <c r="DE27" s="8"/>
       <c r="DF27" s="8"/>
@@ -8389,9 +8425,11 @@
         <v>58692.731816551561</v>
       </c>
       <c r="DB28" s="25">
-        <v>134820.60500808683</v>
-      </c>
-      <c r="DC28" s="8"/>
+        <v>135511.76485182048</v>
+      </c>
+      <c r="DC28" s="18">
+        <v>115665.95783198555</v>
+      </c>
       <c r="DD28" s="8"/>
       <c r="DE28" s="8"/>
       <c r="DF28" s="8"/>
@@ -8782,9 +8820,11 @@
         <v>12618.084127551199</v>
       </c>
       <c r="DB29" s="25">
-        <v>16735.964069887654</v>
-      </c>
-      <c r="DC29" s="8"/>
+        <v>16693.966561541121</v>
+      </c>
+      <c r="DC29" s="18">
+        <v>16863.03292493122</v>
+      </c>
       <c r="DD29" s="8"/>
       <c r="DE29" s="8"/>
       <c r="DF29" s="8"/>
@@ -9175,9 +9215,11 @@
         <v>18686.348306944376</v>
       </c>
       <c r="DB30" s="25">
-        <v>10712.777744200954</v>
-      </c>
-      <c r="DC30" s="8"/>
+        <v>10628.404354462364</v>
+      </c>
+      <c r="DC30" s="18">
+        <v>3769.9575278786742</v>
+      </c>
       <c r="DD30" s="8"/>
       <c r="DE30" s="8"/>
       <c r="DF30" s="8"/>
@@ -9568,9 +9610,11 @@
         <v>17537.400557122703</v>
       </c>
       <c r="DB31" s="25">
-        <v>19434.423989880277</v>
-      </c>
-      <c r="DC31" s="8"/>
+        <v>19213.07431700184</v>
+      </c>
+      <c r="DC31" s="18">
+        <v>10340.429185210036</v>
+      </c>
       <c r="DD31" s="8"/>
       <c r="DE31" s="8"/>
       <c r="DF31" s="8"/>
@@ -9961,9 +10005,11 @@
         <v>10025.05594074243</v>
       </c>
       <c r="DB32" s="25">
-        <v>5416.5066899102567</v>
-      </c>
-      <c r="DC32" s="8"/>
+        <v>5494.2124299525403</v>
+      </c>
+      <c r="DC32" s="18">
+        <v>4551.2283465099081</v>
+      </c>
       <c r="DD32" s="8"/>
       <c r="DE32" s="8"/>
       <c r="DF32" s="8"/>
@@ -10354,9 +10400,11 @@
         <v>16603.955991284784</v>
       </c>
       <c r="DB33" s="25">
-        <v>28026.864613343947</v>
-      </c>
-      <c r="DC33" s="8"/>
+        <v>28038.278308190202</v>
+      </c>
+      <c r="DC33" s="18">
+        <v>22109.416896558803</v>
+      </c>
       <c r="DD33" s="8"/>
       <c r="DE33" s="8"/>
       <c r="DF33" s="8"/>
@@ -10927,9 +10975,11 @@
         <v>1395223.0543014701</v>
       </c>
       <c r="DB35" s="26">
-        <v>1175331.0787521622</v>
-      </c>
-      <c r="DC35" s="8"/>
+        <v>1177637.0287578891</v>
+      </c>
+      <c r="DC35" s="19">
+        <v>998078.27758723777</v>
+      </c>
       <c r="DD35" s="8"/>
       <c r="DE35" s="8"/>
       <c r="DF35" s="8"/>
@@ -11110,6 +11160,7 @@
       <c r="CZ36" s="10"/>
       <c r="DA36" s="10"/>
       <c r="DB36" s="10"/>
+      <c r="DC36" s="10"/>
     </row>
     <row r="37" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
@@ -11488,7 +11539,7 @@
     </row>
     <row r="42" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:179" x14ac:dyDescent="0.2">
@@ -11498,7 +11549,7 @@
     </row>
     <row r="45" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:179" x14ac:dyDescent="0.2">
@@ -11667,6 +11718,7 @@
       <c r="DB48" s="21">
         <v>2026</v>
       </c>
+      <c r="DC48" s="21"/>
     </row>
     <row r="49" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
@@ -11986,6 +12038,9 @@
       </c>
       <c r="DB49" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC49" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -12308,9 +12363,11 @@
         <v>629127.06621503388</v>
       </c>
       <c r="DB51" s="25">
-        <v>592865.62454089522</v>
-      </c>
-      <c r="DC51" s="8"/>
+        <v>593850.78998869937</v>
+      </c>
+      <c r="DC51" s="18">
+        <v>514184.74740737537</v>
+      </c>
       <c r="DD51" s="8"/>
       <c r="DE51" s="8"/>
       <c r="DF51" s="8"/>
@@ -12701,9 +12758,11 @@
         <v>43306.558778910614</v>
       </c>
       <c r="DB52" s="25">
-        <v>31315.372210053894</v>
-      </c>
-      <c r="DC52" s="8"/>
+        <v>31350.765266037954</v>
+      </c>
+      <c r="DC52" s="18">
+        <v>33138.042357322905</v>
+      </c>
       <c r="DD52" s="8"/>
       <c r="DE52" s="8"/>
       <c r="DF52" s="8"/>
@@ -13094,9 +13153,11 @@
         <v>2575.1883170188926</v>
       </c>
       <c r="DB53" s="25">
-        <v>2800.588351920866</v>
-      </c>
-      <c r="DC53" s="8"/>
+        <v>2801.422486726457</v>
+      </c>
+      <c r="DC53" s="18">
+        <v>3222.6808990152635</v>
+      </c>
       <c r="DD53" s="8"/>
       <c r="DE53" s="8"/>
       <c r="DF53" s="8"/>
@@ -13487,9 +13548,11 @@
         <v>9695.9109708965771</v>
       </c>
       <c r="DB54" s="25">
-        <v>11770.974072405057</v>
-      </c>
-      <c r="DC54" s="8"/>
+        <v>11786.254535114756</v>
+      </c>
+      <c r="DC54" s="18">
+        <v>11798.309445267663</v>
+      </c>
       <c r="DD54" s="8"/>
       <c r="DE54" s="8"/>
       <c r="DF54" s="8"/>
@@ -13880,9 +13943,11 @@
         <v>10542.527102964159</v>
       </c>
       <c r="DB55" s="25">
-        <v>14455.424585020897</v>
-      </c>
-      <c r="DC55" s="8"/>
+        <v>14220.301367861422</v>
+      </c>
+      <c r="DC55" s="18">
+        <v>12829.168305461484</v>
+      </c>
       <c r="DD55" s="8"/>
       <c r="DE55" s="8"/>
       <c r="DF55" s="8"/>
@@ -14273,9 +14338,11 @@
         <v>7573.3902834049368</v>
       </c>
       <c r="DB56" s="25">
-        <v>3329.0114480924503</v>
-      </c>
-      <c r="DC56" s="8"/>
+        <v>3379.8293341985845</v>
+      </c>
+      <c r="DC56" s="18">
+        <v>1862.7879755645172</v>
+      </c>
       <c r="DD56" s="8"/>
       <c r="DE56" s="8"/>
       <c r="DF56" s="8"/>
@@ -14666,9 +14733,11 @@
         <v>17834.935067156912</v>
       </c>
       <c r="DB57" s="25">
-        <v>8390.6400746806685</v>
-      </c>
-      <c r="DC57" s="8"/>
+        <v>8282.2536930960705</v>
+      </c>
+      <c r="DC57" s="18">
+        <v>11335.203805636193</v>
+      </c>
       <c r="DD57" s="8"/>
       <c r="DE57" s="8"/>
       <c r="DF57" s="8"/>
@@ -15059,9 +15128,11 @@
         <v>6672.2137945430113</v>
       </c>
       <c r="DB58" s="25">
-        <v>6552.2422703734519</v>
-      </c>
-      <c r="DC58" s="8"/>
+        <v>6383.6193940251651</v>
+      </c>
+      <c r="DC58" s="18">
+        <v>8538.7639518942597</v>
+      </c>
       <c r="DD58" s="8"/>
       <c r="DE58" s="8"/>
       <c r="DF58" s="8"/>
@@ -15452,9 +15523,11 @@
         <v>7580.853978844998</v>
       </c>
       <c r="DB59" s="25">
-        <v>9856.8296163057457</v>
-      </c>
-      <c r="DC59" s="8"/>
+        <v>10346.866909874494</v>
+      </c>
+      <c r="DC59" s="18">
+        <v>12577.386628985481</v>
+      </c>
       <c r="DD59" s="8"/>
       <c r="DE59" s="8"/>
       <c r="DF59" s="8"/>
@@ -15845,9 +15918,11 @@
         <v>52560.043276405631</v>
       </c>
       <c r="DB60" s="25">
-        <v>7976.5718642711436</v>
-      </c>
-      <c r="DC60" s="8"/>
+        <v>7983.0717057257134</v>
+      </c>
+      <c r="DC60" s="18">
+        <v>60769.707306740136</v>
+      </c>
       <c r="DD60" s="8"/>
       <c r="DE60" s="8"/>
       <c r="DF60" s="8"/>
@@ -16238,9 +16313,11 @@
         <v>144431.68995618518</v>
       </c>
       <c r="DB61" s="25">
-        <v>99771.208822483721</v>
-      </c>
-      <c r="DC61" s="8"/>
+        <v>99846.221756186103</v>
+      </c>
+      <c r="DC61" s="18">
+        <v>74793.673758014513</v>
+      </c>
       <c r="DD61" s="8"/>
       <c r="DE61" s="8"/>
       <c r="DF61" s="8"/>
@@ -16631,9 +16708,11 @@
         <v>19750.95396082248</v>
       </c>
       <c r="DB62" s="25">
-        <v>9975.5671724332387</v>
-      </c>
-      <c r="DC62" s="8"/>
+        <v>9988.116291109769</v>
+      </c>
+      <c r="DC62" s="18">
+        <v>13376.261502259735</v>
+      </c>
       <c r="DD62" s="8"/>
       <c r="DE62" s="8"/>
       <c r="DF62" s="8"/>
@@ -17024,9 +17103,11 @@
         <v>6191.1007186748702</v>
       </c>
       <c r="DB63" s="25">
-        <v>6549.0212912793831</v>
-      </c>
-      <c r="DC63" s="8"/>
+        <v>6782.5200333915054</v>
+      </c>
+      <c r="DC63" s="18">
+        <v>10051.771706808191</v>
+      </c>
       <c r="DD63" s="8"/>
       <c r="DE63" s="8"/>
       <c r="DF63" s="8"/>
@@ -17417,9 +17498,11 @@
         <v>26305.326570432677</v>
       </c>
       <c r="DB64" s="25">
-        <v>11082.136847150443</v>
-      </c>
-      <c r="DC64" s="8"/>
+        <v>11081.802049753991</v>
+      </c>
+      <c r="DC64" s="18">
+        <v>19748.314156909772</v>
+      </c>
       <c r="DD64" s="8"/>
       <c r="DE64" s="8"/>
       <c r="DF64" s="8"/>
@@ -17810,9 +17893,11 @@
         <v>8992.610787920843</v>
       </c>
       <c r="DB65" s="25">
-        <v>20672.889994893281</v>
-      </c>
-      <c r="DC65" s="8"/>
+        <v>20813.482342757343</v>
+      </c>
+      <c r="DC65" s="18">
+        <v>14440.727169751299</v>
+      </c>
       <c r="DD65" s="8"/>
       <c r="DE65" s="8"/>
       <c r="DF65" s="8"/>
@@ -18203,9 +18288,11 @@
         <v>10751.209958423067</v>
       </c>
       <c r="DB66" s="25">
-        <v>5232.4658827454568</v>
-      </c>
-      <c r="DC66" s="8"/>
+        <v>5330.5496483775532</v>
+      </c>
+      <c r="DC66" s="18">
+        <v>11264.95262416319</v>
+      </c>
       <c r="DD66" s="8"/>
       <c r="DE66" s="8"/>
       <c r="DF66" s="8"/>
@@ -18596,9 +18683,11 @@
         <v>77576.413455007772</v>
       </c>
       <c r="DB67" s="25">
-        <v>157834.99214555701</v>
-      </c>
-      <c r="DC67" s="8"/>
+        <v>158644.13558843418</v>
+      </c>
+      <c r="DC67" s="18">
+        <v>114049.42699296205</v>
+      </c>
       <c r="DD67" s="8"/>
       <c r="DE67" s="8"/>
       <c r="DF67" s="8"/>
@@ -18989,9 +19078,11 @@
         <v>12292.594454917213</v>
       </c>
       <c r="DB68" s="25">
-        <v>14954.935641446209</v>
-      </c>
-      <c r="DC68" s="8"/>
+        <v>14917.407475647051</v>
+      </c>
+      <c r="DC68" s="18">
+        <v>22722.667566085933</v>
+      </c>
       <c r="DD68" s="8"/>
       <c r="DE68" s="8"/>
       <c r="DF68" s="8"/>
@@ -19382,9 +19473,11 @@
         <v>18505.023781317446</v>
       </c>
       <c r="DB69" s="25">
-        <v>12646.634074472633</v>
-      </c>
-      <c r="DC69" s="8"/>
+        <v>12547.029713108521</v>
+      </c>
+      <c r="DC69" s="18">
+        <v>3966.0416386163834</v>
+      </c>
       <c r="DD69" s="8"/>
       <c r="DE69" s="8"/>
       <c r="DF69" s="8"/>
@@ -19775,9 +19868,11 @@
         <v>19617.496877123624</v>
       </c>
       <c r="DB70" s="25">
-        <v>21353.364175182636</v>
-      </c>
-      <c r="DC70" s="8"/>
+        <v>21109.884561646846</v>
+      </c>
+      <c r="DC70" s="18">
+        <v>13490.437471550707</v>
+      </c>
       <c r="DD70" s="8"/>
       <c r="DE70" s="8"/>
       <c r="DF70" s="8"/>
@@ -20168,9 +20263,11 @@
         <v>9047.1660381157162</v>
       </c>
       <c r="DB71" s="25">
-        <v>6054.9187096154201</v>
-      </c>
-      <c r="DC71" s="8"/>
+        <v>6145.4211690274897</v>
+      </c>
+      <c r="DC71" s="18">
+        <v>4664.5140514236173</v>
+      </c>
       <c r="DD71" s="8"/>
       <c r="DE71" s="8"/>
       <c r="DF71" s="8"/>
@@ -20561,9 +20658,11 @@
         <v>15679.620918370609</v>
       </c>
       <c r="DB72" s="25">
-        <v>29236.411924553096</v>
-      </c>
-      <c r="DC72" s="8"/>
+        <v>29248.068676236813</v>
+      </c>
+      <c r="DC72" s="18">
+        <v>26372.00255922605</v>
+      </c>
       <c r="DD72" s="8"/>
       <c r="DE72" s="8"/>
       <c r="DF72" s="8"/>
@@ -21134,9 +21233,11 @@
         <v>1156609.895262491</v>
       </c>
       <c r="DB74" s="26">
-        <v>1084677.8257158317</v>
-      </c>
-      <c r="DC74" s="8"/>
+        <v>1086839.8139870372</v>
+      </c>
+      <c r="DC74" s="19">
+        <v>999197.58928103477</v>
+      </c>
       <c r="DD74" s="8"/>
       <c r="DE74" s="8"/>
       <c r="DF74" s="8"/>
@@ -21317,6 +21418,7 @@
       <c r="CZ75" s="10"/>
       <c r="DA75" s="10"/>
       <c r="DB75" s="10"/>
+      <c r="DC75" s="10"/>
     </row>
     <row r="76" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
@@ -21429,7 +21531,7 @@
       <c r="CZ77" s="7"/>
       <c r="DA77" s="7"/>
       <c r="DB77" s="7"/>
-      <c r="DC77" s="8"/>
+      <c r="DC77" s="7"/>
       <c r="DD77" s="8"/>
       <c r="DE77" s="8"/>
       <c r="DF77" s="8"/>
@@ -21609,7 +21711,7 @@
       <c r="CZ78" s="7"/>
       <c r="DA78" s="7"/>
       <c r="DB78" s="7"/>
-      <c r="DC78" s="8"/>
+      <c r="DC78" s="7"/>
       <c r="DD78" s="8"/>
       <c r="DE78" s="8"/>
       <c r="DF78" s="8"/>
@@ -21692,6 +21794,7 @@
       <c r="CZ79" s="4"/>
       <c r="DA79" s="4"/>
       <c r="DB79" s="4"/>
+      <c r="DC79" s="4"/>
     </row>
     <row r="80" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
@@ -21702,16 +21805,18 @@
       <c r="CZ80" s="4"/>
       <c r="DA80" s="4"/>
       <c r="DB80" s="4"/>
+      <c r="DC80" s="4"/>
     </row>
     <row r="81" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="CX81" s="4"/>
       <c r="CY81" s="4"/>
       <c r="CZ81" s="4"/>
       <c r="DA81" s="4"/>
       <c r="DB81" s="4"/>
+      <c r="DC81" s="4"/>
     </row>
     <row r="82" spans="1:175" x14ac:dyDescent="0.2">
       <c r="CX82" s="4"/>
@@ -21719,6 +21824,7 @@
       <c r="CZ82" s="4"/>
       <c r="DA82" s="4"/>
       <c r="DB82" s="4"/>
+      <c r="DC82" s="4"/>
     </row>
     <row r="83" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
@@ -21729,16 +21835,18 @@
       <c r="CZ83" s="4"/>
       <c r="DA83" s="4"/>
       <c r="DB83" s="4"/>
+      <c r="DC83" s="4"/>
     </row>
     <row r="84" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="CX84" s="4"/>
       <c r="CY84" s="4"/>
       <c r="CZ84" s="4"/>
       <c r="DA84" s="4"/>
       <c r="DB84" s="4"/>
+      <c r="DC84" s="4"/>
     </row>
     <row r="85" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
@@ -21749,13 +21857,14 @@
       <c r="CZ85" s="4"/>
       <c r="DA85" s="4"/>
       <c r="DB85" s="4"/>
+      <c r="DC85" s="4"/>
     </row>
     <row r="86" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX86" s="4"/>
       <c r="CY86" s="4"/>
       <c r="CZ86" s="4"/>
       <c r="DA86" s="4"/>
       <c r="DB86" s="4"/>
+      <c r="DC86" s="4"/>
     </row>
     <row r="87" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="17"/>
@@ -21910,12 +22019,13 @@
       <c r="CV87" s="21"/>
       <c r="CW87" s="21"/>
       <c r="CX87" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="CY87" s="22"/>
+        <v>71</v>
+      </c>
+      <c r="CY87" s="21"/>
       <c r="CZ87" s="22"/>
       <c r="DA87" s="22"/>
       <c r="DB87" s="22"/>
+      <c r="DC87" s="22"/>
     </row>
     <row r="88" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
@@ -22224,17 +22334,20 @@
       <c r="CX88" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY88" s="23"/>
+      <c r="CY88" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ88" s="23"/>
       <c r="DA88" s="23"/>
       <c r="DB88" s="23"/>
+      <c r="DC88" s="23"/>
     </row>
     <row r="89" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6"/>
-      <c r="CY89" s="4"/>
       <c r="CZ89" s="4"/>
       <c r="DA89" s="4"/>
       <c r="DB89" s="4"/>
+      <c r="DC89" s="4"/>
     </row>
     <row r="90" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
@@ -22541,13 +22654,15 @@
         <v>6.526155231812524</v>
       </c>
       <c r="CX90" s="16">
-        <v>1.2101426619543645</v>
-      </c>
-      <c r="CY90" s="20"/>
+        <v>1.3733011660913093</v>
+      </c>
+      <c r="CY90" s="16">
+        <v>3.3845656946775051</v>
+      </c>
       <c r="CZ90" s="20"/>
       <c r="DA90" s="20"/>
       <c r="DB90" s="20"/>
-      <c r="DC90" s="8"/>
+      <c r="DC90" s="20"/>
       <c r="DD90" s="8"/>
       <c r="DE90" s="8"/>
       <c r="DF90" s="8"/>
@@ -22922,13 +23037,15 @@
         <v>-4.4279519440357404</v>
       </c>
       <c r="CX91" s="16">
-        <v>5.1010676245855819</v>
-      </c>
-      <c r="CY91" s="20"/>
+        <v>5.2187866356724584</v>
+      </c>
+      <c r="CY91" s="16">
+        <v>-3.1561284630470681</v>
+      </c>
       <c r="CZ91" s="20"/>
       <c r="DA91" s="20"/>
       <c r="DB91" s="20"/>
-      <c r="DC91" s="8"/>
+      <c r="DC91" s="20"/>
       <c r="DD91" s="8"/>
       <c r="DE91" s="8"/>
       <c r="DF91" s="8"/>
@@ -23303,13 +23420,15 @@
         <v>11.343262491359795</v>
       </c>
       <c r="CX92" s="16">
-        <v>7.3918314957037552</v>
-      </c>
-      <c r="CY92" s="20"/>
+        <v>7.4238173691096705</v>
+      </c>
+      <c r="CY92" s="16">
+        <v>7.8653360558590606</v>
+      </c>
       <c r="CZ92" s="20"/>
       <c r="DA92" s="20"/>
       <c r="DB92" s="20"/>
-      <c r="DC92" s="8"/>
+      <c r="DC92" s="20"/>
       <c r="DD92" s="8"/>
       <c r="DE92" s="8"/>
       <c r="DF92" s="8"/>
@@ -23684,13 +23803,15 @@
         <v>-8.3408759391205507</v>
       </c>
       <c r="CX93" s="16">
-        <v>18.748634393338918</v>
-      </c>
-      <c r="CY93" s="20"/>
+        <v>18.896770868851618</v>
+      </c>
+      <c r="CY93" s="16">
+        <v>10.342449858665191</v>
+      </c>
       <c r="CZ93" s="20"/>
       <c r="DA93" s="20"/>
       <c r="DB93" s="20"/>
-      <c r="DC93" s="8"/>
+      <c r="DC93" s="20"/>
       <c r="DD93" s="8"/>
       <c r="DE93" s="8"/>
       <c r="DF93" s="8"/>
@@ -24065,13 +24186,15 @@
         <v>-5.0686588074935912</v>
       </c>
       <c r="CX94" s="16">
-        <v>16.506628039598652</v>
-      </c>
-      <c r="CY94" s="20"/>
+        <v>14.608628612733469</v>
+      </c>
+      <c r="CY94" s="16">
+        <v>12.383851756684749</v>
+      </c>
       <c r="CZ94" s="20"/>
       <c r="DA94" s="20"/>
       <c r="DB94" s="20"/>
-      <c r="DC94" s="8"/>
+      <c r="DC94" s="20"/>
       <c r="DD94" s="8"/>
       <c r="DE94" s="8"/>
       <c r="DF94" s="8"/>
@@ -24446,13 +24569,15 @@
         <v>9.9820267604848283</v>
       </c>
       <c r="CX95" s="16">
-        <v>7.6653112441018862</v>
-      </c>
-      <c r="CY95" s="20"/>
+        <v>9.3088392432379123</v>
+      </c>
+      <c r="CY95" s="16">
+        <v>21.71848526524245</v>
+      </c>
       <c r="CZ95" s="20"/>
       <c r="DA95" s="20"/>
       <c r="DB95" s="20"/>
-      <c r="DC95" s="8"/>
+      <c r="DC95" s="20"/>
       <c r="DD95" s="8"/>
       <c r="DE95" s="8"/>
       <c r="DF95" s="8"/>
@@ -24827,13 +24952,15 @@
         <v>13.045945657276107</v>
       </c>
       <c r="CX96" s="16">
-        <v>12.378403677734269</v>
-      </c>
-      <c r="CY96" s="20"/>
+        <v>10.965438277129806</v>
+      </c>
+      <c r="CY96" s="16">
+        <v>0.28911789685824374</v>
+      </c>
       <c r="CZ96" s="20"/>
       <c r="DA96" s="20"/>
       <c r="DB96" s="20"/>
-      <c r="DC96" s="8"/>
+      <c r="DC96" s="20"/>
       <c r="DD96" s="8"/>
       <c r="DE96" s="8"/>
       <c r="DF96" s="8"/>
@@ -25208,13 +25335,15 @@
         <v>4.8822318874847497</v>
       </c>
       <c r="CX97" s="16">
-        <v>-4.7468206419928265</v>
-      </c>
-      <c r="CY97" s="20"/>
+        <v>-7.1970756309049619</v>
+      </c>
+      <c r="CY97" s="16">
+        <v>-0.51375757673129385</v>
+      </c>
       <c r="CZ97" s="20"/>
       <c r="DA97" s="20"/>
       <c r="DB97" s="20"/>
-      <c r="DC97" s="8"/>
+      <c r="DC97" s="20"/>
       <c r="DD97" s="8"/>
       <c r="DE97" s="8"/>
       <c r="DF97" s="8"/>
@@ -25589,13 +25718,15 @@
         <v>-12.567821209987883</v>
       </c>
       <c r="CX98" s="16">
-        <v>-12.543896406199835</v>
-      </c>
-      <c r="CY98" s="20"/>
+        <v>-8.0196782346474009</v>
+      </c>
+      <c r="CY98" s="16">
+        <v>3.8066928652849157</v>
+      </c>
       <c r="CZ98" s="20"/>
       <c r="DA98" s="20"/>
       <c r="DB98" s="20"/>
-      <c r="DC98" s="8"/>
+      <c r="DC98" s="20"/>
       <c r="DD98" s="8"/>
       <c r="DE98" s="8"/>
       <c r="DF98" s="8"/>
@@ -25970,13 +26101,15 @@
         <v>-3.7533444720508413</v>
       </c>
       <c r="CX99" s="16">
-        <v>-19.146453259209935</v>
-      </c>
-      <c r="CY99" s="20"/>
+        <v>-19.080568409954225</v>
+      </c>
+      <c r="CY99" s="16">
+        <v>74.344849063730265</v>
+      </c>
       <c r="CZ99" s="20"/>
       <c r="DA99" s="20"/>
       <c r="DB99" s="20"/>
-      <c r="DC99" s="8"/>
+      <c r="DC99" s="20"/>
       <c r="DD99" s="8"/>
       <c r="DE99" s="8"/>
       <c r="DF99" s="8"/>
@@ -26351,13 +26484,15 @@
         <v>-10.670507425064983</v>
       </c>
       <c r="CX100" s="16">
-        <v>-5.0896885892715744</v>
-      </c>
-      <c r="CY100" s="20"/>
+        <v>-5.0178826951610773</v>
+      </c>
+      <c r="CY100" s="16">
+        <v>-12.373368926830892</v>
+      </c>
       <c r="CZ100" s="20"/>
       <c r="DA100" s="20"/>
       <c r="DB100" s="20"/>
-      <c r="DC100" s="8"/>
+      <c r="DC100" s="20"/>
       <c r="DD100" s="8"/>
       <c r="DE100" s="8"/>
       <c r="DF100" s="8"/>
@@ -26732,13 +26867,15 @@
         <v>3.5736879222241384</v>
       </c>
       <c r="CX101" s="16">
-        <v>-1.3183230893037603</v>
-      </c>
-      <c r="CY101" s="20"/>
+        <v>-1.1941829724216291</v>
+      </c>
+      <c r="CY101" s="16">
+        <v>8.2258541530058551</v>
+      </c>
       <c r="CZ101" s="20"/>
       <c r="DA101" s="20"/>
       <c r="DB101" s="20"/>
-      <c r="DC101" s="8"/>
+      <c r="DC101" s="20"/>
       <c r="DD101" s="8"/>
       <c r="DE101" s="8"/>
       <c r="DF101" s="8"/>
@@ -27113,13 +27250,15 @@
         <v>0.67068652832919895</v>
       </c>
       <c r="CX102" s="16">
-        <v>-7.0046863553614855</v>
-      </c>
-      <c r="CY102" s="20"/>
+        <v>-3.687588653882159</v>
+      </c>
+      <c r="CY102" s="16">
+        <v>5.7518587146731619</v>
+      </c>
       <c r="CZ102" s="20"/>
       <c r="DA102" s="20"/>
       <c r="DB102" s="20"/>
-      <c r="DC102" s="8"/>
+      <c r="DC102" s="20"/>
       <c r="DD102" s="8"/>
       <c r="DE102" s="8"/>
       <c r="DF102" s="8"/>
@@ -27494,13 +27633,15 @@
         <v>4.2060642924826652</v>
       </c>
       <c r="CX103" s="16">
-        <v>2.1581611922945569</v>
-      </c>
-      <c r="CY103" s="20"/>
+        <v>2.1550749385453685</v>
+      </c>
+      <c r="CY103" s="16">
+        <v>1.2570323572360422</v>
+      </c>
       <c r="CZ103" s="20"/>
       <c r="DA103" s="20"/>
       <c r="DB103" s="20"/>
-      <c r="DC103" s="8"/>
+      <c r="DC103" s="20"/>
       <c r="DD103" s="8"/>
       <c r="DE103" s="8"/>
       <c r="DF103" s="8"/>
@@ -27875,13 +28016,15 @@
         <v>-38.645311294591842</v>
       </c>
       <c r="CX104" s="16">
-        <v>7.2100134965853897</v>
-      </c>
-      <c r="CY104" s="20"/>
+        <v>7.939128173620972</v>
+      </c>
+      <c r="CY104" s="16">
+        <v>22.370277424395056</v>
+      </c>
       <c r="CZ104" s="20"/>
       <c r="DA104" s="20"/>
       <c r="DB104" s="20"/>
-      <c r="DC104" s="8"/>
+      <c r="DC104" s="20"/>
       <c r="DD104" s="8"/>
       <c r="DE104" s="8"/>
       <c r="DF104" s="8"/>
@@ -28256,13 +28399,15 @@
         <v>10.543964285724144</v>
       </c>
       <c r="CX105" s="16">
-        <v>10.508430628742872</v>
-      </c>
-      <c r="CY105" s="20"/>
+        <v>12.5844668425013</v>
+      </c>
+      <c r="CY105" s="16">
+        <v>-10.06181892277742</v>
+      </c>
       <c r="CZ105" s="20"/>
       <c r="DA105" s="20"/>
       <c r="DB105" s="20"/>
-      <c r="DC105" s="8"/>
+      <c r="DC105" s="20"/>
       <c r="DD105" s="8"/>
       <c r="DE105" s="8"/>
       <c r="DF105" s="8"/>
@@ -28637,13 +28782,15 @@
         <v>11.65384241492022</v>
       </c>
       <c r="CX106" s="16">
-        <v>15.1863063613565</v>
-      </c>
-      <c r="CY106" s="20"/>
+        <v>15.776810680041265</v>
+      </c>
+      <c r="CY106" s="16">
+        <v>21.379879407218993</v>
+      </c>
       <c r="CZ106" s="20"/>
       <c r="DA106" s="20"/>
       <c r="DB106" s="20"/>
-      <c r="DC106" s="8"/>
+      <c r="DC106" s="20"/>
       <c r="DD106" s="8"/>
       <c r="DE106" s="8"/>
       <c r="DF106" s="8"/>
@@ -29018,13 +29165,15 @@
         <v>-6.5153569438053864</v>
       </c>
       <c r="CX107" s="16">
-        <v>-8.5924787919653625</v>
-      </c>
-      <c r="CY107" s="20"/>
+        <v>-8.8218583555709813</v>
+      </c>
+      <c r="CY107" s="16">
+        <v>0.93553028371549374</v>
+      </c>
       <c r="CZ107" s="20"/>
       <c r="DA107" s="20"/>
       <c r="DB107" s="20"/>
-      <c r="DC107" s="8"/>
+      <c r="DC107" s="20"/>
       <c r="DD107" s="8"/>
       <c r="DE107" s="8"/>
       <c r="DF107" s="8"/>
@@ -29399,13 +29548,15 @@
         <v>-19.86907730907329</v>
       </c>
       <c r="CX108" s="16">
-        <v>-7.6792317704039021</v>
-      </c>
-      <c r="CY108" s="20"/>
+        <v>-8.4063462821390402</v>
+      </c>
+      <c r="CY108" s="16">
+        <v>-19.576080429871055</v>
+      </c>
       <c r="CZ108" s="20"/>
       <c r="DA108" s="20"/>
       <c r="DB108" s="20"/>
-      <c r="DC108" s="8"/>
+      <c r="DC108" s="20"/>
       <c r="DD108" s="8"/>
       <c r="DE108" s="8"/>
       <c r="DF108" s="8"/>
@@ -29780,13 +29931,15 @@
         <v>1.2145586573577845</v>
       </c>
       <c r="CX109" s="16">
-        <v>0.19999784725411018</v>
-      </c>
-      <c r="CY109" s="20"/>
+        <v>-0.9412367351270774</v>
+      </c>
+      <c r="CY109" s="16">
+        <v>0.68089034803935533</v>
+      </c>
       <c r="CZ109" s="20"/>
       <c r="DA109" s="20"/>
       <c r="DB109" s="20"/>
-      <c r="DC109" s="8"/>
+      <c r="DC109" s="20"/>
       <c r="DD109" s="8"/>
       <c r="DE109" s="8"/>
       <c r="DF109" s="8"/>
@@ -30161,13 +30314,15 @@
         <v>2.612713713973875</v>
       </c>
       <c r="CX110" s="16">
-        <v>-1.93358541956556</v>
-      </c>
-      <c r="CY110" s="20"/>
+        <v>-0.52671494851804823</v>
+      </c>
+      <c r="CY110" s="16">
+        <v>24.653591925653259</v>
+      </c>
       <c r="CZ110" s="20"/>
       <c r="DA110" s="20"/>
       <c r="DB110" s="20"/>
-      <c r="DC110" s="8"/>
+      <c r="DC110" s="20"/>
       <c r="DD110" s="8"/>
       <c r="DE110" s="8"/>
       <c r="DF110" s="8"/>
@@ -30542,13 +30697,15 @@
         <v>18.367273213253725</v>
       </c>
       <c r="CX111" s="16">
-        <v>8.6447047074317425</v>
-      </c>
-      <c r="CY111" s="20"/>
+        <v>8.6889493107186127</v>
+      </c>
+      <c r="CY111" s="16">
+        <v>4.2380892302034567</v>
+      </c>
       <c r="CZ111" s="20"/>
       <c r="DA111" s="20"/>
       <c r="DB111" s="20"/>
-      <c r="DC111" s="8"/>
+      <c r="DC111" s="20"/>
       <c r="DD111" s="8"/>
       <c r="DE111" s="8"/>
       <c r="DF111" s="8"/>
@@ -30720,11 +30877,11 @@
       <c r="CV112" s="8"/>
       <c r="CW112" s="8"/>
       <c r="CX112" s="8"/>
-      <c r="CY112" s="7"/>
+      <c r="CY112" s="8"/>
       <c r="CZ112" s="7"/>
       <c r="DA112" s="7"/>
       <c r="DB112" s="7"/>
-      <c r="DC112" s="8"/>
+      <c r="DC112" s="7"/>
       <c r="DD112" s="8"/>
       <c r="DE112" s="8"/>
       <c r="DF112" s="8"/>
@@ -31099,13 +31256,15 @@
         <v>2.128526213851444</v>
       </c>
       <c r="CX113" s="16">
-        <v>2.1603792704449063</v>
-      </c>
-      <c r="CY113" s="20"/>
+        <v>2.3608136258554993</v>
+      </c>
+      <c r="CY113" s="16">
+        <v>7.6874246942811197</v>
+      </c>
       <c r="CZ113" s="20"/>
       <c r="DA113" s="20"/>
       <c r="DB113" s="20"/>
-      <c r="DC113" s="8"/>
+      <c r="DC113" s="20"/>
       <c r="DD113" s="8"/>
       <c r="DE113" s="8"/>
       <c r="DF113" s="8"/>
@@ -31278,19 +31437,20 @@
       <c r="CV114" s="10"/>
       <c r="CW114" s="10"/>
       <c r="CX114" s="10"/>
-      <c r="CY114" s="24"/>
+      <c r="CY114" s="10"/>
       <c r="CZ114" s="24"/>
       <c r="DA114" s="24"/>
       <c r="DB114" s="24"/>
+      <c r="DC114" s="24"/>
     </row>
     <row r="115" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A115" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CY115" s="4"/>
       <c r="CZ115" s="4"/>
       <c r="DA115" s="4"/>
       <c r="DB115" s="4"/>
+      <c r="DC115" s="4"/>
     </row>
     <row r="116" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="8"/>
@@ -31394,11 +31554,11 @@
       <c r="CV116" s="8"/>
       <c r="CW116" s="8"/>
       <c r="CX116" s="8"/>
-      <c r="CY116" s="7"/>
+      <c r="CY116" s="8"/>
       <c r="CZ116" s="7"/>
       <c r="DA116" s="7"/>
       <c r="DB116" s="7"/>
-      <c r="DC116" s="8"/>
+      <c r="DC116" s="7"/>
       <c r="DD116" s="8"/>
       <c r="DE116" s="8"/>
       <c r="DF116" s="8"/>
@@ -31570,11 +31730,11 @@
       <c r="CV117" s="8"/>
       <c r="CW117" s="8"/>
       <c r="CX117" s="8"/>
-      <c r="CY117" s="7"/>
+      <c r="CY117" s="8"/>
       <c r="CZ117" s="7"/>
       <c r="DA117" s="7"/>
       <c r="DB117" s="7"/>
-      <c r="DC117" s="8"/>
+      <c r="DC117" s="7"/>
       <c r="DD117" s="8"/>
       <c r="DE117" s="8"/>
       <c r="DF117" s="8"/>
@@ -31648,67 +31808,67 @@
       <c r="A118" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="CY118" s="4"/>
       <c r="CZ118" s="4"/>
       <c r="DA118" s="4"/>
       <c r="DB118" s="4"/>
+      <c r="DC118" s="4"/>
     </row>
     <row r="119" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="CY119" s="4"/>
       <c r="CZ119" s="4"/>
       <c r="DA119" s="4"/>
       <c r="DB119" s="4"/>
+      <c r="DC119" s="4"/>
     </row>
     <row r="120" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="CY120" s="4"/>
+        <v>73</v>
+      </c>
       <c r="CZ120" s="4"/>
       <c r="DA120" s="4"/>
       <c r="DB120" s="4"/>
+      <c r="DC120" s="4"/>
     </row>
     <row r="121" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY121" s="4"/>
       <c r="CZ121" s="4"/>
       <c r="DA121" s="4"/>
       <c r="DB121" s="4"/>
+      <c r="DC121" s="4"/>
     </row>
     <row r="122" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="CY122" s="4"/>
       <c r="CZ122" s="4"/>
       <c r="DA122" s="4"/>
       <c r="DB122" s="4"/>
+      <c r="DC122" s="4"/>
     </row>
     <row r="123" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="CY123" s="4"/>
+        <v>72</v>
+      </c>
       <c r="CZ123" s="4"/>
       <c r="DA123" s="4"/>
       <c r="DB123" s="4"/>
+      <c r="DC123" s="4"/>
     </row>
     <row r="124" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="CY124" s="4"/>
       <c r="CZ124" s="4"/>
       <c r="DA124" s="4"/>
       <c r="DB124" s="4"/>
+      <c r="DC124" s="4"/>
     </row>
     <row r="125" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY125" s="4"/>
       <c r="CZ125" s="4"/>
       <c r="DA125" s="4"/>
       <c r="DB125" s="4"/>
+      <c r="DC125" s="4"/>
     </row>
     <row r="126" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="17"/>
@@ -31863,12 +32023,13 @@
       <c r="CV126" s="21"/>
       <c r="CW126" s="21"/>
       <c r="CX126" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="CY126" s="22"/>
+        <v>71</v>
+      </c>
+      <c r="CY126" s="21"/>
       <c r="CZ126" s="22"/>
       <c r="DA126" s="22"/>
       <c r="DB126" s="22"/>
+      <c r="DC126" s="22"/>
     </row>
     <row r="127" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
@@ -32177,17 +32338,20 @@
       <c r="CX127" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY127" s="23"/>
+      <c r="CY127" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ127" s="23"/>
       <c r="DA127" s="23"/>
       <c r="DB127" s="23"/>
+      <c r="DC127" s="23"/>
     </row>
     <row r="128" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="6"/>
-      <c r="CY128" s="4"/>
       <c r="CZ128" s="4"/>
       <c r="DA128" s="4"/>
       <c r="DB128" s="4"/>
+      <c r="DC128" s="4"/>
     </row>
     <row r="129" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
@@ -32494,13 +32658,15 @@
         <v>6.3910046320353615</v>
       </c>
       <c r="CX129" s="16">
-        <v>-1.1627576512698141</v>
-      </c>
-      <c r="CY129" s="20"/>
+        <v>-0.99851969904646865</v>
+      </c>
+      <c r="CY129" s="16">
+        <v>2.0162108412458082</v>
+      </c>
       <c r="CZ129" s="20"/>
       <c r="DA129" s="20"/>
       <c r="DB129" s="20"/>
-      <c r="DC129" s="8"/>
+      <c r="DC129" s="20"/>
       <c r="DD129" s="8"/>
       <c r="DE129" s="8"/>
       <c r="DF129" s="8"/>
@@ -32875,13 +33041,15 @@
         <v>-3.1101492295421735</v>
       </c>
       <c r="CX130" s="16">
-        <v>3.4437017841743653</v>
-      </c>
-      <c r="CY130" s="20"/>
+        <v>3.5606152509499509</v>
+      </c>
+      <c r="CY130" s="16">
+        <v>-6.0053616110082686</v>
+      </c>
       <c r="CZ130" s="20"/>
       <c r="DA130" s="20"/>
       <c r="DB130" s="20"/>
-      <c r="DC130" s="8"/>
+      <c r="DC130" s="20"/>
       <c r="DD130" s="8"/>
       <c r="DE130" s="8"/>
       <c r="DF130" s="8"/>
@@ -33256,13 +33424,15 @@
         <v>8.4492842348747814</v>
       </c>
       <c r="CX131" s="16">
-        <v>5.8220014116035799</v>
-      </c>
-      <c r="CY131" s="20"/>
+        <v>5.8535197225735516</v>
+      </c>
+      <c r="CY131" s="16">
+        <v>3.5274249296001869</v>
+      </c>
       <c r="CZ131" s="20"/>
       <c r="DA131" s="20"/>
       <c r="DB131" s="20"/>
-      <c r="DC131" s="8"/>
+      <c r="DC131" s="20"/>
       <c r="DD131" s="8"/>
       <c r="DE131" s="8"/>
       <c r="DF131" s="8"/>
@@ -33637,13 +33807,15 @@
         <v>-5.5653187306029821</v>
       </c>
       <c r="CX132" s="16">
-        <v>17.799109664809649</v>
-      </c>
-      <c r="CY132" s="20"/>
+        <v>17.95203030598995</v>
+      </c>
+      <c r="CY132" s="16">
+        <v>10.379852218378204</v>
+      </c>
       <c r="CZ132" s="20"/>
       <c r="DA132" s="20"/>
       <c r="DB132" s="20"/>
-      <c r="DC132" s="8"/>
+      <c r="DC132" s="20"/>
       <c r="DD132" s="8"/>
       <c r="DE132" s="8"/>
       <c r="DF132" s="8"/>
@@ -34018,13 +34190,15 @@
         <v>-6.2851820923144004</v>
       </c>
       <c r="CX133" s="16">
-        <v>16.316366258265276</v>
-      </c>
-      <c r="CY133" s="20"/>
+        <v>14.42443440375007</v>
+      </c>
+      <c r="CY133" s="16">
+        <v>11.906017554226139</v>
+      </c>
       <c r="CZ133" s="20"/>
       <c r="DA133" s="20"/>
       <c r="DB133" s="20"/>
-      <c r="DC133" s="8"/>
+      <c r="DC133" s="20"/>
       <c r="DD133" s="8"/>
       <c r="DE133" s="8"/>
       <c r="DF133" s="8"/>
@@ -34399,13 +34573,15 @@
         <v>9.3180688810494701</v>
       </c>
       <c r="CX134" s="16">
-        <v>8.1138275847741852</v>
-      </c>
-      <c r="CY134" s="20"/>
+        <v>9.7642022567656142</v>
+      </c>
+      <c r="CY134" s="16">
+        <v>20.100013557966648</v>
+      </c>
       <c r="CZ134" s="20"/>
       <c r="DA134" s="20"/>
       <c r="DB134" s="20"/>
-      <c r="DC134" s="8"/>
+      <c r="DC134" s="20"/>
       <c r="DD134" s="8"/>
       <c r="DE134" s="8"/>
       <c r="DF134" s="8"/>
@@ -34780,13 +34956,15 @@
         <v>13.631819526107051</v>
       </c>
       <c r="CX135" s="16">
-        <v>11.583911325243974</v>
-      </c>
-      <c r="CY135" s="20"/>
+        <v>10.142522315114093</v>
+      </c>
+      <c r="CY135" s="16">
+        <v>-1.6350946466886569</v>
+      </c>
       <c r="CZ135" s="20"/>
       <c r="DA135" s="20"/>
       <c r="DB135" s="20"/>
-      <c r="DC135" s="8"/>
+      <c r="DC135" s="20"/>
       <c r="DD135" s="8"/>
       <c r="DE135" s="8"/>
       <c r="DF135" s="8"/>
@@ -35161,13 +35339,15 @@
         <v>6.5098165291881003</v>
       </c>
       <c r="CX136" s="16">
-        <v>-3.6649480562358008</v>
-      </c>
-      <c r="CY136" s="20"/>
+        <v>-6.1441441667595456</v>
+      </c>
+      <c r="CY136" s="16">
+        <v>0.57141176196321908</v>
+      </c>
       <c r="CZ136" s="20"/>
       <c r="DA136" s="20"/>
       <c r="DB136" s="20"/>
-      <c r="DC136" s="8"/>
+      <c r="DC136" s="20"/>
       <c r="DD136" s="8"/>
       <c r="DE136" s="8"/>
       <c r="DF136" s="8"/>
@@ -35542,13 +35722,15 @@
         <v>-14.152310254201467</v>
       </c>
       <c r="CX137" s="16">
-        <v>-12.899866258741895</v>
-      </c>
-      <c r="CY137" s="20"/>
+        <v>-8.5696388459199682</v>
+      </c>
+      <c r="CY137" s="16">
+        <v>2.3173541992832725</v>
+      </c>
       <c r="CZ137" s="20"/>
       <c r="DA137" s="20"/>
       <c r="DB137" s="20"/>
-      <c r="DC137" s="8"/>
+      <c r="DC137" s="20"/>
       <c r="DD137" s="8"/>
       <c r="DE137" s="8"/>
       <c r="DF137" s="8"/>
@@ -35923,13 +36105,15 @@
         <v>-6.7539873147461691</v>
       </c>
       <c r="CX138" s="16">
-        <v>-23.634319751473186</v>
-      </c>
-      <c r="CY138" s="20"/>
+        <v>-23.572091914423382</v>
+      </c>
+      <c r="CY138" s="16">
+        <v>20.457732855477872</v>
+      </c>
       <c r="CZ138" s="20"/>
       <c r="DA138" s="20"/>
       <c r="DB138" s="20"/>
-      <c r="DC138" s="8"/>
+      <c r="DC138" s="20"/>
       <c r="DD138" s="8"/>
       <c r="DE138" s="8"/>
       <c r="DF138" s="8"/>
@@ -36304,13 +36488,15 @@
         <v>-10.623076904660138</v>
       </c>
       <c r="CX139" s="16">
-        <v>-5.1971267718641911</v>
-      </c>
-      <c r="CY139" s="20"/>
+        <v>-5.1258492788059442</v>
+      </c>
+      <c r="CY139" s="16">
+        <v>-15.249152381646951</v>
+      </c>
       <c r="CZ139" s="20"/>
       <c r="DA139" s="20"/>
       <c r="DB139" s="20"/>
-      <c r="DC139" s="8"/>
+      <c r="DC139" s="20"/>
       <c r="DD139" s="8"/>
       <c r="DE139" s="8"/>
       <c r="DF139" s="8"/>
@@ -36685,13 +36871,15 @@
         <v>9.4294511471349409</v>
       </c>
       <c r="CX140" s="16">
-        <v>-1.6211349253856326</v>
-      </c>
-      <c r="CY140" s="20"/>
+        <v>-1.4973757413970503</v>
+      </c>
+      <c r="CY140" s="16">
+        <v>6.9103433812302058</v>
+      </c>
       <c r="CZ140" s="20"/>
       <c r="DA140" s="20"/>
       <c r="DB140" s="20"/>
-      <c r="DC140" s="8"/>
+      <c r="DC140" s="20"/>
       <c r="DD140" s="8"/>
       <c r="DE140" s="8"/>
       <c r="DF140" s="8"/>
@@ -37066,13 +37254,15 @@
         <v>-0.83948547016981934</v>
       </c>
       <c r="CX141" s="16">
-        <v>-5.8998920166408482</v>
-      </c>
-      <c r="CY141" s="20"/>
+        <v>-2.5448476719252113</v>
+      </c>
+      <c r="CY141" s="16">
+        <v>5.1400519909612399</v>
+      </c>
       <c r="CZ141" s="20"/>
       <c r="DA141" s="20"/>
       <c r="DB141" s="20"/>
-      <c r="DC141" s="8"/>
+      <c r="DC141" s="20"/>
       <c r="DD141" s="8"/>
       <c r="DE141" s="8"/>
       <c r="DF141" s="8"/>
@@ -37447,13 +37637,15 @@
         <v>5.8470122432635776</v>
       </c>
       <c r="CX142" s="16">
-        <v>2.93194964637091</v>
-      </c>
-      <c r="CY142" s="20"/>
+        <v>2.9288400160506427</v>
+      </c>
+      <c r="CY142" s="16">
+        <v>-1.1367505488575489</v>
+      </c>
       <c r="CZ142" s="20"/>
       <c r="DA142" s="20"/>
       <c r="DB142" s="20"/>
-      <c r="DC142" s="8"/>
+      <c r="DC142" s="20"/>
       <c r="DD142" s="8"/>
       <c r="DE142" s="8"/>
       <c r="DF142" s="8"/>
@@ -37828,13 +38020,15 @@
         <v>-39.367750512562218</v>
       </c>
       <c r="CX143" s="16">
-        <v>3.7593603771671553</v>
-      </c>
-      <c r="CY143" s="20"/>
+        <v>4.4650078261645092</v>
+      </c>
+      <c r="CY143" s="16">
+        <v>17.070744970938122</v>
+      </c>
       <c r="CZ143" s="20"/>
       <c r="DA143" s="20"/>
       <c r="DB143" s="20"/>
-      <c r="DC143" s="8"/>
+      <c r="DC143" s="20"/>
       <c r="DD143" s="8"/>
       <c r="DE143" s="8"/>
       <c r="DF143" s="8"/>
@@ -38209,13 +38403,15 @@
         <v>12.046660871218535</v>
       </c>
       <c r="CX144" s="16">
-        <v>8.6227549246004997</v>
-      </c>
-      <c r="CY144" s="20"/>
+        <v>10.658913224546623</v>
+      </c>
+      <c r="CY144" s="16">
+        <v>-11.547335429971071</v>
+      </c>
       <c r="CZ144" s="20"/>
       <c r="DA144" s="20"/>
       <c r="DB144" s="20"/>
-      <c r="DC144" s="8"/>
+      <c r="DC144" s="20"/>
       <c r="DD144" s="8"/>
       <c r="DE144" s="8"/>
       <c r="DF144" s="8"/>
@@ -38590,13 +38786,15 @@
         <v>11.518874060795994</v>
       </c>
       <c r="CX145" s="16">
-        <v>10.950335066988728</v>
-      </c>
-      <c r="CY145" s="20"/>
+        <v>11.519123615612273</v>
+      </c>
+      <c r="CY145" s="16">
+        <v>15.486128892821085</v>
+      </c>
       <c r="CZ145" s="20"/>
       <c r="DA145" s="20"/>
       <c r="DB145" s="20"/>
-      <c r="DC145" s="8"/>
+      <c r="DC145" s="20"/>
       <c r="DD145" s="8"/>
       <c r="DE145" s="8"/>
       <c r="DF145" s="8"/>
@@ -38971,13 +39169,15 @@
         <v>-6.6142892322296518</v>
       </c>
       <c r="CX146" s="16">
-        <v>-7.294896098226971</v>
-      </c>
-      <c r="CY146" s="20"/>
+        <v>-7.5275318375618809</v>
+      </c>
+      <c r="CY146" s="16">
+        <v>1.8488904992006496</v>
+      </c>
       <c r="CZ146" s="20"/>
       <c r="DA146" s="20"/>
       <c r="DB146" s="20"/>
-      <c r="DC146" s="8"/>
+      <c r="DC146" s="20"/>
       <c r="DD146" s="8"/>
       <c r="DE146" s="8"/>
       <c r="DF146" s="8"/>
@@ -39352,13 +39552,15 @@
         <v>-19.651557174121066</v>
       </c>
       <c r="CX147" s="16">
-        <v>-9.7595110409526313</v>
-      </c>
-      <c r="CY147" s="20"/>
+        <v>-10.470241360104851</v>
+      </c>
+      <c r="CY147" s="16">
+        <v>-21.972150377284933</v>
+      </c>
       <c r="CZ147" s="20"/>
       <c r="DA147" s="20"/>
       <c r="DB147" s="20"/>
-      <c r="DC147" s="8"/>
+      <c r="DC147" s="20"/>
       <c r="DD147" s="8"/>
       <c r="DE147" s="8"/>
       <c r="DF147" s="8"/>
@@ -39733,13 +39935,15 @@
         <v>0.92283124303132524</v>
       </c>
       <c r="CX148" s="16">
-        <v>-1.008754797264757</v>
-      </c>
-      <c r="CY148" s="20"/>
+        <v>-2.1374926358391946</v>
+      </c>
+      <c r="CY148" s="16">
+        <v>-1.8113242861767134</v>
+      </c>
       <c r="CZ148" s="20"/>
       <c r="DA148" s="20"/>
       <c r="DB148" s="20"/>
-      <c r="DC148" s="8"/>
+      <c r="DC148" s="20"/>
       <c r="DD148" s="8"/>
       <c r="DE148" s="8"/>
       <c r="DF148" s="8"/>
@@ -40114,13 +40318,15 @@
         <v>2.1591017776340919</v>
       </c>
       <c r="CX149" s="16">
-        <v>-3.3473487712047785</v>
-      </c>
-      <c r="CY149" s="20"/>
+        <v>-1.9026881466101031</v>
+      </c>
+      <c r="CY149" s="16">
+        <v>22.297172833655139</v>
+      </c>
       <c r="CZ149" s="20"/>
       <c r="DA149" s="20"/>
       <c r="DB149" s="20"/>
-      <c r="DC149" s="8"/>
+      <c r="DC149" s="20"/>
       <c r="DD149" s="8"/>
       <c r="DE149" s="8"/>
       <c r="DF149" s="8"/>
@@ -40495,13 +40701,15 @@
         <v>18.295322022049064</v>
       </c>
       <c r="CX150" s="16">
-        <v>8.6458048192394159</v>
-      </c>
-      <c r="CY150" s="20"/>
+        <v>8.689122623473537</v>
+      </c>
+      <c r="CY150" s="16">
+        <v>1.6504780701061605</v>
+      </c>
       <c r="CZ150" s="20"/>
       <c r="DA150" s="20"/>
       <c r="DB150" s="20"/>
-      <c r="DC150" s="8"/>
+      <c r="DC150" s="20"/>
       <c r="DD150" s="8"/>
       <c r="DE150" s="8"/>
       <c r="DF150" s="8"/>
@@ -40673,11 +40881,11 @@
       <c r="CV151" s="8"/>
       <c r="CW151" s="8"/>
       <c r="CX151" s="8"/>
-      <c r="CY151" s="7"/>
+      <c r="CY151" s="8"/>
       <c r="CZ151" s="7"/>
       <c r="DA151" s="7"/>
       <c r="DB151" s="7"/>
-      <c r="DC151" s="8"/>
+      <c r="DC151" s="7"/>
       <c r="DD151" s="8"/>
       <c r="DE151" s="8"/>
       <c r="DF151" s="8"/>
@@ -41052,13 +41260,15 @@
         <v>1.7708419752965767</v>
       </c>
       <c r="CX152" s="16">
-        <v>0.49468271573576317</v>
-      </c>
-      <c r="CY152" s="20"/>
+        <v>0.69498949826498801</v>
+      </c>
+      <c r="CY152" s="16">
+        <v>2.601175965753356</v>
+      </c>
       <c r="CZ152" s="20"/>
       <c r="DA152" s="20"/>
       <c r="DB152" s="20"/>
-      <c r="DC152" s="8"/>
+      <c r="DC152" s="20"/>
       <c r="DD152" s="8"/>
       <c r="DE152" s="8"/>
       <c r="DF152" s="8"/>
@@ -41231,19 +41441,20 @@
       <c r="CV153" s="10"/>
       <c r="CW153" s="10"/>
       <c r="CX153" s="10"/>
-      <c r="CY153" s="24"/>
+      <c r="CY153" s="10"/>
       <c r="CZ153" s="24"/>
       <c r="DA153" s="24"/>
       <c r="DB153" s="24"/>
+      <c r="DC153" s="24"/>
     </row>
     <row r="154" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A154" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CY154" s="4"/>
       <c r="CZ154" s="4"/>
       <c r="DA154" s="4"/>
       <c r="DB154" s="4"/>
+      <c r="DC154" s="4"/>
     </row>
     <row r="155" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B155" s="8"/>
@@ -41347,11 +41558,11 @@
       <c r="CV155" s="8"/>
       <c r="CW155" s="8"/>
       <c r="CX155" s="8"/>
-      <c r="CY155" s="7"/>
+      <c r="CY155" s="8"/>
       <c r="CZ155" s="7"/>
       <c r="DA155" s="7"/>
       <c r="DB155" s="7"/>
-      <c r="DC155" s="8"/>
+      <c r="DC155" s="7"/>
       <c r="DD155" s="8"/>
       <c r="DE155" s="8"/>
       <c r="DF155" s="8"/>
@@ -41606,7 +41817,7 @@
     </row>
     <row r="158" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="CZ158" s="6"/>
       <c r="DA158" s="6"/>
@@ -41618,7 +41829,7 @@
     </row>
     <row r="161" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="162" spans="1:179" x14ac:dyDescent="0.2">
@@ -41787,6 +41998,7 @@
       <c r="DB164" s="21">
         <v>2026</v>
       </c>
+      <c r="DC164" s="21"/>
     </row>
     <row r="165" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A165" s="5" t="s">
@@ -42106,6 +42318,9 @@
       </c>
       <c r="DB165" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC165" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="166" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -42428,9 +42643,11 @@
         <v>134.0009112412896</v>
       </c>
       <c r="DB167" s="16">
-        <v>123.82517368497858</v>
-      </c>
-      <c r="DC167" s="8"/>
+        <v>123.81903912089756</v>
+      </c>
+      <c r="DC167" s="16">
+        <v>103.76014334540034</v>
+      </c>
       <c r="DD167" s="8"/>
       <c r="DE167" s="8"/>
       <c r="DF167" s="8"/>
@@ -42821,9 +43038,11 @@
         <v>134.26059903443775</v>
       </c>
       <c r="DB168" s="16">
-        <v>117.44145820956311</v>
-      </c>
-      <c r="DC168" s="8"/>
+        <v>117.44026656786262</v>
+      </c>
+      <c r="DC168" s="16">
+        <v>109.13667465921688</v>
+      </c>
       <c r="DD168" s="8"/>
       <c r="DE168" s="8"/>
       <c r="DF168" s="8"/>
@@ -43214,9 +43433,11 @@
         <v>148.73823641789875</v>
       </c>
       <c r="DB169" s="16">
-        <v>103.97943091550204</v>
-      </c>
-      <c r="DC169" s="8"/>
+        <v>103.97943091550201</v>
+      </c>
+      <c r="DC169" s="16">
+        <v>102.76995437411338</v>
+      </c>
       <c r="DD169" s="8"/>
       <c r="DE169" s="8"/>
       <c r="DF169" s="8"/>
@@ -43607,9 +43828,11 @@
         <v>101.88675539619258</v>
       </c>
       <c r="DB170" s="16">
-        <v>90.847739570807121</v>
-      </c>
-      <c r="DC170" s="8"/>
+        <v>90.843142439904881</v>
+      </c>
+      <c r="DC170" s="16">
+        <v>88.549922681661315</v>
+      </c>
       <c r="DD170" s="8"/>
       <c r="DE170" s="8"/>
       <c r="DF170" s="8"/>
@@ -44000,9 +44223,11 @@
         <v>75.88969548718002</v>
       </c>
       <c r="DB171" s="16">
-        <v>93.306018240767131</v>
-      </c>
-      <c r="DC171" s="8"/>
+        <v>93.303597993345633</v>
+      </c>
+      <c r="DC171" s="16">
+        <v>86.648386057541373</v>
+      </c>
       <c r="DD171" s="8"/>
       <c r="DE171" s="8"/>
       <c r="DF171" s="8"/>
@@ -44393,9 +44618,11 @@
         <v>96.11698254275467</v>
       </c>
       <c r="DB172" s="16">
-        <v>85.188592929729083</v>
-      </c>
-      <c r="DC172" s="8"/>
+        <v>85.188592929729111</v>
+      </c>
+      <c r="DC172" s="16">
+        <v>123.26872882211413</v>
+      </c>
       <c r="DD172" s="8"/>
       <c r="DE172" s="8"/>
       <c r="DF172" s="8"/>
@@ -44786,9 +45013,11 @@
         <v>74.847683871071297</v>
       </c>
       <c r="DB173" s="16">
-        <v>73.067018087082303</v>
-      </c>
-      <c r="DC173" s="8"/>
+        <v>73.092500728108718</v>
+      </c>
+      <c r="DC173" s="16">
+        <v>55.286058350017619</v>
+      </c>
       <c r="DD173" s="8"/>
       <c r="DE173" s="8"/>
       <c r="DF173" s="8"/>
@@ -45179,9 +45408,11 @@
         <v>102.90212757130215</v>
       </c>
       <c r="DB174" s="16">
-        <v>92.521766131910056</v>
-      </c>
-      <c r="DC174" s="8"/>
+        <v>92.522861793850694</v>
+      </c>
+      <c r="DC174" s="16">
+        <v>75.354224397283119</v>
+      </c>
       <c r="DD174" s="8"/>
       <c r="DE174" s="8"/>
       <c r="DF174" s="8"/>
@@ -45572,9 +45803,11 @@
         <v>121.9581770413261</v>
       </c>
       <c r="DB175" s="16">
-        <v>95.828709187738028</v>
-      </c>
-      <c r="DC175" s="8"/>
+        <v>96.012731418323654</v>
+      </c>
+      <c r="DC175" s="16">
+        <v>109.7060648366909</v>
+      </c>
       <c r="DD175" s="8"/>
       <c r="DE175" s="8"/>
       <c r="DF175" s="8"/>
@@ -45967,7 +46200,9 @@
       <c r="DB176" s="16">
         <v>167.59042085543135</v>
       </c>
-      <c r="DC176" s="8"/>
+      <c r="DC176" s="16">
+        <v>143.07801523380638</v>
+      </c>
       <c r="DD176" s="8"/>
       <c r="DE176" s="8"/>
       <c r="DF176" s="8"/>
@@ -46358,9 +46593,11 @@
         <v>116.63977229920155</v>
       </c>
       <c r="DB177" s="16">
-        <v>76.886140199307647</v>
-      </c>
-      <c r="DC177" s="8"/>
+        <v>76.886502543529403</v>
+      </c>
+      <c r="DC177" s="16">
+        <v>82.471312593229925</v>
+      </c>
       <c r="DD177" s="8"/>
       <c r="DE177" s="8"/>
       <c r="DF177" s="8"/>
@@ -46753,7 +46990,9 @@
       <c r="DB178" s="16">
         <v>78.046599542828517</v>
       </c>
-      <c r="DC178" s="8"/>
+      <c r="DC178" s="16">
+        <v>60.021196795667663</v>
+      </c>
       <c r="DD178" s="8"/>
       <c r="DE178" s="8"/>
       <c r="DF178" s="8"/>
@@ -47144,9 +47383,11 @@
         <v>125.14746118504696</v>
       </c>
       <c r="DB179" s="16">
-        <v>116.12782134015329</v>
-      </c>
-      <c r="DC179" s="8"/>
+        <v>116.12956207459052</v>
+      </c>
+      <c r="DC179" s="16">
+        <v>96.042723879344535</v>
+      </c>
       <c r="DD179" s="8"/>
       <c r="DE179" s="8"/>
       <c r="DF179" s="8"/>
@@ -47539,7 +47780,9 @@
       <c r="DB180" s="16">
         <v>113.65664893130148</v>
       </c>
-      <c r="DC180" s="8"/>
+      <c r="DC180" s="16">
+        <v>93.164306433076035</v>
+      </c>
       <c r="DD180" s="8"/>
       <c r="DE180" s="8"/>
       <c r="DF180" s="8"/>
@@ -47930,9 +48173,11 @@
         <v>72.980093786738266</v>
       </c>
       <c r="DB181" s="16">
-        <v>66.001610314070518</v>
-      </c>
-      <c r="DC181" s="8"/>
+        <v>66.00161031407039</v>
+      </c>
+      <c r="DC181" s="16">
+        <v>53.425952574391879</v>
+      </c>
       <c r="DD181" s="8"/>
       <c r="DE181" s="8"/>
       <c r="DF181" s="8"/>
@@ -48323,9 +48568,11 @@
         <v>113.03470850848201</v>
       </c>
       <c r="DB182" s="16">
-        <v>114.91008833558105</v>
-      </c>
-      <c r="DC182" s="8"/>
+        <v>114.91471259954291</v>
+      </c>
+      <c r="DC182" s="16">
+        <v>79.850142514645782</v>
+      </c>
       <c r="DD182" s="8"/>
       <c r="DE182" s="8"/>
       <c r="DF182" s="8"/>
@@ -48718,7 +48965,9 @@
       <c r="DB183" s="16">
         <v>85.41870416400053</v>
       </c>
-      <c r="DC183" s="8"/>
+      <c r="DC183" s="16">
+        <v>101.41739496781798</v>
+      </c>
       <c r="DD183" s="8"/>
       <c r="DE183" s="8"/>
       <c r="DF183" s="8"/>
@@ -49111,7 +49360,9 @@
       <c r="DB184" s="16">
         <v>111.90930185955123</v>
       </c>
-      <c r="DC184" s="8"/>
+      <c r="DC184" s="16">
+        <v>74.212382308931268</v>
+      </c>
       <c r="DD184" s="8"/>
       <c r="DE184" s="8"/>
       <c r="DF184" s="8"/>
@@ -49504,7 +49755,9 @@
       <c r="DB185" s="16">
         <v>84.70852940882358</v>
       </c>
-      <c r="DC185" s="8"/>
+      <c r="DC185" s="16">
+        <v>95.055924052120744</v>
+      </c>
       <c r="DD185" s="8"/>
       <c r="DE185" s="8"/>
       <c r="DF185" s="8"/>
@@ -49895,9 +50148,11 @@
         <v>89.396729190121277</v>
       </c>
       <c r="DB186" s="16">
-        <v>91.013405805476793</v>
-      </c>
-      <c r="DC186" s="8"/>
+        <v>91.014587317586788</v>
+      </c>
+      <c r="DC186" s="16">
+        <v>76.650065700363228</v>
+      </c>
       <c r="DD186" s="8"/>
       <c r="DE186" s="8"/>
       <c r="DF186" s="8"/>
@@ -50288,9 +50543,11 @@
         <v>110.8087980093088</v>
       </c>
       <c r="DB187" s="16">
-        <v>89.456307337514815</v>
-      </c>
-      <c r="DC187" s="8"/>
+        <v>89.403350540773388</v>
+      </c>
+      <c r="DC187" s="16">
+        <v>97.571328895897864</v>
+      </c>
       <c r="DD187" s="8"/>
       <c r="DE187" s="8"/>
       <c r="DF187" s="8"/>
@@ -50681,9 +50938,11 @@
         <v>105.89513660901841</v>
       </c>
       <c r="DB188" s="16">
-        <v>95.862873616877181</v>
-      </c>
-      <c r="DC188" s="8"/>
+        <v>95.863691440831673</v>
+      </c>
+      <c r="DC188" s="16">
+        <v>83.836700860716348</v>
+      </c>
       <c r="DD188" s="8"/>
       <c r="DE188" s="8"/>
       <c r="DF188" s="8"/>
@@ -51254,9 +51513,11 @@
         <v>120.63039232297301</v>
       </c>
       <c r="DB190" s="16">
-        <v>108.35762019717734</v>
-      </c>
-      <c r="DC190" s="8"/>
+        <v>108.3542407632055</v>
+      </c>
+      <c r="DC190" s="16">
+        <v>99.887978943723994</v>
+      </c>
       <c r="DD190" s="8"/>
       <c r="DE190" s="8"/>
       <c r="DF190" s="8"/>
@@ -51437,6 +51698,7 @@
       <c r="CZ191" s="10"/>
       <c r="DA191" s="10"/>
       <c r="DB191" s="10"/>
+      <c r="DC191" s="10"/>
     </row>
     <row r="192" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A192" s="11" t="s">
@@ -51455,7 +51717,7 @@
     </row>
     <row r="197" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="199" spans="1:179" x14ac:dyDescent="0.2">
@@ -51465,7 +51727,7 @@
     </row>
     <row r="200" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="201" spans="1:179" x14ac:dyDescent="0.2">
@@ -51634,6 +51896,7 @@
       <c r="DB203" s="21">
         <v>2026</v>
       </c>
+      <c r="DC203" s="21"/>
     </row>
     <row r="204" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A204" s="5" t="s">
@@ -51953,6 +52216,9 @@
       </c>
       <c r="DB204" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC204" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="205" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -52275,9 +52541,11 @@
         <v>60.423026912769153</v>
       </c>
       <c r="DB206" s="16">
-        <v>62.460433709087447</v>
-      </c>
-      <c r="DC206" s="8"/>
+        <v>62.438622769141674</v>
+      </c>
+      <c r="DC206" s="16">
+        <v>53.454608015296145</v>
+      </c>
       <c r="DD206" s="8"/>
       <c r="DE206" s="8"/>
       <c r="DF206" s="8"/>
@@ -52668,9 +52936,11 @@
         <v>4.1673369041967545</v>
       </c>
       <c r="DB207" s="16">
-        <v>3.1290953189364838</v>
-      </c>
-      <c r="DC207" s="8"/>
+        <v>3.126466084234294</v>
+      </c>
+      <c r="DC207" s="16">
+        <v>3.6235391840580249</v>
+      </c>
       <c r="DD207" s="8"/>
       <c r="DE207" s="8"/>
       <c r="DF207" s="8"/>
@@ -53061,9 +53331,11 @@
         <v>0.27452884148988888</v>
       </c>
       <c r="DB208" s="16">
-        <v>0.24776302467087269</v>
-      </c>
-      <c r="DC208" s="8"/>
+        <v>0.24735152581856698</v>
+      </c>
+      <c r="DC208" s="16">
+        <v>0.33183245882753615</v>
+      </c>
       <c r="DD208" s="8"/>
       <c r="DE208" s="8"/>
       <c r="DF208" s="8"/>
@@ -53454,9 +53726,11 @@
         <v>0.70804801167050124</v>
       </c>
       <c r="DB209" s="16">
-        <v>0.90984268718556616</v>
-      </c>
-      <c r="DC209" s="8"/>
+        <v>0.90919389711762411</v>
+      </c>
+      <c r="DC209" s="16">
+        <v>1.0467509539214972</v>
+      </c>
       <c r="DD209" s="8"/>
       <c r="DE209" s="8"/>
       <c r="DF209" s="8"/>
@@ -53847,9 +54121,11 @@
         <v>0.57343459817602682</v>
       </c>
       <c r="DB210" s="16">
-        <v>1.1475729131913863</v>
-      </c>
-      <c r="DC210" s="8"/>
+        <v>1.1266674278836248</v>
+      </c>
+      <c r="DC210" s="16">
+        <v>1.1137670792876644</v>
+      </c>
       <c r="DD210" s="8"/>
       <c r="DE210" s="8"/>
       <c r="DF210" s="8"/>
@@ -54240,9 +54516,11 @@
         <v>0.52173121667914601</v>
       </c>
       <c r="DB211" s="16">
-        <v>0.24128843883805454</v>
-      </c>
-      <c r="DC211" s="8"/>
+        <v>0.24449206189337205</v>
+      </c>
+      <c r="DC211" s="16">
+        <v>0.23006562808685813</v>
+      </c>
       <c r="DD211" s="8"/>
       <c r="DE211" s="8"/>
       <c r="DF211" s="8"/>
@@ -54633,9 +54911,11 @@
         <v>0.9567671474837941</v>
       </c>
       <c r="DB212" s="16">
-        <v>0.52162242723113406</v>
-      </c>
-      <c r="DC212" s="8"/>
+        <v>0.51405536622054038</v>
+      </c>
+      <c r="DC212" s="16">
+        <v>0.62788536037742693</v>
+      </c>
       <c r="DD212" s="8"/>
       <c r="DE212" s="8"/>
       <c r="DF212" s="8"/>
@@ -55026,9 +55306,11 @@
         <v>0.49209693959136264</v>
       </c>
       <c r="DB213" s="16">
-        <v>0.51579085922132784</v>
-      </c>
-      <c r="DC213" s="8"/>
+        <v>0.50153886173306073</v>
+      </c>
+      <c r="DC213" s="16">
+        <v>0.64467081325716202</v>
+      </c>
       <c r="DD213" s="8"/>
       <c r="DE213" s="8"/>
       <c r="DF213" s="8"/>
@@ -55419,9 +55701,11 @@
         <v>0.66265184539923039</v>
       </c>
       <c r="DB214" s="16">
-        <v>0.80366058201820445</v>
-      </c>
-      <c r="DC214" s="8"/>
+        <v>0.84357992265812165</v>
+      </c>
+      <c r="DC214" s="16">
+        <v>1.3824723210399763</v>
+      </c>
       <c r="DD214" s="8"/>
       <c r="DE214" s="8"/>
       <c r="DF214" s="8"/>
@@ -55812,9 +56096,11 @@
         <v>4.4737680335472874</v>
       </c>
       <c r="DB215" s="16">
-        <v>1.1373791265147675</v>
-      </c>
-      <c r="DC215" s="8"/>
+        <v>1.1360770035337562</v>
+      </c>
+      <c r="DC215" s="16">
+        <v>8.7115502892284375</v>
+      </c>
       <c r="DD215" s="8"/>
       <c r="DE215" s="8"/>
       <c r="DF215" s="8"/>
@@ -56205,9 +56491,11 @@
         <v>12.074398697284028</v>
       </c>
       <c r="DB216" s="16">
-        <v>6.5266913196272629</v>
-      </c>
-      <c r="DC216" s="8"/>
+        <v>6.5188395027930852</v>
+      </c>
+      <c r="DC216" s="16">
+        <v>6.1802090948263579</v>
+      </c>
       <c r="DD216" s="8"/>
       <c r="DE216" s="8"/>
       <c r="DF216" s="8"/>
@@ -56598,9 +56886,11 @@
         <v>1.0380030340360229</v>
       </c>
       <c r="DB217" s="16">
-        <v>0.66241683759955694</v>
-      </c>
-      <c r="DC217" s="8"/>
+        <v>0.66195142758177605</v>
+      </c>
+      <c r="DC217" s="16">
+        <v>0.80440506726414573</v>
+      </c>
       <c r="DD217" s="8"/>
       <c r="DE217" s="8"/>
       <c r="DF217" s="8"/>
@@ -56991,9 +57281,11 @@
         <v>0.55532377743785921</v>
       </c>
       <c r="DB218" s="16">
-        <v>0.64707178106273922</v>
-      </c>
-      <c r="DC218" s="8"/>
+        <v>0.66884028100803394</v>
+      </c>
+      <c r="DC218" s="16">
+        <v>0.96725833655948423</v>
+      </c>
       <c r="DD218" s="8"/>
       <c r="DE218" s="8"/>
       <c r="DF218" s="8"/>
@@ -57384,9 +57676,11 @@
         <v>2.1215685849495172</v>
       </c>
       <c r="DB219" s="16">
-        <v>1.071662750875676</v>
-      </c>
-      <c r="DC219" s="8"/>
+        <v>1.0695319986868481</v>
+      </c>
+      <c r="DC219" s="16">
+        <v>1.8433804571908268</v>
+      </c>
       <c r="DD219" s="8"/>
       <c r="DE219" s="8"/>
       <c r="DF219" s="8"/>
@@ -57777,9 +58071,11 @@
         <v>0.47037753330321092</v>
       </c>
       <c r="DB220" s="16">
-        <v>1.1609018549541046</v>
-      </c>
-      <c r="DC220" s="8"/>
+        <v>1.1665082850820236</v>
+      </c>
+      <c r="DC220" s="16">
+        <v>0.77299508689430507</v>
+      </c>
       <c r="DD220" s="8"/>
       <c r="DE220" s="8"/>
       <c r="DF220" s="8"/>
@@ -58170,9 +58466,11 @@
         <v>0.87101476714937909</v>
       </c>
       <c r="DB221" s="16">
-        <v>0.5115691464889619</v>
-      </c>
-      <c r="DC221" s="8"/>
+        <v>0.52015906929064237</v>
+      </c>
+      <c r="DC221" s="16">
+        <v>0.9012400055781612</v>
+      </c>
       <c r="DD221" s="8"/>
       <c r="DE221" s="8"/>
       <c r="DF221" s="8"/>
@@ -58563,9 +58861,11 @@
         <v>4.2066916566209231</v>
       </c>
       <c r="DB222" s="16">
-        <v>11.470861908222881</v>
-      </c>
-      <c r="DC222" s="8"/>
+        <v>11.507091025725586</v>
+      </c>
+      <c r="DC222" s="16">
+        <v>11.588866367435362</v>
+      </c>
       <c r="DD222" s="8"/>
       <c r="DE222" s="8"/>
       <c r="DF222" s="8"/>
@@ -58956,9 +59256,11 @@
         <v>0.90437755372875117</v>
       </c>
       <c r="DB223" s="16">
-        <v>1.4239361463712903</v>
-      </c>
-      <c r="DC223" s="8"/>
+        <v>1.4175816617408048</v>
+      </c>
+      <c r="DC223" s="16">
+        <v>1.6895501388624594</v>
+      </c>
       <c r="DD223" s="8"/>
       <c r="DE223" s="8"/>
       <c r="DF223" s="8"/>
@@ -59349,9 +59651,11 @@
         <v>1.3393090265627707</v>
       </c>
       <c r="DB224" s="16">
-        <v>0.91146894163426762</v>
-      </c>
-      <c r="DC224" s="8"/>
+        <v>0.90251954506497289</v>
+      </c>
+      <c r="DC224" s="16">
+        <v>0.37772162890792482</v>
+      </c>
       <c r="DD224" s="8"/>
       <c r="DE224" s="8"/>
       <c r="DF224" s="8"/>
@@ -59742,9 +60046,11 @@
         <v>1.2569603478852309</v>
       </c>
       <c r="DB225" s="16">
-        <v>1.6535276179809371</v>
-      </c>
-      <c r="DC225" s="8"/>
+        <v>1.6314937326033983</v>
+      </c>
+      <c r="DC225" s="16">
+        <v>1.0360338880640776</v>
+      </c>
       <c r="DD225" s="8"/>
       <c r="DE225" s="8"/>
       <c r="DF225" s="8"/>
@@ -60135,9 +60441,11 @@
         <v>0.71852711362783184</v>
       </c>
       <c r="DB226" s="16">
-        <v>0.460849439603087</v>
-      </c>
-      <c r="DC226" s="8"/>
+        <v>0.46654548861694278</v>
+      </c>
+      <c r="DC226" s="16">
+        <v>0.45599913841548412</v>
+      </c>
       <c r="DD226" s="8"/>
       <c r="DE226" s="8"/>
       <c r="DF226" s="8"/>
@@ -60528,9 +60836,11 @@
         <v>1.1900574564113471</v>
       </c>
       <c r="DB227" s="16">
-        <v>2.3845931686839936</v>
-      </c>
-      <c r="DC227" s="8"/>
+        <v>2.3808930615712329</v>
+      </c>
+      <c r="DC227" s="16">
+        <v>2.2151986866206808</v>
+      </c>
       <c r="DD227" s="8"/>
       <c r="DE227" s="8"/>
       <c r="DF227" s="8"/>
@@ -61103,7 +61413,9 @@
       <c r="DB229" s="16">
         <v>100</v>
       </c>
-      <c r="DC229" s="8"/>
+      <c r="DC229" s="16">
+        <v>100</v>
+      </c>
       <c r="DD229" s="8"/>
       <c r="DE229" s="8"/>
       <c r="DF229" s="8"/>
@@ -61284,6 +61596,7 @@
       <c r="CZ230" s="10"/>
       <c r="DA230" s="10"/>
       <c r="DB230" s="10"/>
+      <c r="DC230" s="10"/>
     </row>
     <row r="231" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A231" s="11" t="s">
@@ -61662,7 +61975,7 @@
     </row>
     <row r="236" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A236" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="238" spans="1:179" x14ac:dyDescent="0.2">
@@ -61672,7 +61985,7 @@
     </row>
     <row r="239" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A239" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="240" spans="1:179" x14ac:dyDescent="0.2">
@@ -61841,6 +62154,7 @@
       <c r="DB242" s="21">
         <v>2026</v>
       </c>
+      <c r="DC242" s="21"/>
     </row>
     <row r="243" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A243" s="5" t="s">
@@ -62160,6 +62474,9 @@
       </c>
       <c r="DB243" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC243" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="244" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -62482,9 +62799,11 @@
         <v>54.394058774004726</v>
       </c>
       <c r="DB245" s="16">
-        <v>54.658222975069513</v>
-      </c>
-      <c r="DC245" s="8"/>
+        <v>54.640139452581948</v>
+      </c>
+      <c r="DC245" s="16">
+        <v>51.459766609060097</v>
+      </c>
       <c r="DD245" s="8"/>
       <c r="DE245" s="8"/>
       <c r="DF245" s="8"/>
@@ -62875,9 +63194,11 @@
         <v>3.7442666672916758</v>
       </c>
       <c r="DB246" s="16">
-        <v>2.887066690921551</v>
-      </c>
-      <c r="DC246" s="8"/>
+        <v>2.8845801251086551</v>
+      </c>
+      <c r="DC246" s="16">
+        <v>3.3164654031208323</v>
+      </c>
       <c r="DD246" s="8"/>
       <c r="DE246" s="8"/>
       <c r="DF246" s="8"/>
@@ -63268,9 +63589,11 @@
         <v>0.22264968746739427</v>
       </c>
       <c r="DB247" s="16">
-        <v>0.25819540932097707</v>
-      </c>
-      <c r="DC247" s="8"/>
+        <v>0.25775854460553188</v>
+      </c>
+      <c r="DC247" s="16">
+        <v>0.32252688893436177</v>
+      </c>
       <c r="DD247" s="8"/>
       <c r="DE247" s="8"/>
       <c r="DF247" s="8"/>
@@ -63661,9 +63984,11 @@
         <v>0.83830434190571257</v>
       </c>
       <c r="DB248" s="16">
-        <v>1.0852046380349685</v>
-      </c>
-      <c r="DC248" s="8"/>
+        <v>1.0844518560538612</v>
+      </c>
+      <c r="DC248" s="16">
+        <v>1.1807784137827082</v>
+      </c>
       <c r="DD248" s="8"/>
       <c r="DE248" s="8"/>
       <c r="DF248" s="8"/>
@@ -64054,9 +64379,11 @@
         <v>0.91150241288326073</v>
       </c>
       <c r="DB249" s="16">
-        <v>1.3326929197138384</v>
-      </c>
-      <c r="DC249" s="8"/>
+        <v>1.3084082111138993</v>
+      </c>
+      <c r="DC249" s="16">
+        <v>1.2839470834484916</v>
+      </c>
       <c r="DD249" s="8"/>
       <c r="DE249" s="8"/>
       <c r="DF249" s="8"/>
@@ -64447,9 +64774,11 @@
         <v>0.65479210530929843</v>
       </c>
       <c r="DB250" s="16">
-        <v>0.30691246462012567</v>
-      </c>
-      <c r="DC250" s="8"/>
+        <v>0.31097768877271698</v>
+      </c>
+      <c r="DC250" s="16">
+        <v>0.18642838969466213</v>
+      </c>
       <c r="DD250" s="8"/>
       <c r="DE250" s="8"/>
       <c r="DF250" s="8"/>
@@ -64840,9 +65169,11 @@
         <v>1.5420009062873614</v>
       </c>
       <c r="DB251" s="16">
-        <v>0.77356057953367641</v>
-      </c>
-      <c r="DC251" s="8"/>
+        <v>0.76204916184592897</v>
+      </c>
+      <c r="DC251" s="16">
+        <v>1.1344306598850338</v>
+      </c>
       <c r="DD251" s="8"/>
       <c r="DE251" s="8"/>
       <c r="DF251" s="8"/>
@@ -65233,9 +65564,11 @@
         <v>0.57687676907076446</v>
       </c>
       <c r="DB252" s="16">
-        <v>0.60407266701974915</v>
-      </c>
-      <c r="DC252" s="8"/>
+        <v>0.58735604933417573</v>
+      </c>
+      <c r="DC252" s="16">
+        <v>0.85456210498248542</v>
+      </c>
       <c r="DD252" s="8"/>
       <c r="DE252" s="8"/>
       <c r="DF252" s="8"/>
@@ -65626,9 +65959,11 @@
         <v>0.65543741324507121</v>
       </c>
       <c r="DB253" s="16">
-        <v>0.90873339369694806</v>
-      </c>
-      <c r="DC253" s="8"/>
+        <v>0.9520139745265076</v>
+      </c>
+      <c r="DC253" s="16">
+        <v>1.258748696344979</v>
+      </c>
       <c r="DD253" s="8"/>
       <c r="DE253" s="8"/>
       <c r="DF253" s="8"/>
@@ -66019,9 +66354,11 @@
         <v>4.5443190043326753</v>
       </c>
       <c r="DB254" s="16">
-        <v>0.73538627555209912</v>
-      </c>
-      <c r="DC254" s="8"/>
+        <v>0.73452146332770685</v>
+      </c>
+      <c r="DC254" s="16">
+        <v>6.0818508730056609</v>
+      </c>
       <c r="DD254" s="8"/>
       <c r="DE254" s="8"/>
       <c r="DF254" s="8"/>
@@ -66412,9 +66749,11 @@
         <v>12.487502531993004</v>
       </c>
       <c r="DB255" s="16">
-        <v>9.1982343933914059</v>
-      </c>
-      <c r="DC255" s="8"/>
+        <v>9.1868388028502022</v>
+      </c>
+      <c r="DC255" s="16">
+        <v>7.4853737199097674</v>
+      </c>
       <c r="DD255" s="8"/>
       <c r="DE255" s="8"/>
       <c r="DF255" s="8"/>
@@ -66805,9 +67144,11 @@
         <v>1.7076590855501914</v>
       </c>
       <c r="DB256" s="16">
-        <v>0.91968019774442034</v>
-      </c>
-      <c r="DC256" s="8"/>
+        <v>0.91900537342928978</v>
+      </c>
+      <c r="DC256" s="16">
+        <v>1.3387003377264475</v>
+      </c>
       <c r="DD256" s="8"/>
       <c r="DE256" s="8"/>
       <c r="DF256" s="8"/>
@@ -67198,9 +67539,11 @@
         <v>0.5352799369981015</v>
       </c>
       <c r="DB257" s="16">
-        <v>0.60377571441154565</v>
-      </c>
-      <c r="DC257" s="8"/>
+        <v>0.62405884897702146</v>
+      </c>
+      <c r="DC257" s="16">
+        <v>1.0059843833331172</v>
+      </c>
       <c r="DD257" s="8"/>
       <c r="DE257" s="8"/>
       <c r="DF257" s="8"/>
@@ -67591,9 +67934,11 @@
         <v>2.2743473558526595</v>
       </c>
       <c r="DB258" s="16">
-        <v>1.0216984789780137</v>
-      </c>
-      <c r="DC258" s="8"/>
+        <v>1.0196352679702405</v>
+      </c>
+      <c r="DC258" s="16">
+        <v>1.9764173141289827</v>
+      </c>
       <c r="DD258" s="8"/>
       <c r="DE258" s="8"/>
       <c r="DF258" s="8"/>
@@ -67984,9 +68329,11 @@
         <v>0.77749730697920261</v>
       </c>
       <c r="DB259" s="16">
-        <v>1.905901411900832</v>
-      </c>
-      <c r="DC259" s="8"/>
+        <v>1.9150459961899764</v>
+      </c>
+      <c r="DC259" s="16">
+        <v>1.4452323869338013</v>
+      </c>
       <c r="DD259" s="8"/>
       <c r="DE259" s="8"/>
       <c r="DF259" s="8"/>
@@ -68377,9 +68724,11 @@
         <v>0.92954504387869652</v>
       </c>
       <c r="DB260" s="16">
-        <v>0.48239816088176213</v>
-      </c>
-      <c r="DC260" s="8"/>
+        <v>0.4904632292428267</v>
+      </c>
+      <c r="DC260" s="16">
+        <v>1.1273999001807844</v>
+      </c>
       <c r="DD260" s="8"/>
       <c r="DE260" s="8"/>
       <c r="DF260" s="8"/>
@@ -68770,9 +69119,11 @@
         <v>6.7072237383376283</v>
       </c>
       <c r="DB261" s="16">
-        <v>14.551324679417505</v>
-      </c>
-      <c r="DC261" s="8"/>
+        <v>14.596827752054208</v>
+      </c>
+      <c r="DC261" s="16">
+        <v>11.414101496684502</v>
+      </c>
       <c r="DD261" s="8"/>
       <c r="DE261" s="8"/>
       <c r="DF261" s="8"/>
@@ -69163,9 +69514,11 @@
         <v>1.0628124923769069</v>
       </c>
       <c r="DB262" s="16">
-        <v>1.3787444794104387</v>
-      </c>
-      <c r="DC262" s="8"/>
+        <v>1.3725488598842379</v>
+      </c>
+      <c r="DC262" s="16">
+        <v>2.274091512013741</v>
+      </c>
       <c r="DD262" s="8"/>
       <c r="DE262" s="8"/>
       <c r="DF262" s="8"/>
@@ -69556,9 +69909,11 @@
         <v>1.5999364917345584</v>
       </c>
       <c r="DB263" s="16">
-        <v>1.1659346005461579</v>
-      </c>
-      <c r="DC263" s="8"/>
+        <v>1.1544506882831373</v>
+      </c>
+      <c r="DC263" s="16">
+        <v>0.39692265885770595</v>
+      </c>
       <c r="DD263" s="8"/>
       <c r="DE263" s="8"/>
       <c r="DF263" s="8"/>
@@ -69949,9 +70304,11 @@
         <v>1.69612044281114</v>
       </c>
       <c r="DB264" s="16">
-        <v>1.9686365544617372</v>
-      </c>
-      <c r="DC264" s="8"/>
+        <v>1.9423179285460577</v>
+      </c>
+      <c r="DC264" s="16">
+        <v>1.3501271036149769</v>
+      </c>
       <c r="DD264" s="8"/>
       <c r="DE264" s="8"/>
       <c r="DF264" s="8"/>
@@ -70342,9 +70699,11 @@
         <v>0.78221413072576862</v>
       </c>
       <c r="DB265" s="16">
-        <v>0.55822277971060064</v>
-      </c>
-      <c r="DC265" s="8"/>
+        <v>0.56543945942532314</v>
+      </c>
+      <c r="DC265" s="16">
+        <v>0.46682599132168978</v>
+      </c>
       <c r="DD265" s="8"/>
       <c r="DE265" s="8"/>
       <c r="DF265" s="8"/>
@@ -70735,9 +71094,11 @@
         <v>1.3556533609642119</v>
       </c>
       <c r="DB266" s="16">
-        <v>2.6954005356621504</v>
-      </c>
-      <c r="DC266" s="8"/>
+        <v>2.6911112658765424</v>
+      </c>
+      <c r="DC266" s="16">
+        <v>2.6393180730351671</v>
+      </c>
       <c r="DD266" s="8"/>
       <c r="DE266" s="8"/>
       <c r="DF266" s="8"/>
@@ -71310,7 +71671,9 @@
       <c r="DB268" s="16">
         <v>100</v>
       </c>
-      <c r="DC268" s="8"/>
+      <c r="DC268" s="16">
+        <v>100</v>
+      </c>
       <c r="DD268" s="8"/>
       <c r="DE268" s="8"/>
       <c r="DF268" s="8"/>
@@ -71491,6 +71854,7 @@
       <c r="CZ269" s="10"/>
       <c r="DA269" s="10"/>
       <c r="DB269" s="10"/>
+      <c r="DC269" s="10"/>
     </row>
     <row r="270" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A270" s="11" t="s">
@@ -71771,8 +72135,6 @@
       <c r="CM272" s="8"/>
       <c r="CN272" s="8"/>
       <c r="CO272" s="8"/>
-      <c r="DB272" s="7"/>
-      <c r="DC272" s="8"/>
       <c r="DD272" s="8"/>
       <c r="DE272" s="8"/>
       <c r="DF272" s="8"/>
@@ -71842,21 +72204,18 @@
       <c r="FR272" s="8"/>
       <c r="FS272" s="8"/>
     </row>
-    <row r="273" spans="106:106" x14ac:dyDescent="0.2">
-      <c r="DB273" s="8"/>
-    </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.3" top="1" bottom="0.16700000000000001" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="33" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="6" manualBreakCount="6">
-    <brk id="39" max="105" man="1"/>
-    <brk id="78" max="105" man="1"/>
-    <brk id="117" max="105" man="1"/>
-    <brk id="156" max="105" man="1"/>
-    <brk id="194" max="105" man="1"/>
-    <brk id="233" max="105" man="1"/>
+    <brk id="39" max="106" man="1"/>
+    <brk id="78" max="106" man="1"/>
+    <brk id="117" max="106" man="1"/>
+    <brk id="156" max="106" man="1"/>
+    <brk id="194" max="106" man="1"/>
+    <brk id="233" max="106" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>